--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY152"/>
+  <dimension ref="A1:AY151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128799069</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128800923</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128814701</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128801339</v>
+        <v>128814640</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456742</v>
+        <v>456331</v>
       </c>
       <c r="R5" t="n">
-        <v>6800421</v>
+        <v>6800312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1072,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128814640</v>
+        <v>128814658</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,16 +1112,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1136,7 +1134,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1146,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456331</v>
+        <v>456645</v>
       </c>
       <c r="R6" t="n">
-        <v>6800312</v>
+        <v>6800444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128814728</v>
+        <v>128803425</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456616</v>
+        <v>456681</v>
       </c>
       <c r="R7" t="n">
-        <v>6800533</v>
+        <v>6800496</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,9 +1274,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,22 +1301,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128814658</v>
+        <v>128803579</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,42 +1324,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456645</v>
+        <v>456698</v>
       </c>
       <c r="R8" t="n">
-        <v>6800444</v>
+        <v>6800503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,9 +1381,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,22 +1413,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128803579</v>
+        <v>128814728</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456698</v>
+        <v>456616</v>
       </c>
       <c r="R9" t="n">
-        <v>6800503</v>
+        <v>6800533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,24 +1493,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,44 +1510,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128803425</v>
+        <v>128801339</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456681</v>
+        <v>456742</v>
       </c>
       <c r="R10" t="n">
-        <v>6800496</v>
+        <v>6800421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
         <v>128805128</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>128804672</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128814681</v>
       </c>
       <c r="B13" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128814666</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128804638</v>
+        <v>128814744</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456748</v>
+        <v>456737</v>
       </c>
       <c r="R15" t="n">
-        <v>6800617</v>
+        <v>6800417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,19 +2113,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,22 +2130,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128804261</v>
+        <v>128814715</v>
       </c>
       <c r="B16" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456794</v>
+        <v>456589</v>
       </c>
       <c r="R16" t="n">
-        <v>6800605</v>
+        <v>6800303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,19 +2210,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,22 +2227,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814744</v>
+        <v>128805619</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456737</v>
+        <v>456600</v>
       </c>
       <c r="R17" t="n">
-        <v>6800417</v>
+        <v>6800539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,9 +2307,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2344,22 +2334,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128814729</v>
+        <v>128805376</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456606</v>
+        <v>456589</v>
       </c>
       <c r="R18" t="n">
-        <v>6800334</v>
+        <v>6800567</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,9 +2414,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,22 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128814693</v>
+        <v>128814729</v>
       </c>
       <c r="B19" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456515</v>
+        <v>456606</v>
       </c>
       <c r="R19" t="n">
-        <v>6800380</v>
+        <v>6800334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128814715</v>
+        <v>128804638</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456589</v>
+        <v>456748</v>
       </c>
       <c r="R20" t="n">
-        <v>6800303</v>
+        <v>6800617</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,9 +2618,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,22 +2645,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128814654</v>
+        <v>128814693</v>
       </c>
       <c r="B21" t="n">
-        <v>57686</v>
+        <v>78873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,42 +2668,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456705</v>
+        <v>456515</v>
       </c>
       <c r="R21" t="n">
-        <v>6800486</v>
+        <v>6800380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,10 +2754,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128805619</v>
+        <v>128804261</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,21 +2765,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2787,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456600</v>
+        <v>456794</v>
       </c>
       <c r="R22" t="n">
-        <v>6800539</v>
+        <v>6800605</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,10 +2861,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128805376</v>
+        <v>128814654</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,34 +2872,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456589</v>
+        <v>456705</v>
       </c>
       <c r="R23" t="n">
-        <v>6800567</v>
+        <v>6800486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,19 +2937,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,22 +2954,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128805061</v>
+        <v>128814673</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>78874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456690</v>
+        <v>456469</v>
       </c>
       <c r="R24" t="n">
-        <v>6800603</v>
+        <v>6800542</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,19 +3034,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,12 +3051,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3076,7 +3066,7 @@
         <v>128814652</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814673</v>
+        <v>128814644</v>
       </c>
       <c r="B26" t="n">
-        <v>78847</v>
+        <v>57713</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,34 +3179,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456469</v>
+        <v>456603</v>
       </c>
       <c r="R26" t="n">
-        <v>6800542</v>
+        <v>6800371</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814616</v>
+        <v>128814703</v>
       </c>
       <c r="B27" t="n">
-        <v>79708</v>
+        <v>78873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3284,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3308,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456487</v>
+        <v>456766</v>
       </c>
       <c r="R27" t="n">
-        <v>6800546</v>
+        <v>6800611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814716</v>
+        <v>128814616</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456477</v>
+        <v>456487</v>
       </c>
       <c r="R28" t="n">
-        <v>6800324</v>
+        <v>6800546</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,11 +3441,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3474,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814703</v>
+        <v>128814716</v>
       </c>
       <c r="B29" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3485,21 +3478,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3502,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456766</v>
+        <v>456477</v>
       </c>
       <c r="R29" t="n">
-        <v>6800611</v>
+        <v>6800324</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,6 +3538,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3571,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814644</v>
+        <v>128814724</v>
       </c>
       <c r="B30" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,42 +3580,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456603</v>
+        <v>456520</v>
       </c>
       <c r="R30" t="n">
-        <v>6800371</v>
+        <v>6800367</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3676,10 +3666,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128814724</v>
+        <v>128805061</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,21 +3677,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3711,10 +3701,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456520</v>
+        <v>456690</v>
       </c>
       <c r="R31" t="n">
-        <v>6800367</v>
+        <v>6800603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,9 +3734,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3761,22 +3761,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814692</v>
+        <v>128814720</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456354</v>
+        <v>456446</v>
       </c>
       <c r="R32" t="n">
-        <v>6800374</v>
+        <v>6800471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3873,7 +3873,7 @@
         <v>128814626</v>
       </c>
       <c r="B33" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814708</v>
+        <v>128814692</v>
       </c>
       <c r="B34" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456702</v>
+        <v>456354</v>
       </c>
       <c r="R34" t="n">
-        <v>6800512</v>
+        <v>6800374</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814720</v>
+        <v>128814708</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456446</v>
+        <v>456702</v>
       </c>
       <c r="R35" t="n">
-        <v>6800471</v>
+        <v>6800512</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814689</v>
+        <v>128814727</v>
       </c>
       <c r="B36" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456495</v>
+        <v>456600</v>
       </c>
       <c r="R36" t="n">
-        <v>6800433</v>
+        <v>6800519</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814743</v>
+        <v>128804553</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456566</v>
+        <v>456768</v>
       </c>
       <c r="R37" t="n">
-        <v>6800498</v>
+        <v>6800626</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,14 +4326,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4348,22 +4353,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814727</v>
+        <v>128814711</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,21 +4376,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4395,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456600</v>
+        <v>456642</v>
       </c>
       <c r="R38" t="n">
-        <v>6800519</v>
+        <v>6800358</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,7 +4465,7 @@
         <v>128814710</v>
       </c>
       <c r="B39" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4554,10 +4559,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128814711</v>
+        <v>128814689</v>
       </c>
       <c r="B40" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4589,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456642</v>
+        <v>456495</v>
       </c>
       <c r="R40" t="n">
-        <v>6800358</v>
+        <v>6800433</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4651,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128804553</v>
+        <v>128814743</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4662,21 +4667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4686,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456768</v>
+        <v>456566</v>
       </c>
       <c r="R41" t="n">
-        <v>6800626</v>
+        <v>6800498</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4719,19 +4724,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4746,22 +4746,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128814739</v>
+        <v>128814733</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456351</v>
+        <v>456547</v>
       </c>
       <c r="R42" t="n">
-        <v>6800353</v>
+        <v>6800300</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814733</v>
+        <v>128814739</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456547</v>
+        <v>456351</v>
       </c>
       <c r="R43" t="n">
-        <v>6800300</v>
+        <v>6800353</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4952,10 +4952,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128805036</v>
+        <v>128805352</v>
       </c>
       <c r="B44" t="n">
-        <v>79679</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4963,21 +4963,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456690</v>
+        <v>456605</v>
       </c>
       <c r="R44" t="n">
-        <v>6800603</v>
+        <v>6800580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5059,10 +5059,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128805352</v>
+        <v>128805036</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5070,21 +5070,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456605</v>
+        <v>456690</v>
       </c>
       <c r="R45" t="n">
-        <v>6800580</v>
+        <v>6800603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B46" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R46" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B47" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R47" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,10 +5380,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128814742</v>
+        <v>128814730</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456590</v>
+        <v>456589</v>
       </c>
       <c r="R48" t="n">
-        <v>6800535</v>
+        <v>6800302</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128814730</v>
+        <v>128814742</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456589</v>
+        <v>456590</v>
       </c>
       <c r="R49" t="n">
-        <v>6800302</v>
+        <v>6800535</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
         <v>128805326</v>
       </c>
       <c r="B50" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128799275</v>
+        <v>128814648</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,34 +5692,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456665</v>
+        <v>456618</v>
       </c>
       <c r="R51" t="n">
-        <v>6800399</v>
+        <v>6800564</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,24 +5757,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5781,22 +5774,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814612</v>
+        <v>128799275</v>
       </c>
       <c r="B52" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5804,21 +5797,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5828,10 +5821,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456539</v>
+        <v>456665</v>
       </c>
       <c r="R52" t="n">
-        <v>6800496</v>
+        <v>6800399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5861,9 +5854,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5878,22 +5886,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814719</v>
+        <v>128814612</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5901,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5925,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456527</v>
+        <v>456539</v>
       </c>
       <c r="R53" t="n">
-        <v>6800610</v>
+        <v>6800496</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5987,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814736</v>
+        <v>128814620</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5998,34 +6006,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456569</v>
+        <v>456385</v>
       </c>
       <c r="R54" t="n">
-        <v>6800599</v>
+        <v>6800430</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6066,6 +6077,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6084,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814620</v>
+        <v>128814719</v>
       </c>
       <c r="B55" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6095,37 +6107,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456385</v>
+        <v>456527</v>
       </c>
       <c r="R55" t="n">
-        <v>6800430</v>
+        <v>6800610</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6166,7 +6175,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6185,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814648</v>
+        <v>128814736</v>
       </c>
       <c r="B56" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6196,42 +6204,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456618</v>
+        <v>456569</v>
       </c>
       <c r="R56" t="n">
-        <v>6800564</v>
+        <v>6800599</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6293,7 +6293,7 @@
         <v>128814718</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>128802364</v>
       </c>
       <c r="B58" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128799700</v>
       </c>
       <c r="B59" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814735</v>
+        <v>128814628</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>79706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6612,21 +6612,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456477</v>
+        <v>456549</v>
       </c>
       <c r="R60" t="n">
-        <v>6800413</v>
+        <v>6800517</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814628</v>
+        <v>128814735</v>
       </c>
       <c r="B61" t="n">
-        <v>79679</v>
+        <v>79116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456549</v>
+        <v>456477</v>
       </c>
       <c r="R61" t="n">
-        <v>6800517</v>
+        <v>6800413</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
         <v>128814734</v>
       </c>
       <c r="B62" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>128802369</v>
       </c>
       <c r="B63" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>128802133</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128814656</v>
+        <v>128814721</v>
       </c>
       <c r="B65" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7122,42 +7122,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456658</v>
+        <v>456414</v>
       </c>
       <c r="R65" t="n">
-        <v>6800419</v>
+        <v>6800442</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7216,10 +7208,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128814660</v>
+        <v>128814675</v>
       </c>
       <c r="B66" t="n">
-        <v>57686</v>
+        <v>78874</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7227,31 +7219,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7259,10 +7246,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456747</v>
+        <v>456513</v>
       </c>
       <c r="R66" t="n">
-        <v>6800420</v>
+        <v>6800383</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7303,6 +7290,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7321,10 +7309,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128814675</v>
+        <v>128804576</v>
       </c>
       <c r="B67" t="n">
-        <v>78847</v>
+        <v>57713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7332,37 +7320,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456513</v>
+        <v>456761</v>
       </c>
       <c r="R67" t="n">
-        <v>6800383</v>
+        <v>6800606</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7392,40 +7382,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128814721</v>
+        <v>128814656</v>
       </c>
       <c r="B68" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7433,34 +7432,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456414</v>
+        <v>456658</v>
       </c>
       <c r="R68" t="n">
-        <v>6800442</v>
+        <v>6800419</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7519,10 +7526,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128804576</v>
+        <v>128814660</v>
       </c>
       <c r="B69" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7548,21 +7555,24 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456761</v>
+        <v>456747</v>
       </c>
       <c r="R69" t="n">
-        <v>6800606</v>
+        <v>6800420</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7592,19 +7602,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7619,22 +7619,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128814691</v>
+        <v>128799394</v>
       </c>
       <c r="B70" t="n">
-        <v>78846</v>
+        <v>91444</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456385</v>
+        <v>456679</v>
       </c>
       <c r="R70" t="n">
-        <v>6800430</v>
+        <v>6800380</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7699,9 +7699,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,22 +7726,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814717</v>
+        <v>128803330</v>
       </c>
       <c r="B71" t="n">
-        <v>79089</v>
+        <v>79706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7739,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7763,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456529</v>
+        <v>456690</v>
       </c>
       <c r="R71" t="n">
-        <v>6800501</v>
+        <v>6800454</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7796,9 +7806,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7813,12 +7833,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7828,7 +7848,7 @@
         <v>128814707</v>
       </c>
       <c r="B72" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7922,10 +7942,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814714</v>
+        <v>128814691</v>
       </c>
       <c r="B73" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7953,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456599</v>
+        <v>456385</v>
       </c>
       <c r="R73" t="n">
-        <v>6800361</v>
+        <v>6800430</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128814697</v>
+        <v>128814714</v>
       </c>
       <c r="B74" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,21 +8050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8054,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456499</v>
+        <v>456599</v>
       </c>
       <c r="R74" t="n">
-        <v>6800562</v>
+        <v>6800361</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,10 +8136,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128803330</v>
+        <v>128814697</v>
       </c>
       <c r="B75" t="n">
-        <v>79679</v>
+        <v>78873</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,21 +8147,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8151,10 +8171,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456690</v>
+        <v>456499</v>
       </c>
       <c r="R75" t="n">
-        <v>6800454</v>
+        <v>6800562</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,19 +8204,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8211,22 +8221,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128799394</v>
+        <v>128814717</v>
       </c>
       <c r="B76" t="n">
-        <v>91417</v>
+        <v>79116</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8234,21 +8244,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8258,10 +8268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456679</v>
+        <v>456529</v>
       </c>
       <c r="R76" t="n">
-        <v>6800380</v>
+        <v>6800501</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8291,19 +8301,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,22 +8318,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128800436</v>
+        <v>128814677</v>
       </c>
       <c r="B77" t="n">
-        <v>79708</v>
+        <v>78874</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456671</v>
+        <v>456747</v>
       </c>
       <c r="R77" t="n">
-        <v>6800350</v>
+        <v>6800569</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8398,19 +8398,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8425,65 +8415,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128800812</v>
+        <v>128801262</v>
       </c>
       <c r="B78" t="n">
-        <v>58059</v>
+        <v>78874</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456691</v>
+        <v>456703</v>
       </c>
       <c r="R78" t="n">
-        <v>6800368</v>
+        <v>6800429</v>
       </c>
       <c r="S78" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8549,48 +8534,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814677</v>
+        <v>128800812</v>
       </c>
       <c r="B79" t="n">
-        <v>78847</v>
+        <v>58086</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456747</v>
+        <v>456691</v>
       </c>
       <c r="R79" t="n">
-        <v>6800569</v>
+        <v>6800368</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8617,9 +8607,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8634,22 +8634,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814709</v>
+        <v>128814702</v>
       </c>
       <c r="B80" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8681,10 +8681,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456706</v>
+        <v>456788</v>
       </c>
       <c r="R80" t="n">
-        <v>6800520</v>
+        <v>6800626</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8743,10 +8743,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814702</v>
+        <v>128814695</v>
       </c>
       <c r="B81" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456788</v>
+        <v>456547</v>
       </c>
       <c r="R81" t="n">
-        <v>6800626</v>
+        <v>6800403</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,10 +8840,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814722</v>
+        <v>128814709</v>
       </c>
       <c r="B82" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8851,21 +8851,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456349</v>
+        <v>456706</v>
       </c>
       <c r="R82" t="n">
-        <v>6800436</v>
+        <v>6800520</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128814695</v>
+        <v>128814618</v>
       </c>
       <c r="B83" t="n">
-        <v>78846</v>
+        <v>79735</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8948,21 +8948,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8972,10 +8972,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456547</v>
+        <v>456450</v>
       </c>
       <c r="R83" t="n">
-        <v>6800403</v>
+        <v>6800571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9034,10 +9034,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814618</v>
+        <v>128800436</v>
       </c>
       <c r="B84" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9069,10 +9069,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456450</v>
+        <v>456671</v>
       </c>
       <c r="R84" t="n">
-        <v>6800571</v>
+        <v>6800350</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9102,9 +9102,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9119,22 +9129,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128801262</v>
+        <v>128814722</v>
       </c>
       <c r="B85" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9142,21 +9152,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9166,10 +9176,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456703</v>
+        <v>456349</v>
       </c>
       <c r="R85" t="n">
-        <v>6800429</v>
+        <v>6800436</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9199,19 +9209,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9226,22 +9226,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814741</v>
+        <v>128814630</v>
       </c>
       <c r="B86" t="n">
-        <v>79089</v>
+        <v>79706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456637</v>
+        <v>456496</v>
       </c>
       <c r="R86" t="n">
-        <v>6800536</v>
+        <v>6800554</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814726</v>
+        <v>128814741</v>
       </c>
       <c r="B87" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456524</v>
+        <v>456637</v>
       </c>
       <c r="R87" t="n">
-        <v>6800431</v>
+        <v>6800536</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9435,7 +9435,7 @@
         <v>128814723</v>
       </c>
       <c r="B88" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814630</v>
+        <v>128814726</v>
       </c>
       <c r="B89" t="n">
-        <v>79679</v>
+        <v>79116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456496</v>
+        <v>456524</v>
       </c>
       <c r="R89" t="n">
-        <v>6800554</v>
+        <v>6800431</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9629,7 +9629,7 @@
         <v>128799696</v>
       </c>
       <c r="B90" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9733,10 +9733,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128804256</v>
+        <v>128814637</v>
       </c>
       <c r="B91" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9744,34 +9744,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456794</v>
+        <v>456352</v>
       </c>
       <c r="R91" t="n">
-        <v>6800605</v>
+        <v>6800325</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9801,19 +9809,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9828,22 +9826,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814705</v>
+        <v>128814694</v>
       </c>
       <c r="B92" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9875,10 +9873,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456749</v>
+        <v>456594</v>
       </c>
       <c r="R92" t="n">
-        <v>6800566</v>
+        <v>6800423</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9937,10 +9935,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814622</v>
+        <v>128814690</v>
       </c>
       <c r="B93" t="n">
-        <v>79708</v>
+        <v>78873</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9948,21 +9946,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9972,10 +9970,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456546</v>
+        <v>456465</v>
       </c>
       <c r="R93" t="n">
-        <v>6800434</v>
+        <v>6800546</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10037,7 +10035,7 @@
         <v>128814732</v>
       </c>
       <c r="B94" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10131,10 +10129,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814690</v>
+        <v>128814699</v>
       </c>
       <c r="B95" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10166,10 +10164,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456465</v>
+        <v>456496</v>
       </c>
       <c r="R95" t="n">
-        <v>6800546</v>
+        <v>6800549</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10228,10 +10226,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814699</v>
+        <v>128814705</v>
       </c>
       <c r="B96" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10263,10 +10261,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456496</v>
+        <v>456749</v>
       </c>
       <c r="R96" t="n">
-        <v>6800549</v>
+        <v>6800566</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10325,10 +10323,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814694</v>
+        <v>128814622</v>
       </c>
       <c r="B97" t="n">
-        <v>78846</v>
+        <v>79735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10336,21 +10334,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10360,10 +10358,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456594</v>
+        <v>456546</v>
       </c>
       <c r="R97" t="n">
-        <v>6800423</v>
+        <v>6800434</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10422,10 +10420,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128814637</v>
+        <v>128804256</v>
       </c>
       <c r="B98" t="n">
-        <v>57689</v>
+        <v>79735</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10433,42 +10431,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456352</v>
+        <v>456794</v>
       </c>
       <c r="R98" t="n">
-        <v>6800325</v>
+        <v>6800605</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10498,9 +10488,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10515,12 +10515,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10530,7 +10530,7 @@
         <v>128814664</v>
       </c>
       <c r="B99" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128814632</v>
+        <v>128814624</v>
       </c>
       <c r="B100" t="n">
-        <v>79679</v>
+        <v>79735</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10643,34 +10643,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456382</v>
+        <v>456688</v>
       </c>
       <c r="R100" t="n">
-        <v>6800427</v>
+        <v>6800585</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10711,6 +10714,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10729,48 +10733,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128814713</v>
+        <v>128805203</v>
       </c>
       <c r="B101" t="n">
-        <v>90849</v>
+        <v>79116</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456692</v>
+        <v>456650</v>
       </c>
       <c r="R101" t="n">
-        <v>6800391</v>
+        <v>6800594</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10800,40 +10801,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814698</v>
+        <v>128814737</v>
       </c>
       <c r="B102" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10841,21 +10851,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10865,10 +10875,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456491</v>
+        <v>456555</v>
       </c>
       <c r="R102" t="n">
-        <v>6800537</v>
+        <v>6800627</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10927,10 +10937,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814737</v>
+        <v>128814698</v>
       </c>
       <c r="B103" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10938,21 +10948,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10962,10 +10972,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456555</v>
+        <v>456491</v>
       </c>
       <c r="R103" t="n">
-        <v>6800627</v>
+        <v>6800537</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11024,10 +11034,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128814624</v>
+        <v>128804050</v>
       </c>
       <c r="B104" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11035,37 +11045,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456688</v>
+        <v>456753</v>
       </c>
       <c r="R104" t="n">
-        <v>6800585</v>
+        <v>6800562</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11095,40 +11102,54 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814683</v>
+        <v>128814632</v>
       </c>
       <c r="B105" t="n">
-        <v>78847</v>
+        <v>79706</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11136,37 +11157,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456644</v>
+        <v>456382</v>
       </c>
       <c r="R105" t="n">
-        <v>6800358</v>
+        <v>6800427</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11207,7 +11225,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11226,45 +11243,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814725</v>
+        <v>128814713</v>
       </c>
       <c r="B106" t="n">
-        <v>79089</v>
+        <v>90876</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456598</v>
+        <v>456692</v>
       </c>
       <c r="R106" t="n">
-        <v>6800407</v>
+        <v>6800391</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11299,17 +11319,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11328,10 +11344,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128804554</v>
+        <v>128805054</v>
       </c>
       <c r="B107" t="n">
-        <v>78847</v>
+        <v>79735</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11339,21 +11355,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11363,10 +11379,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456768</v>
+        <v>456690</v>
       </c>
       <c r="R107" t="n">
-        <v>6800626</v>
+        <v>6800603</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11435,10 +11451,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128804050</v>
+        <v>128804554</v>
       </c>
       <c r="B108" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11446,21 +11462,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11470,10 +11486,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456753</v>
+        <v>456768</v>
       </c>
       <c r="R108" t="n">
-        <v>6800562</v>
+        <v>6800626</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11516,11 +11532,6 @@
       <c r="AB108" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11547,10 +11558,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128805203</v>
+        <v>128814725</v>
       </c>
       <c r="B109" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11582,10 +11593,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456650</v>
+        <v>456598</v>
       </c>
       <c r="R109" t="n">
-        <v>6800594</v>
+        <v>6800407</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11615,19 +11626,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11642,22 +11648,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128805054</v>
+        <v>128814683</v>
       </c>
       <c r="B110" t="n">
-        <v>79708</v>
+        <v>78874</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11665,34 +11671,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456690</v>
+        <v>456644</v>
       </c>
       <c r="R110" t="n">
-        <v>6800603</v>
+        <v>6800358</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11722,71 +11731,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128800793</v>
+        <v>128803369</v>
       </c>
       <c r="B111" t="n">
-        <v>91728</v>
+        <v>79735</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456671</v>
+        <v>456688</v>
       </c>
       <c r="R111" t="n">
-        <v>6800350</v>
+        <v>6800474</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11842,11 +11842,6 @@
       <c r="AB111" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11873,10 +11868,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814731</v>
+        <v>128814687</v>
       </c>
       <c r="B112" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11884,21 +11879,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11908,10 +11903,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456580</v>
+        <v>456556</v>
       </c>
       <c r="R112" t="n">
-        <v>6800292</v>
+        <v>6800320</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11970,10 +11965,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814696</v>
+        <v>128805558</v>
       </c>
       <c r="B113" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11981,21 +11976,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12005,10 +12000,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456559</v>
+        <v>456627</v>
       </c>
       <c r="R113" t="n">
-        <v>6800576</v>
+        <v>6800521</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12038,9 +12033,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12055,22 +12060,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814646</v>
+        <v>128814614</v>
       </c>
       <c r="B114" t="n">
-        <v>57686</v>
+        <v>79735</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12078,42 +12083,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456519</v>
+        <v>456522</v>
       </c>
       <c r="R114" t="n">
-        <v>6800414</v>
+        <v>6800319</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12172,10 +12169,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814614</v>
+        <v>128814731</v>
       </c>
       <c r="B115" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12183,21 +12180,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12207,10 +12204,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456522</v>
+        <v>456580</v>
       </c>
       <c r="R115" t="n">
-        <v>6800319</v>
+        <v>6800292</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12269,10 +12266,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814679</v>
+        <v>128814696</v>
       </c>
       <c r="B116" t="n">
-        <v>78847</v>
+        <v>78873</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12280,21 +12277,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12304,10 +12301,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456753</v>
+        <v>456559</v>
       </c>
       <c r="R116" t="n">
-        <v>6800533</v>
+        <v>6800576</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12369,7 +12366,7 @@
         <v>128814634</v>
       </c>
       <c r="B117" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12471,10 +12468,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814687</v>
+        <v>128814679</v>
       </c>
       <c r="B118" t="n">
-        <v>78846</v>
+        <v>78874</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12482,21 +12479,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12506,10 +12503,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456556</v>
+        <v>456753</v>
       </c>
       <c r="R118" t="n">
-        <v>6800320</v>
+        <v>6800533</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12568,10 +12565,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128803369</v>
+        <v>128814646</v>
       </c>
       <c r="B119" t="n">
-        <v>79708</v>
+        <v>57713</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12579,34 +12576,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456688</v>
+        <v>456519</v>
       </c>
       <c r="R119" t="n">
-        <v>6800474</v>
+        <v>6800414</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12636,19 +12641,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12663,22 +12658,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128805558</v>
+        <v>128814706</v>
       </c>
       <c r="B120" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12686,21 +12681,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12710,10 +12705,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>456627</v>
+        <v>456703</v>
       </c>
       <c r="R120" t="n">
-        <v>6800521</v>
+        <v>6800495</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12743,19 +12738,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12770,22 +12755,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128805585</v>
+        <v>128804496</v>
       </c>
       <c r="B121" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12793,21 +12778,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12817,10 +12802,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>456604</v>
+        <v>456753</v>
       </c>
       <c r="R121" t="n">
-        <v>6800527</v>
+        <v>6800630</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12889,10 +12874,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128804496</v>
+        <v>128814700</v>
       </c>
       <c r="B122" t="n">
-        <v>79708</v>
+        <v>78873</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12900,21 +12885,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12924,10 +12909,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>456753</v>
+        <v>456507</v>
       </c>
       <c r="R122" t="n">
-        <v>6800630</v>
+        <v>6800413</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12957,19 +12942,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12984,22 +12959,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128814706</v>
+        <v>128805585</v>
       </c>
       <c r="B123" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13007,21 +12982,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13031,10 +13006,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>456703</v>
+        <v>456604</v>
       </c>
       <c r="R123" t="n">
-        <v>6800495</v>
+        <v>6800527</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13064,9 +13039,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13081,22 +13066,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128814700</v>
+        <v>128816339</v>
       </c>
       <c r="B124" t="n">
-        <v>78846</v>
+        <v>79706</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13104,34 +13089,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Millberget, Dlr</t>
+          <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>456507</v>
+        <v>456522</v>
       </c>
       <c r="R124" t="n">
-        <v>6800413</v>
+        <v>6800344</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13172,28 +13160,29 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128816339</v>
+        <v>128816342</v>
       </c>
       <c r="B125" t="n">
-        <v>79679</v>
+        <v>57716</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13201,26 +13190,31 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13228,10 +13222,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>456522</v>
+        <v>456400</v>
       </c>
       <c r="R125" t="n">
-        <v>6800344</v>
+        <v>6800460</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13272,7 +13266,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13291,10 +13284,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128816342</v>
+        <v>128816336</v>
       </c>
       <c r="B126" t="n">
-        <v>57689</v>
+        <v>79735</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13302,42 +13295,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>456400</v>
+        <v>456691</v>
       </c>
       <c r="R126" t="n">
-        <v>6800460</v>
+        <v>6800607</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13396,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816336</v>
+        <v>128816343</v>
       </c>
       <c r="B127" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13407,34 +13392,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456691</v>
+        <v>456341</v>
       </c>
       <c r="R127" t="n">
-        <v>6800607</v>
+        <v>6800306</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13493,10 +13486,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816343</v>
+        <v>128816353</v>
       </c>
       <c r="B128" t="n">
-        <v>57689</v>
+        <v>78873</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13504,42 +13497,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456341</v>
+        <v>456522</v>
       </c>
       <c r="R128" t="n">
-        <v>6800306</v>
+        <v>6800357</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13601,7 +13586,7 @@
         <v>128816338</v>
       </c>
       <c r="B129" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13699,10 +13684,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128816353</v>
+        <v>128816347</v>
       </c>
       <c r="B130" t="n">
-        <v>78846</v>
+        <v>78874</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13710,34 +13695,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>456522</v>
+        <v>456473</v>
       </c>
       <c r="R130" t="n">
-        <v>6800357</v>
+        <v>6800370</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13778,6 +13766,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13796,10 +13785,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128816347</v>
+        <v>128816349</v>
       </c>
       <c r="B131" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13825,19 +13814,16 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>456473</v>
+        <v>456688</v>
       </c>
       <c r="R131" t="n">
-        <v>6800370</v>
+        <v>6800401</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13878,7 +13864,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13897,10 +13882,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128816349</v>
+        <v>128816354</v>
       </c>
       <c r="B132" t="n">
-        <v>78847</v>
+        <v>78873</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13908,21 +13893,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13932,10 +13917,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>456688</v>
+        <v>456692</v>
       </c>
       <c r="R132" t="n">
-        <v>6800401</v>
+        <v>6800605</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13994,10 +13979,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128816354</v>
+        <v>128816356</v>
       </c>
       <c r="B133" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14029,10 +14014,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>456692</v>
+        <v>456672</v>
       </c>
       <c r="R133" t="n">
-        <v>6800605</v>
+        <v>6800413</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14094,7 +14079,7 @@
         <v>128816351</v>
       </c>
       <c r="B134" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14192,10 +14177,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128816356</v>
+        <v>128816340</v>
       </c>
       <c r="B135" t="n">
-        <v>78846</v>
+        <v>79706</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14203,34 +14188,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>456672</v>
+        <v>456564</v>
       </c>
       <c r="R135" t="n">
-        <v>6800413</v>
+        <v>6800618</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14271,6 +14259,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14289,10 +14278,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128816340</v>
+        <v>128816331</v>
       </c>
       <c r="B136" t="n">
-        <v>79679</v>
+        <v>79148</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14300,21 +14289,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14327,10 +14316,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>456564</v>
+        <v>456376</v>
       </c>
       <c r="R136" t="n">
-        <v>6800618</v>
+        <v>6800472</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14393,7 +14382,7 @@
         <v>128816335</v>
       </c>
       <c r="B137" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14487,10 +14476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128816331</v>
+        <v>128816348</v>
       </c>
       <c r="B138" t="n">
-        <v>79121</v>
+        <v>78874</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14498,37 +14487,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>456376</v>
+        <v>456703</v>
       </c>
       <c r="R138" t="n">
-        <v>6800472</v>
+        <v>6800475</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14569,7 +14555,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14588,10 +14573,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128816348</v>
+        <v>128816352</v>
       </c>
       <c r="B139" t="n">
-        <v>78847</v>
+        <v>78873</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14599,34 +14584,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456703</v>
+        <v>456483</v>
       </c>
       <c r="R139" t="n">
-        <v>6800475</v>
+        <v>6800432</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14667,6 +14655,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14685,10 +14674,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128816352</v>
+        <v>128816350</v>
       </c>
       <c r="B140" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14723,10 +14712,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>456483</v>
+        <v>456521</v>
       </c>
       <c r="R140" t="n">
-        <v>6800432</v>
+        <v>6800343</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14786,10 +14775,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128816350</v>
+        <v>128816334</v>
       </c>
       <c r="B141" t="n">
-        <v>78846</v>
+        <v>79148</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14797,37 +14786,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>456521</v>
+        <v>456751</v>
       </c>
       <c r="R141" t="n">
-        <v>6800343</v>
+        <v>6800479</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14868,7 +14854,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14887,10 +14872,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128816334</v>
+        <v>128816358</v>
       </c>
       <c r="B142" t="n">
-        <v>79121</v>
+        <v>79116</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14898,21 +14883,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14922,10 +14907,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>456751</v>
+        <v>456463</v>
       </c>
       <c r="R142" t="n">
-        <v>6800479</v>
+        <v>6800400</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14984,10 +14969,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128816358</v>
+        <v>128816361</v>
       </c>
       <c r="B143" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15019,10 +15004,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>456463</v>
+        <v>456636</v>
       </c>
       <c r="R143" t="n">
-        <v>6800400</v>
+        <v>6800408</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15081,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816361</v>
+        <v>128816359</v>
       </c>
       <c r="B144" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15116,10 +15101,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456636</v>
+        <v>456335</v>
       </c>
       <c r="R144" t="n">
-        <v>6800408</v>
+        <v>6800427</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15178,10 +15163,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816332</v>
+        <v>128816345</v>
       </c>
       <c r="B145" t="n">
-        <v>79121</v>
+        <v>57713</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15189,26 +15174,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15216,10 +15206,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456355</v>
+        <v>456606</v>
       </c>
       <c r="R145" t="n">
-        <v>6800454</v>
+        <v>6800517</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15260,7 +15250,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15279,10 +15268,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816359</v>
+        <v>128816332</v>
       </c>
       <c r="B146" t="n">
-        <v>79089</v>
+        <v>79148</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15290,34 +15279,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456335</v>
+        <v>456355</v>
       </c>
       <c r="R146" t="n">
-        <v>6800427</v>
+        <v>6800454</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15358,6 +15350,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15376,10 +15369,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128816345</v>
+        <v>128816346</v>
       </c>
       <c r="B147" t="n">
-        <v>57686</v>
+        <v>78874</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15387,31 +15380,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -15419,10 +15407,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>456606</v>
+        <v>456521</v>
       </c>
       <c r="R147" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15463,6 +15451,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15484,7 +15473,7 @@
         <v>128816333</v>
       </c>
       <c r="B148" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15578,10 +15567,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128816346</v>
+        <v>128816341</v>
       </c>
       <c r="B149" t="n">
-        <v>78847</v>
+        <v>79706</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15589,21 +15578,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15616,10 +15605,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>456521</v>
+        <v>456482</v>
       </c>
       <c r="R149" t="n">
-        <v>6800343</v>
+        <v>6800573</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15679,10 +15668,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128816341</v>
+        <v>128816337</v>
       </c>
       <c r="B150" t="n">
-        <v>79679</v>
+        <v>79735</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15690,37 +15679,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>456482</v>
+        <v>456758</v>
       </c>
       <c r="R150" t="n">
-        <v>6800573</v>
+        <v>6800574</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15761,7 +15747,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15780,10 +15765,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128816337</v>
+        <v>128816360</v>
       </c>
       <c r="B151" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15791,21 +15776,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15815,10 +15800,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>456758</v>
+        <v>456583</v>
       </c>
       <c r="R151" t="n">
-        <v>6800574</v>
+        <v>6800417</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15874,103 +15859,6 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>128816360</v>
-      </c>
-      <c r="B152" t="n">
-        <v>79089</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Södra Våmsjön, Dlr</t>
-        </is>
-      </c>
-      <c r="Q152" t="n">
-        <v>456583</v>
-      </c>
-      <c r="R152" t="n">
-        <v>6800417</v>
-      </c>
-      <c r="S152" t="n">
-        <v>10</v>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AD152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT152" t="inlineStr"/>
-      <c r="AW152" t="inlineStr">
-        <is>
-          <t>Louise Tegnér</t>
-        </is>
-      </c>
-      <c r="AX152" t="inlineStr">
-        <is>
-          <t>Louise Tegnér</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128799069</v>
+        <v>128814701</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>78873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456632</v>
+        <v>456547</v>
       </c>
       <c r="R2" t="n">
-        <v>6800431</v>
+        <v>6800436</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -899,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128814701</v>
+        <v>128799069</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456547</v>
+        <v>456632</v>
       </c>
       <c r="R4" t="n">
-        <v>6800436</v>
+        <v>6800431</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,9 +957,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814728</v>
+        <v>128801339</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,21 +1436,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456616</v>
+        <v>456742</v>
       </c>
       <c r="R9" t="n">
-        <v>6800533</v>
+        <v>6800421</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,9 +1493,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,22 +1520,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128801339</v>
+        <v>128805128</v>
       </c>
       <c r="B10" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1543,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456742</v>
+        <v>456660</v>
       </c>
       <c r="R10" t="n">
-        <v>6800421</v>
+        <v>6800603</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128805128</v>
+        <v>128814728</v>
       </c>
       <c r="B11" t="n">
         <v>79116</v>
@@ -1664,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456660</v>
+        <v>456616</v>
       </c>
       <c r="R11" t="n">
-        <v>6800603</v>
+        <v>6800533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,19 +1707,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128804672</v>
+        <v>128814666</v>
       </c>
       <c r="B12" t="n">
-        <v>79735</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,34 +1747,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456733</v>
+        <v>456659</v>
       </c>
       <c r="R12" t="n">
-        <v>6800618</v>
+        <v>6800402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,19 +1812,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,22 +1829,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814681</v>
+        <v>128804672</v>
       </c>
       <c r="B13" t="n">
-        <v>78874</v>
+        <v>79735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456761</v>
+        <v>456733</v>
       </c>
       <c r="R13" t="n">
-        <v>6800515</v>
+        <v>6800618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,9 +1909,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,22 +1936,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814666</v>
+        <v>128814681</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>78874</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,42 +1959,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456659</v>
+        <v>456761</v>
       </c>
       <c r="R14" t="n">
-        <v>6800402</v>
+        <v>6800515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814715</v>
+        <v>128804638</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456589</v>
+        <v>456748</v>
       </c>
       <c r="R16" t="n">
-        <v>6800303</v>
+        <v>6800617</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,9 +2210,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,19 +2237,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128805619</v>
+        <v>128814729</v>
       </c>
       <c r="B17" t="n">
         <v>79116</v>
@@ -2274,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456600</v>
+        <v>456606</v>
       </c>
       <c r="R17" t="n">
-        <v>6800539</v>
+        <v>6800334</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,19 +2317,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,19 +2334,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128805376</v>
+        <v>128805619</v>
       </c>
       <c r="B18" t="n">
         <v>79116</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456589</v>
+        <v>456600</v>
       </c>
       <c r="R18" t="n">
-        <v>6800567</v>
+        <v>6800539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128814729</v>
+        <v>128805376</v>
       </c>
       <c r="B19" t="n">
         <v>79116</v>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456606</v>
+        <v>456589</v>
       </c>
       <c r="R19" t="n">
-        <v>6800334</v>
+        <v>6800567</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,9 +2521,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2538,22 +2548,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128804638</v>
+        <v>128814693</v>
       </c>
       <c r="B20" t="n">
-        <v>79735</v>
+        <v>78873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,21 +2571,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456748</v>
+        <v>456515</v>
       </c>
       <c r="R20" t="n">
-        <v>6800617</v>
+        <v>6800380</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,19 +2628,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2645,22 +2645,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128814693</v>
+        <v>128814715</v>
       </c>
       <c r="B21" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,21 +2668,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456515</v>
+        <v>456589</v>
       </c>
       <c r="R21" t="n">
-        <v>6800380</v>
+        <v>6800303</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128804261</v>
+        <v>128814654</v>
       </c>
       <c r="B22" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,34 +2765,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456794</v>
+        <v>456705</v>
       </c>
       <c r="R22" t="n">
-        <v>6800605</v>
+        <v>6800486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,19 +2830,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128814654</v>
+        <v>128804261</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>78874</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,42 +2870,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456705</v>
+        <v>456794</v>
       </c>
       <c r="R23" t="n">
-        <v>6800486</v>
+        <v>6800605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,9 +2927,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,22 +2954,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814673</v>
+        <v>128814616</v>
       </c>
       <c r="B24" t="n">
-        <v>78874</v>
+        <v>79735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456469</v>
+        <v>456487</v>
       </c>
       <c r="R24" t="n">
-        <v>6800542</v>
+        <v>6800546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814652</v>
+        <v>128814716</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,42 +3074,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456781</v>
+        <v>456477</v>
       </c>
       <c r="R25" t="n">
-        <v>6800644</v>
+        <v>6800324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,6 +3134,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,10 +3165,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814644</v>
+        <v>128805061</v>
       </c>
       <c r="B26" t="n">
-        <v>57713</v>
+        <v>78873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,42 +3176,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456603</v>
+        <v>456690</v>
       </c>
       <c r="R26" t="n">
-        <v>6800371</v>
+        <v>6800603</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,9 +3233,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3261,12 +3260,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3370,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814616</v>
+        <v>128814724</v>
       </c>
       <c r="B28" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,21 +3380,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456487</v>
+        <v>456520</v>
       </c>
       <c r="R28" t="n">
-        <v>6800546</v>
+        <v>6800367</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814716</v>
+        <v>128814652</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,34 +3477,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456477</v>
+        <v>456781</v>
       </c>
       <c r="R29" t="n">
-        <v>6800324</v>
+        <v>6800644</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,11 +3545,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814724</v>
+        <v>128814644</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,34 +3582,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456520</v>
+        <v>456603</v>
       </c>
       <c r="R30" t="n">
-        <v>6800367</v>
+        <v>6800371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3666,10 +3676,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128805061</v>
+        <v>128814673</v>
       </c>
       <c r="B31" t="n">
-        <v>78873</v>
+        <v>78874</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3677,21 +3687,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3701,10 +3711,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456690</v>
+        <v>456469</v>
       </c>
       <c r="R31" t="n">
-        <v>6800603</v>
+        <v>6800542</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,19 +3744,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3761,22 +3761,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814720</v>
+        <v>128814692</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456446</v>
+        <v>456354</v>
       </c>
       <c r="R32" t="n">
-        <v>6800471</v>
+        <v>6800374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814692</v>
+        <v>128814708</v>
       </c>
       <c r="B34" t="n">
         <v>78873</v>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456354</v>
+        <v>456702</v>
       </c>
       <c r="R34" t="n">
-        <v>6800374</v>
+        <v>6800512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814708</v>
+        <v>128814720</v>
       </c>
       <c r="B35" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456702</v>
+        <v>456446</v>
       </c>
       <c r="R35" t="n">
-        <v>6800512</v>
+        <v>6800471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814727</v>
+        <v>128804553</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456600</v>
+        <v>456768</v>
       </c>
       <c r="R36" t="n">
-        <v>6800519</v>
+        <v>6800626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,9 +4229,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4246,22 +4256,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128804553</v>
+        <v>128814689</v>
       </c>
       <c r="B37" t="n">
-        <v>79735</v>
+        <v>78873</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4269,21 +4279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4293,10 +4303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456768</v>
+        <v>456495</v>
       </c>
       <c r="R37" t="n">
-        <v>6800626</v>
+        <v>6800433</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,19 +4336,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4353,22 +4353,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814711</v>
+        <v>128814743</v>
       </c>
       <c r="B38" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,21 +4376,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4400,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456642</v>
+        <v>456566</v>
       </c>
       <c r="R38" t="n">
-        <v>6800358</v>
+        <v>6800498</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,6 +4436,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4462,10 +4467,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814710</v>
+        <v>128814727</v>
       </c>
       <c r="B39" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4473,21 +4478,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4497,10 +4502,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456770</v>
+        <v>456600</v>
       </c>
       <c r="R39" t="n">
-        <v>6800515</v>
+        <v>6800519</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4559,7 +4564,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128814689</v>
+        <v>128814710</v>
       </c>
       <c r="B40" t="n">
         <v>78873</v>
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456495</v>
+        <v>456770</v>
       </c>
       <c r="R40" t="n">
-        <v>6800433</v>
+        <v>6800515</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,10 +4661,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128814743</v>
+        <v>128814711</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,21 +4672,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4691,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456566</v>
+        <v>456642</v>
       </c>
       <c r="R41" t="n">
-        <v>6800498</v>
+        <v>6800358</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4727,11 +4732,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,7 +4758,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128814733</v>
+        <v>128814739</v>
       </c>
       <c r="B42" t="n">
         <v>79116</v>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456547</v>
+        <v>456351</v>
       </c>
       <c r="R42" t="n">
-        <v>6800300</v>
+        <v>6800353</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814739</v>
+        <v>128814733</v>
       </c>
       <c r="B43" t="n">
         <v>79116</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456351</v>
+        <v>456547</v>
       </c>
       <c r="R43" t="n">
-        <v>6800353</v>
+        <v>6800300</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128814730</v>
+        <v>128814742</v>
       </c>
       <c r="B48" t="n">
         <v>79116</v>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456589</v>
+        <v>456590</v>
       </c>
       <c r="R48" t="n">
-        <v>6800302</v>
+        <v>6800535</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128814742</v>
+        <v>128814730</v>
       </c>
       <c r="B49" t="n">
         <v>79116</v>
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456590</v>
+        <v>456589</v>
       </c>
       <c r="R49" t="n">
-        <v>6800535</v>
+        <v>6800302</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5786,10 +5786,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128799275</v>
+        <v>128814612</v>
       </c>
       <c r="B52" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5797,21 +5797,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456665</v>
+        <v>456539</v>
       </c>
       <c r="R52" t="n">
-        <v>6800399</v>
+        <v>6800496</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5854,24 +5854,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5886,22 +5871,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814612</v>
+        <v>128814719</v>
       </c>
       <c r="B53" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,21 +5894,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5918,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456539</v>
+        <v>456527</v>
       </c>
       <c r="R53" t="n">
-        <v>6800496</v>
+        <v>6800610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,10 +5980,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814620</v>
+        <v>128814736</v>
       </c>
       <c r="B54" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,37 +5991,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456385</v>
+        <v>456569</v>
       </c>
       <c r="R54" t="n">
-        <v>6800430</v>
+        <v>6800599</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6059,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6096,10 +6077,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814719</v>
+        <v>128814620</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6107,34 +6088,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456527</v>
+        <v>456385</v>
       </c>
       <c r="R55" t="n">
-        <v>6800610</v>
+        <v>6800430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6175,6 +6159,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6193,7 +6178,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814736</v>
+        <v>128814718</v>
       </c>
       <c r="B56" t="n">
         <v>79116</v>
@@ -6228,10 +6213,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456569</v>
+        <v>456559</v>
       </c>
       <c r="R56" t="n">
-        <v>6800599</v>
+        <v>6800586</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,10 +6275,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814718</v>
+        <v>128802364</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6301,21 +6286,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6325,10 +6310,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456559</v>
+        <v>456718</v>
       </c>
       <c r="R57" t="n">
-        <v>6800586</v>
+        <v>6800502</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6358,9 +6343,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6375,22 +6370,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128802364</v>
+        <v>128799275</v>
       </c>
       <c r="B58" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,21 +6393,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6422,10 +6417,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456718</v>
+        <v>456665</v>
       </c>
       <c r="R58" t="n">
-        <v>6800502</v>
+        <v>6800399</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6468,6 +6463,11 @@
       <c r="AB58" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128799700</v>
+        <v>128814735</v>
       </c>
       <c r="B59" t="n">
-        <v>79706</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456668</v>
+        <v>456477</v>
       </c>
       <c r="R59" t="n">
-        <v>6800363</v>
+        <v>6800413</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,19 +6562,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6589,22 +6579,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814628</v>
+        <v>128814734</v>
       </c>
       <c r="B60" t="n">
-        <v>79706</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6612,21 +6602,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6636,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456549</v>
+        <v>456472</v>
       </c>
       <c r="R60" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6688,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814735</v>
+        <v>128814628</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6699,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6723,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456477</v>
+        <v>456549</v>
       </c>
       <c r="R61" t="n">
-        <v>6800413</v>
+        <v>6800517</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128814734</v>
+        <v>128799700</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6806,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6830,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456472</v>
+        <v>456668</v>
       </c>
       <c r="R62" t="n">
-        <v>6800343</v>
+        <v>6800363</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6863,9 +6853,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,22 +6880,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128802369</v>
+        <v>128802133</v>
       </c>
       <c r="B63" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456718</v>
+        <v>456775</v>
       </c>
       <c r="R63" t="n">
-        <v>6800502</v>
+        <v>6800500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6973,6 +6973,11 @@
       <c r="AB63" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6999,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128802133</v>
+        <v>128802369</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7010,21 +7015,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7034,10 +7039,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456775</v>
+        <v>456718</v>
       </c>
       <c r="R64" t="n">
-        <v>6800500</v>
+        <v>6800502</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7080,11 +7085,6 @@
       <c r="AB64" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7208,10 +7208,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128814675</v>
+        <v>128804576</v>
       </c>
       <c r="B66" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7219,37 +7219,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456513</v>
+        <v>456761</v>
       </c>
       <c r="R66" t="n">
-        <v>6800383</v>
+        <v>6800606</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7279,37 +7281,46 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128804576</v>
+        <v>128814656</v>
       </c>
       <c r="B67" t="n">
         <v>57713</v>
@@ -7338,21 +7349,24 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456761</v>
+        <v>456658</v>
       </c>
       <c r="R67" t="n">
-        <v>6800606</v>
+        <v>6800419</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7382,19 +7396,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7409,19 +7413,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128814656</v>
+        <v>128814660</v>
       </c>
       <c r="B68" t="n">
         <v>57713</v>
@@ -7454,7 +7458,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7464,10 +7468,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456658</v>
+        <v>456747</v>
       </c>
       <c r="R68" t="n">
-        <v>6800419</v>
+        <v>6800420</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7526,10 +7530,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128814660</v>
+        <v>128814675</v>
       </c>
       <c r="B69" t="n">
-        <v>57713</v>
+        <v>78874</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7537,31 +7541,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7569,10 +7568,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456747</v>
+        <v>456513</v>
       </c>
       <c r="R69" t="n">
-        <v>6800420</v>
+        <v>6800383</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7613,6 +7612,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128799394</v>
+        <v>128814691</v>
       </c>
       <c r="B70" t="n">
-        <v>91444</v>
+        <v>78873</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456679</v>
+        <v>456385</v>
       </c>
       <c r="R70" t="n">
-        <v>6800380</v>
+        <v>6800430</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7699,19 +7699,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7726,22 +7716,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128803330</v>
+        <v>128814717</v>
       </c>
       <c r="B71" t="n">
-        <v>79706</v>
+        <v>79116</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456690</v>
+        <v>456529</v>
       </c>
       <c r="R71" t="n">
-        <v>6800454</v>
+        <v>6800501</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,19 +7796,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7833,12 +7813,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7942,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814691</v>
+        <v>128814714</v>
       </c>
       <c r="B73" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7953,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456385</v>
+        <v>456599</v>
       </c>
       <c r="R73" t="n">
-        <v>6800430</v>
+        <v>6800361</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128814714</v>
+        <v>128814697</v>
       </c>
       <c r="B74" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8050,21 +8030,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8074,10 +8054,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456599</v>
+        <v>456499</v>
       </c>
       <c r="R74" t="n">
-        <v>6800361</v>
+        <v>6800562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8136,10 +8116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128814697</v>
+        <v>128803330</v>
       </c>
       <c r="B75" t="n">
-        <v>78873</v>
+        <v>79706</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8147,21 +8127,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8171,10 +8151,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456499</v>
+        <v>456690</v>
       </c>
       <c r="R75" t="n">
-        <v>6800562</v>
+        <v>6800454</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8204,9 +8184,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8221,22 +8211,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128814717</v>
+        <v>128799394</v>
       </c>
       <c r="B76" t="n">
-        <v>79116</v>
+        <v>91444</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8244,21 +8234,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8268,10 +8258,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456529</v>
+        <v>456679</v>
       </c>
       <c r="R76" t="n">
-        <v>6800501</v>
+        <v>6800380</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,9 +8291,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,60 +8318,65 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128814677</v>
+        <v>128800812</v>
       </c>
       <c r="B77" t="n">
-        <v>78874</v>
+        <v>58086</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456747</v>
+        <v>456691</v>
       </c>
       <c r="R77" t="n">
-        <v>6800569</v>
+        <v>6800368</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8398,9 +8403,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8415,22 +8430,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128801262</v>
+        <v>128800436</v>
       </c>
       <c r="B78" t="n">
-        <v>78874</v>
+        <v>79735</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8438,21 +8453,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8462,10 +8477,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456703</v>
+        <v>456671</v>
       </c>
       <c r="R78" t="n">
-        <v>6800429</v>
+        <v>6800350</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8534,53 +8549,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128800812</v>
+        <v>128814709</v>
       </c>
       <c r="B79" t="n">
-        <v>58086</v>
+        <v>78873</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456691</v>
+        <v>456706</v>
       </c>
       <c r="R79" t="n">
-        <v>6800368</v>
+        <v>6800520</v>
       </c>
       <c r="S79" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8607,19 +8617,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8634,12 +8634,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8743,10 +8743,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814695</v>
+        <v>128814722</v>
       </c>
       <c r="B81" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8754,21 +8754,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456547</v>
+        <v>456349</v>
       </c>
       <c r="R81" t="n">
-        <v>6800403</v>
+        <v>6800436</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,7 +8840,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814709</v>
+        <v>128814695</v>
       </c>
       <c r="B82" t="n">
         <v>78873</v>
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456706</v>
+        <v>456547</v>
       </c>
       <c r="R82" t="n">
-        <v>6800520</v>
+        <v>6800403</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9034,10 +9034,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128800436</v>
+        <v>128814677</v>
       </c>
       <c r="B84" t="n">
-        <v>79735</v>
+        <v>78874</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9045,21 +9045,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9069,10 +9069,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456671</v>
+        <v>456747</v>
       </c>
       <c r="R84" t="n">
-        <v>6800350</v>
+        <v>6800569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9102,19 +9102,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9129,22 +9119,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128814722</v>
+        <v>128801262</v>
       </c>
       <c r="B85" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9152,21 +9142,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9176,10 +9166,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456349</v>
+        <v>456703</v>
       </c>
       <c r="R85" t="n">
-        <v>6800436</v>
+        <v>6800429</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9209,9 +9199,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9226,12 +9226,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814723</v>
+        <v>128814726</v>
       </c>
       <c r="B88" t="n">
         <v>79116</v>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456351</v>
+        <v>456524</v>
       </c>
       <c r="R88" t="n">
-        <v>6800371</v>
+        <v>6800431</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,7 +9529,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814726</v>
+        <v>128814723</v>
       </c>
       <c r="B89" t="n">
         <v>79116</v>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456524</v>
+        <v>456351</v>
       </c>
       <c r="R89" t="n">
-        <v>6800431</v>
+        <v>6800371</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128799696</v>
+        <v>128814637</v>
       </c>
       <c r="B90" t="n">
-        <v>78874</v>
+        <v>57716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,34 +9637,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456668</v>
+        <v>456352</v>
       </c>
       <c r="R90" t="n">
-        <v>6800363</v>
+        <v>6800325</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9694,19 +9702,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9721,22 +9719,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814637</v>
+        <v>128814705</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>78873</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9744,42 +9742,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456352</v>
+        <v>456749</v>
       </c>
       <c r="R91" t="n">
-        <v>6800325</v>
+        <v>6800566</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9838,10 +9828,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814694</v>
+        <v>128814622</v>
       </c>
       <c r="B92" t="n">
-        <v>78873</v>
+        <v>79735</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9849,21 +9839,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9873,10 +9863,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456594</v>
+        <v>456546</v>
       </c>
       <c r="R92" t="n">
-        <v>6800423</v>
+        <v>6800434</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9935,10 +9925,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814690</v>
+        <v>128814732</v>
       </c>
       <c r="B93" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9946,21 +9936,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9970,10 +9960,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456465</v>
+        <v>456571</v>
       </c>
       <c r="R93" t="n">
-        <v>6800546</v>
+        <v>6800296</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10032,10 +10022,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814732</v>
+        <v>128814690</v>
       </c>
       <c r="B94" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10043,21 +10033,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10067,10 +10057,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456571</v>
+        <v>456465</v>
       </c>
       <c r="R94" t="n">
-        <v>6800296</v>
+        <v>6800546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10226,7 +10216,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814705</v>
+        <v>128814694</v>
       </c>
       <c r="B96" t="n">
         <v>78873</v>
@@ -10261,10 +10251,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456749</v>
+        <v>456594</v>
       </c>
       <c r="R96" t="n">
-        <v>6800566</v>
+        <v>6800423</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10323,7 +10313,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814622</v>
+        <v>128804256</v>
       </c>
       <c r="B97" t="n">
         <v>79735</v>
@@ -10358,10 +10348,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456546</v>
+        <v>456794</v>
       </c>
       <c r="R97" t="n">
-        <v>6800434</v>
+        <v>6800605</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10391,9 +10381,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10408,22 +10408,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128804256</v>
+        <v>128814664</v>
       </c>
       <c r="B98" t="n">
-        <v>79735</v>
+        <v>57713</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10431,34 +10431,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456794</v>
+        <v>456676</v>
       </c>
       <c r="R98" t="n">
-        <v>6800605</v>
+        <v>6800380</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10488,19 +10496,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10515,22 +10513,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128814664</v>
+        <v>128799696</v>
       </c>
       <c r="B99" t="n">
-        <v>57713</v>
+        <v>78874</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10538,42 +10536,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456676</v>
+        <v>456668</v>
       </c>
       <c r="R99" t="n">
-        <v>6800380</v>
+        <v>6800363</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10603,9 +10593,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10620,44 +10620,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128814624</v>
+        <v>128814713</v>
       </c>
       <c r="B100" t="n">
-        <v>79735</v>
+        <v>90876</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456688</v>
+        <v>456692</v>
       </c>
       <c r="R100" t="n">
-        <v>6800585</v>
+        <v>6800391</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805203</v>
+        <v>128805054</v>
       </c>
       <c r="B101" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456650</v>
+        <v>456690</v>
       </c>
       <c r="R101" t="n">
-        <v>6800594</v>
+        <v>6800603</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10840,7 +10840,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814737</v>
+        <v>128804050</v>
       </c>
       <c r="B102" t="n">
         <v>79116</v>
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456555</v>
+        <v>456753</v>
       </c>
       <c r="R102" t="n">
-        <v>6800627</v>
+        <v>6800562</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10908,9 +10908,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10925,22 +10940,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814698</v>
+        <v>128805203</v>
       </c>
       <c r="B103" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10948,21 +10963,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10972,10 +10987,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456491</v>
+        <v>456650</v>
       </c>
       <c r="R103" t="n">
-        <v>6800537</v>
+        <v>6800594</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11005,9 +11020,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11022,22 +11047,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128804050</v>
+        <v>128814698</v>
       </c>
       <c r="B104" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11045,21 +11070,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11069,10 +11094,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456753</v>
+        <v>456491</v>
       </c>
       <c r="R104" t="n">
-        <v>6800562</v>
+        <v>6800537</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11102,24 +11127,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11134,22 +11144,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814632</v>
+        <v>128814737</v>
       </c>
       <c r="B105" t="n">
-        <v>79706</v>
+        <v>79116</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11157,21 +11167,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11181,10 +11191,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456382</v>
+        <v>456555</v>
       </c>
       <c r="R105" t="n">
-        <v>6800427</v>
+        <v>6800627</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11243,32 +11253,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814713</v>
+        <v>128814624</v>
       </c>
       <c r="B106" t="n">
-        <v>90876</v>
+        <v>79735</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11281,10 +11291,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456692</v>
+        <v>456688</v>
       </c>
       <c r="R106" t="n">
-        <v>6800391</v>
+        <v>6800585</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11344,10 +11354,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128805054</v>
+        <v>128814725</v>
       </c>
       <c r="B107" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11355,21 +11365,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11379,10 +11389,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456690</v>
+        <v>456598</v>
       </c>
       <c r="R107" t="n">
-        <v>6800603</v>
+        <v>6800407</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11412,19 +11422,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11439,19 +11444,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128804554</v>
+        <v>128814683</v>
       </c>
       <c r="B108" t="n">
         <v>78874</v>
@@ -11480,16 +11485,19 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456768</v>
+        <v>456644</v>
       </c>
       <c r="R108" t="n">
-        <v>6800626</v>
+        <v>6800358</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11519,49 +11527,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128814725</v>
+        <v>128804554</v>
       </c>
       <c r="B109" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11569,21 +11568,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11593,10 +11592,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456598</v>
+        <v>456768</v>
       </c>
       <c r="R109" t="n">
-        <v>6800407</v>
+        <v>6800626</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11626,14 +11625,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11648,22 +11652,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814683</v>
+        <v>128814632</v>
       </c>
       <c r="B110" t="n">
-        <v>78874</v>
+        <v>79706</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11671,37 +11675,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456644</v>
+        <v>456382</v>
       </c>
       <c r="R110" t="n">
-        <v>6800358</v>
+        <v>6800427</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11742,7 +11743,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128803369</v>
+        <v>128814646</v>
       </c>
       <c r="B111" t="n">
-        <v>79735</v>
+        <v>57713</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,34 +11772,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456688</v>
+        <v>456519</v>
       </c>
       <c r="R111" t="n">
-        <v>6800474</v>
+        <v>6800414</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11829,19 +11837,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11856,22 +11854,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814687</v>
+        <v>128814634</v>
       </c>
       <c r="B112" t="n">
-        <v>78873</v>
+        <v>57716</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11879,34 +11877,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456556</v>
+        <v>456405</v>
       </c>
       <c r="R112" t="n">
-        <v>6800320</v>
+        <v>6800457</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12072,10 +12078,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814614</v>
+        <v>128814731</v>
       </c>
       <c r="B114" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12083,21 +12089,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12107,10 +12113,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456522</v>
+        <v>456580</v>
       </c>
       <c r="R114" t="n">
-        <v>6800319</v>
+        <v>6800292</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12169,10 +12175,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814731</v>
+        <v>128814696</v>
       </c>
       <c r="B115" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12180,21 +12186,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12204,10 +12210,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456580</v>
+        <v>456559</v>
       </c>
       <c r="R115" t="n">
-        <v>6800292</v>
+        <v>6800576</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12266,10 +12272,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814696</v>
+        <v>128803369</v>
       </c>
       <c r="B116" t="n">
-        <v>78873</v>
+        <v>79735</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12277,21 +12283,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12301,10 +12307,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456559</v>
+        <v>456688</v>
       </c>
       <c r="R116" t="n">
-        <v>6800576</v>
+        <v>6800474</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12334,9 +12340,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12351,22 +12367,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814634</v>
+        <v>128814614</v>
       </c>
       <c r="B117" t="n">
-        <v>57716</v>
+        <v>79735</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12374,42 +12390,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456405</v>
+        <v>456522</v>
       </c>
       <c r="R117" t="n">
-        <v>6800457</v>
+        <v>6800319</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12468,10 +12476,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814679</v>
+        <v>128814687</v>
       </c>
       <c r="B118" t="n">
-        <v>78874</v>
+        <v>78873</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12479,21 +12487,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12503,10 +12511,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456753</v>
+        <v>456556</v>
       </c>
       <c r="R118" t="n">
-        <v>6800533</v>
+        <v>6800320</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12565,10 +12573,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814646</v>
+        <v>128814679</v>
       </c>
       <c r="B119" t="n">
-        <v>57713</v>
+        <v>78874</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12576,42 +12584,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456519</v>
+        <v>456753</v>
       </c>
       <c r="R119" t="n">
-        <v>6800414</v>
+        <v>6800533</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12670,10 +12670,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128814706</v>
+        <v>128805585</v>
       </c>
       <c r="B120" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12681,21 +12681,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12705,10 +12705,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>456703</v>
+        <v>456604</v>
       </c>
       <c r="R120" t="n">
-        <v>6800495</v>
+        <v>6800527</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12738,9 +12738,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12755,22 +12765,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128804496</v>
+        <v>128814706</v>
       </c>
       <c r="B121" t="n">
-        <v>79735</v>
+        <v>78873</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12778,21 +12788,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12802,10 +12812,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>456753</v>
+        <v>456703</v>
       </c>
       <c r="R121" t="n">
-        <v>6800630</v>
+        <v>6800495</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12835,19 +12845,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12862,22 +12862,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128814700</v>
+        <v>128804496</v>
       </c>
       <c r="B122" t="n">
-        <v>78873</v>
+        <v>79735</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12885,21 +12885,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12909,10 +12909,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>456507</v>
+        <v>456753</v>
       </c>
       <c r="R122" t="n">
-        <v>6800413</v>
+        <v>6800630</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12942,9 +12942,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12959,22 +12969,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128805585</v>
+        <v>128814700</v>
       </c>
       <c r="B123" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12982,21 +12992,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13006,10 +13016,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>456604</v>
+        <v>456507</v>
       </c>
       <c r="R123" t="n">
-        <v>6800527</v>
+        <v>6800413</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13039,19 +13049,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13066,12 +13066,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816343</v>
+        <v>128816338</v>
       </c>
       <c r="B127" t="n">
-        <v>57716</v>
+        <v>79706</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,31 +13392,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13424,10 +13419,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456341</v>
+        <v>456478</v>
       </c>
       <c r="R127" t="n">
-        <v>6800306</v>
+        <v>6800591</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13468,6 +13463,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13583,10 +13579,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816338</v>
+        <v>128816343</v>
       </c>
       <c r="B129" t="n">
-        <v>79706</v>
+        <v>57716</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13594,26 +13590,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13621,10 +13622,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456478</v>
+        <v>456341</v>
       </c>
       <c r="R129" t="n">
-        <v>6800591</v>
+        <v>6800306</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13665,7 +13666,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13684,7 +13684,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128816347</v>
+        <v>128816349</v>
       </c>
       <c r="B130" t="n">
         <v>78874</v>
@@ -13713,19 +13713,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>456473</v>
+        <v>456688</v>
       </c>
       <c r="R130" t="n">
-        <v>6800370</v>
+        <v>6800401</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13766,7 +13763,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13785,7 +13781,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128816349</v>
+        <v>128816347</v>
       </c>
       <c r="B131" t="n">
         <v>78874</v>
@@ -13814,16 +13810,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>456688</v>
+        <v>456473</v>
       </c>
       <c r="R131" t="n">
-        <v>6800401</v>
+        <v>6800370</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13864,6 +13863,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14476,10 +14476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128816348</v>
+        <v>128816352</v>
       </c>
       <c r="B138" t="n">
-        <v>78874</v>
+        <v>78873</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14487,34 +14487,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>456703</v>
+        <v>456483</v>
       </c>
       <c r="R138" t="n">
-        <v>6800475</v>
+        <v>6800432</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14555,6 +14558,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14573,10 +14577,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128816352</v>
+        <v>128816348</v>
       </c>
       <c r="B139" t="n">
-        <v>78873</v>
+        <v>78874</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14584,37 +14588,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456483</v>
+        <v>456703</v>
       </c>
       <c r="R139" t="n">
-        <v>6800432</v>
+        <v>6800475</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14655,7 +14656,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15066,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816359</v>
+        <v>128816332</v>
       </c>
       <c r="B144" t="n">
-        <v>79116</v>
+        <v>79148</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15077,34 +15077,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456335</v>
+        <v>456355</v>
       </c>
       <c r="R144" t="n">
-        <v>6800427</v>
+        <v>6800454</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15145,6 +15148,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15163,10 +15167,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816345</v>
+        <v>128816359</v>
       </c>
       <c r="B145" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15174,42 +15178,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456606</v>
+        <v>456335</v>
       </c>
       <c r="R145" t="n">
-        <v>6800517</v>
+        <v>6800427</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15268,10 +15264,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816332</v>
+        <v>128816345</v>
       </c>
       <c r="B146" t="n">
-        <v>79148</v>
+        <v>57713</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15279,26 +15275,31 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15306,10 +15307,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456355</v>
+        <v>456606</v>
       </c>
       <c r="R146" t="n">
-        <v>6800454</v>
+        <v>6800517</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15350,7 +15351,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15369,10 +15369,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128816346</v>
+        <v>128816333</v>
       </c>
       <c r="B147" t="n">
-        <v>78874</v>
+        <v>79148</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15380,37 +15380,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>456521</v>
+        <v>456756</v>
       </c>
       <c r="R147" t="n">
-        <v>6800343</v>
+        <v>6800522</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15451,7 +15448,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15470,10 +15466,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128816333</v>
+        <v>128816346</v>
       </c>
       <c r="B148" t="n">
-        <v>79148</v>
+        <v>78874</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15481,34 +15477,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>456756</v>
+        <v>456521</v>
       </c>
       <c r="R148" t="n">
-        <v>6800522</v>
+        <v>6800343</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15549,6 +15548,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128814701</v>
       </c>
       <c r="B2" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128800923</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1101,53 +1101,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128814658</v>
+        <v>128803425</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456645</v>
+        <v>456681</v>
       </c>
       <c r="R6" t="n">
-        <v>6800444</v>
+        <v>6800496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,9 +1169,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,44 +1196,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128803425</v>
+        <v>128805128</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456681</v>
+        <v>456660</v>
       </c>
       <c r="R7" t="n">
-        <v>6800496</v>
+        <v>6800603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128803579</v>
+        <v>128814728</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456698</v>
+        <v>456616</v>
       </c>
       <c r="R8" t="n">
-        <v>6800503</v>
+        <v>6800533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,24 +1383,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,22 +1400,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128801339</v>
+        <v>128803579</v>
       </c>
       <c r="B9" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456742</v>
+        <v>456698</v>
       </c>
       <c r="R9" t="n">
-        <v>6800421</v>
+        <v>6800503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,6 +1493,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128805128</v>
+        <v>128801339</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,21 +1535,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456660</v>
+        <v>456742</v>
       </c>
       <c r="R10" t="n">
-        <v>6800603</v>
+        <v>6800421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128814728</v>
+        <v>128814658</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1642,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456616</v>
+        <v>456645</v>
       </c>
       <c r="R11" t="n">
-        <v>6800533</v>
+        <v>6800444</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814666</v>
+        <v>128804672</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,42 +1747,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456659</v>
+        <v>456733</v>
       </c>
       <c r="R12" t="n">
-        <v>6800402</v>
+        <v>6800618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,9 +1804,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,22 +1831,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128804672</v>
+        <v>128814666</v>
       </c>
       <c r="B13" t="n">
-        <v>79735</v>
+        <v>57713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,34 +1854,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456733</v>
+        <v>456659</v>
       </c>
       <c r="R13" t="n">
-        <v>6800618</v>
+        <v>6800402</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,19 +1919,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,12 +1936,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1951,7 +1951,7 @@
         <v>128814681</v>
       </c>
       <c r="B14" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128814744</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128804638</v>
+        <v>128814729</v>
       </c>
       <c r="B16" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456748</v>
+        <v>456606</v>
       </c>
       <c r="R16" t="n">
-        <v>6800617</v>
+        <v>6800334</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,19 +2210,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,22 +2227,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814729</v>
+        <v>128814715</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456606</v>
+        <v>456589</v>
       </c>
       <c r="R17" t="n">
-        <v>6800334</v>
+        <v>6800303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128805619</v>
+        <v>128804638</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,21 +2347,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456600</v>
+        <v>456748</v>
       </c>
       <c r="R18" t="n">
-        <v>6800539</v>
+        <v>6800617</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805376</v>
+        <v>128805619</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456589</v>
+        <v>456600</v>
       </c>
       <c r="R19" t="n">
-        <v>6800567</v>
+        <v>6800539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128814693</v>
+        <v>128805376</v>
       </c>
       <c r="B20" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,21 +2561,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2595,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456515</v>
+        <v>456589</v>
       </c>
       <c r="R20" t="n">
-        <v>6800380</v>
+        <v>6800567</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,9 +2618,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2645,22 +2645,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128814715</v>
+        <v>128814654</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,34 +2668,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456589</v>
+        <v>456705</v>
       </c>
       <c r="R21" t="n">
-        <v>6800303</v>
+        <v>6800486</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814654</v>
+        <v>128814693</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,42 +2773,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456705</v>
+        <v>456515</v>
       </c>
       <c r="R22" t="n">
-        <v>6800486</v>
+        <v>6800380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,7 +2862,7 @@
         <v>128804261</v>
       </c>
       <c r="B23" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814616</v>
+        <v>128814652</v>
       </c>
       <c r="B24" t="n">
-        <v>79735</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,34 +2977,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456487</v>
+        <v>456781</v>
       </c>
       <c r="R24" t="n">
-        <v>6800546</v>
+        <v>6800644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814716</v>
+        <v>128814644</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,34 +3082,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456477</v>
+        <v>456603</v>
       </c>
       <c r="R25" t="n">
-        <v>6800324</v>
+        <v>6800371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,11 +3150,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3165,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128805061</v>
+        <v>128814716</v>
       </c>
       <c r="B26" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3176,21 +3187,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3200,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456690</v>
+        <v>456477</v>
       </c>
       <c r="R26" t="n">
-        <v>6800603</v>
+        <v>6800324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,19 +3244,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3260,22 +3266,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814703</v>
+        <v>128814616</v>
       </c>
       <c r="B27" t="n">
-        <v>78873</v>
+        <v>79739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456766</v>
+        <v>456487</v>
       </c>
       <c r="R27" t="n">
-        <v>6800611</v>
+        <v>6800546</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3369,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814724</v>
+        <v>128805061</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456520</v>
+        <v>456690</v>
       </c>
       <c r="R28" t="n">
-        <v>6800367</v>
+        <v>6800603</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,9 +3443,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3454,22 +3470,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814652</v>
+        <v>128814703</v>
       </c>
       <c r="B29" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,42 +3493,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456781</v>
+        <v>456766</v>
       </c>
       <c r="R29" t="n">
-        <v>6800644</v>
+        <v>6800611</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814644</v>
+        <v>128814724</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,42 +3590,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456603</v>
+        <v>456520</v>
       </c>
       <c r="R30" t="n">
-        <v>6800371</v>
+        <v>6800367</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
         <v>128814673</v>
       </c>
       <c r="B31" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814692</v>
+        <v>128814720</v>
       </c>
       <c r="B32" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456354</v>
+        <v>456446</v>
       </c>
       <c r="R32" t="n">
-        <v>6800374</v>
+        <v>6800471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814626</v>
+        <v>128814692</v>
       </c>
       <c r="B33" t="n">
-        <v>79735</v>
+        <v>78877</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456763</v>
+        <v>456354</v>
       </c>
       <c r="R33" t="n">
-        <v>6800617</v>
+        <v>6800374</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814708</v>
+        <v>128814626</v>
       </c>
       <c r="B34" t="n">
-        <v>78873</v>
+        <v>79739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456702</v>
+        <v>456763</v>
       </c>
       <c r="R34" t="n">
-        <v>6800512</v>
+        <v>6800617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814720</v>
+        <v>128814708</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456446</v>
+        <v>456702</v>
       </c>
       <c r="R35" t="n">
-        <v>6800471</v>
+        <v>6800512</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128804553</v>
+        <v>128814743</v>
       </c>
       <c r="B36" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456768</v>
+        <v>456566</v>
       </c>
       <c r="R36" t="n">
-        <v>6800626</v>
+        <v>6800498</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,19 +4229,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,22 +4251,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814689</v>
+        <v>128804553</v>
       </c>
       <c r="B37" t="n">
-        <v>78873</v>
+        <v>79739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4279,21 +4274,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4303,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456495</v>
+        <v>456768</v>
       </c>
       <c r="R37" t="n">
-        <v>6800433</v>
+        <v>6800626</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,9 +4331,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4353,22 +4358,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814743</v>
+        <v>128814689</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,21 +4381,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4400,10 +4405,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456566</v>
+        <v>456495</v>
       </c>
       <c r="R38" t="n">
-        <v>6800498</v>
+        <v>6800433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,11 +4441,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4470,7 +4470,7 @@
         <v>128814727</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>128814710</v>
       </c>
       <c r="B40" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>128814711</v>
       </c>
       <c r="B41" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128814739</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814733</v>
+        <v>128805352</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456547</v>
+        <v>456605</v>
       </c>
       <c r="R43" t="n">
-        <v>6800300</v>
+        <v>6800580</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4923,9 +4923,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4940,22 +4950,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128805352</v>
+        <v>128814733</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4987,10 +4997,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456605</v>
+        <v>456547</v>
       </c>
       <c r="R44" t="n">
-        <v>6800580</v>
+        <v>6800300</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5020,19 +5030,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5047,12 +5047,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5062,7 +5062,7 @@
         <v>128805036</v>
       </c>
       <c r="B45" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B46" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R46" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B47" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R47" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5383,7 +5383,7 @@
         <v>128814742</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>128814730</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>128805326</v>
       </c>
       <c r="B50" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128814648</v>
+        <v>128799275</v>
       </c>
       <c r="B51" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,42 +5692,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456618</v>
+        <v>456665</v>
       </c>
       <c r="R51" t="n">
-        <v>6800564</v>
+        <v>6800399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5757,9 +5749,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5774,22 +5781,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814612</v>
+        <v>128814718</v>
       </c>
       <c r="B52" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5797,21 +5804,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5821,10 +5828,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456539</v>
+        <v>456559</v>
       </c>
       <c r="R52" t="n">
-        <v>6800496</v>
+        <v>6800586</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,10 +5890,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814719</v>
+        <v>128814612</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5894,21 +5901,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5918,10 +5925,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456527</v>
+        <v>456539</v>
       </c>
       <c r="R53" t="n">
-        <v>6800610</v>
+        <v>6800496</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5980,10 +5987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814736</v>
+        <v>128814719</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6015,10 +6022,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456569</v>
+        <v>456527</v>
       </c>
       <c r="R54" t="n">
-        <v>6800599</v>
+        <v>6800610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,10 +6084,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814620</v>
+        <v>128814736</v>
       </c>
       <c r="B55" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6088,37 +6095,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456385</v>
+        <v>456569</v>
       </c>
       <c r="R55" t="n">
-        <v>6800430</v>
+        <v>6800599</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,7 +6163,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6178,10 +6181,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814718</v>
+        <v>128814620</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6189,34 +6192,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456559</v>
+        <v>456385</v>
       </c>
       <c r="R56" t="n">
-        <v>6800586</v>
+        <v>6800430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6257,6 +6263,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6275,10 +6282,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128802364</v>
+        <v>128814648</v>
       </c>
       <c r="B57" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6286,34 +6293,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456718</v>
+        <v>456618</v>
       </c>
       <c r="R57" t="n">
-        <v>6800502</v>
+        <v>6800564</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6343,19 +6358,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6370,22 +6375,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128799275</v>
+        <v>128802364</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,21 +6398,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6417,10 +6422,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456665</v>
+        <v>456718</v>
       </c>
       <c r="R58" t="n">
-        <v>6800399</v>
+        <v>6800502</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6463,11 +6468,6 @@
       <c r="AB58" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128814735</v>
+        <v>128799700</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456477</v>
+        <v>456668</v>
       </c>
       <c r="R59" t="n">
-        <v>6800413</v>
+        <v>6800363</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,9 +6562,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6579,22 +6589,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814734</v>
+        <v>128814735</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6626,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456472</v>
+        <v>456477</v>
       </c>
       <c r="R60" t="n">
-        <v>6800343</v>
+        <v>6800413</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6688,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814628</v>
+        <v>128814734</v>
       </c>
       <c r="B61" t="n">
-        <v>79706</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6699,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6723,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456549</v>
+        <v>456472</v>
       </c>
       <c r="R61" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6785,10 +6795,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128799700</v>
+        <v>128814628</v>
       </c>
       <c r="B62" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,10 +6830,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456668</v>
+        <v>456549</v>
       </c>
       <c r="R62" t="n">
-        <v>6800363</v>
+        <v>6800517</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6853,19 +6863,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,12 +6880,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6895,7 +6895,7 @@
         <v>128802133</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>128802369</v>
       </c>
       <c r="B64" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>128814721</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>128814675</v>
       </c>
       <c r="B69" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128814691</v>
+        <v>128799394</v>
       </c>
       <c r="B70" t="n">
-        <v>78873</v>
+        <v>91449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456385</v>
+        <v>456679</v>
       </c>
       <c r="R70" t="n">
-        <v>6800430</v>
+        <v>6800380</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7699,9 +7699,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,12 +7726,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7731,7 +7741,7 @@
         <v>128814717</v>
       </c>
       <c r="B71" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7825,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128814707</v>
+        <v>128814691</v>
       </c>
       <c r="B72" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7860,10 +7870,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>456665</v>
+        <v>456385</v>
       </c>
       <c r="R72" t="n">
-        <v>6800450</v>
+        <v>6800430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,10 +7932,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814714</v>
+        <v>128814707</v>
       </c>
       <c r="B73" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7943,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7967,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456599</v>
+        <v>456665</v>
       </c>
       <c r="R73" t="n">
-        <v>6800361</v>
+        <v>6800450</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8029,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128814697</v>
+        <v>128814714</v>
       </c>
       <c r="B74" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,21 +8040,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8054,10 +8064,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456499</v>
+        <v>456599</v>
       </c>
       <c r="R74" t="n">
-        <v>6800562</v>
+        <v>6800361</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,10 +8126,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128803330</v>
+        <v>128814697</v>
       </c>
       <c r="B75" t="n">
-        <v>79706</v>
+        <v>78877</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,21 +8137,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8151,10 +8161,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456690</v>
+        <v>456499</v>
       </c>
       <c r="R75" t="n">
-        <v>6800454</v>
+        <v>6800562</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,19 +8194,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8211,22 +8211,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128799394</v>
+        <v>128803330</v>
       </c>
       <c r="B76" t="n">
-        <v>91444</v>
+        <v>79710</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8234,21 +8234,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>112</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456679</v>
+        <v>456690</v>
       </c>
       <c r="R76" t="n">
-        <v>6800380</v>
+        <v>6800454</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8330,53 +8330,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128800812</v>
+        <v>128814722</v>
       </c>
       <c r="B77" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456691</v>
+        <v>456349</v>
       </c>
       <c r="R77" t="n">
-        <v>6800368</v>
+        <v>6800436</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8403,19 +8398,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8430,12 +8415,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8445,7 +8430,7 @@
         <v>128800436</v>
       </c>
       <c r="B78" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8552,7 +8537,7 @@
         <v>128814709</v>
       </c>
       <c r="B79" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8649,7 +8634,7 @@
         <v>128814702</v>
       </c>
       <c r="B80" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8743,10 +8728,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814722</v>
+        <v>128814695</v>
       </c>
       <c r="B81" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8754,21 +8739,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8778,10 +8763,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456349</v>
+        <v>456547</v>
       </c>
       <c r="R81" t="n">
-        <v>6800436</v>
+        <v>6800403</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814695</v>
+        <v>128814618</v>
       </c>
       <c r="B82" t="n">
-        <v>78873</v>
+        <v>79739</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8851,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8875,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456547</v>
+        <v>456450</v>
       </c>
       <c r="R82" t="n">
-        <v>6800403</v>
+        <v>6800571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8937,48 +8922,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128814618</v>
+        <v>128800812</v>
       </c>
       <c r="B83" t="n">
-        <v>79735</v>
+        <v>58086</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456450</v>
+        <v>456691</v>
       </c>
       <c r="R83" t="n">
-        <v>6800571</v>
+        <v>6800368</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9005,9 +8995,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9022,12 +9022,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9037,7 +9037,7 @@
         <v>128814677</v>
       </c>
       <c r="B84" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>128801262</v>
       </c>
       <c r="B85" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814630</v>
+        <v>128814741</v>
       </c>
       <c r="B86" t="n">
-        <v>79706</v>
+        <v>79120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456496</v>
+        <v>456637</v>
       </c>
       <c r="R86" t="n">
-        <v>6800554</v>
+        <v>6800536</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814741</v>
+        <v>128814723</v>
       </c>
       <c r="B87" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456637</v>
+        <v>456351</v>
       </c>
       <c r="R87" t="n">
-        <v>6800536</v>
+        <v>6800371</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9435,7 +9435,7 @@
         <v>128814726</v>
       </c>
       <c r="B88" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814723</v>
+        <v>128814630</v>
       </c>
       <c r="B89" t="n">
-        <v>79116</v>
+        <v>79710</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456351</v>
+        <v>456496</v>
       </c>
       <c r="R89" t="n">
-        <v>6800371</v>
+        <v>6800554</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128814637</v>
+        <v>128814732</v>
       </c>
       <c r="B90" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,42 +9637,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456352</v>
+        <v>456571</v>
       </c>
       <c r="R90" t="n">
-        <v>6800325</v>
+        <v>6800296</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9734,7 +9726,7 @@
         <v>128814705</v>
       </c>
       <c r="B91" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9831,7 +9823,7 @@
         <v>128814622</v>
       </c>
       <c r="B92" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9925,10 +9917,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814732</v>
+        <v>128814690</v>
       </c>
       <c r="B93" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9936,21 +9928,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9960,10 +9952,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456571</v>
+        <v>456465</v>
       </c>
       <c r="R93" t="n">
-        <v>6800296</v>
+        <v>6800546</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10022,10 +10014,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814690</v>
+        <v>128814699</v>
       </c>
       <c r="B94" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10057,10 +10049,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456465</v>
+        <v>456496</v>
       </c>
       <c r="R94" t="n">
-        <v>6800546</v>
+        <v>6800549</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10119,10 +10111,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814699</v>
+        <v>128814694</v>
       </c>
       <c r="B95" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10154,10 +10146,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456496</v>
+        <v>456594</v>
       </c>
       <c r="R95" t="n">
-        <v>6800549</v>
+        <v>6800423</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10216,10 +10208,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814694</v>
+        <v>128804256</v>
       </c>
       <c r="B96" t="n">
-        <v>78873</v>
+        <v>79739</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10227,21 +10219,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10251,10 +10243,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456594</v>
+        <v>456794</v>
       </c>
       <c r="R96" t="n">
-        <v>6800423</v>
+        <v>6800605</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10284,9 +10276,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10301,22 +10303,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128804256</v>
+        <v>128814664</v>
       </c>
       <c r="B97" t="n">
-        <v>79735</v>
+        <v>57713</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10324,34 +10326,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456794</v>
+        <v>456676</v>
       </c>
       <c r="R97" t="n">
-        <v>6800605</v>
+        <v>6800380</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10381,19 +10391,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10408,22 +10408,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128814664</v>
+        <v>128799696</v>
       </c>
       <c r="B98" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10431,42 +10431,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456676</v>
+        <v>456668</v>
       </c>
       <c r="R98" t="n">
-        <v>6800380</v>
+        <v>6800363</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10496,9 +10488,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10513,22 +10515,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128799696</v>
+        <v>128814637</v>
       </c>
       <c r="B99" t="n">
-        <v>78874</v>
+        <v>57716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10536,34 +10538,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456668</v>
+        <v>456352</v>
       </c>
       <c r="R99" t="n">
-        <v>6800363</v>
+        <v>6800325</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10593,19 +10603,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10620,60 +10620,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128814713</v>
+        <v>128805054</v>
       </c>
       <c r="B100" t="n">
-        <v>90876</v>
+        <v>79739</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456692</v>
+        <v>456690</v>
       </c>
       <c r="R100" t="n">
-        <v>6800391</v>
+        <v>6800603</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10703,40 +10700,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805054</v>
+        <v>128814698</v>
       </c>
       <c r="B101" t="n">
-        <v>79735</v>
+        <v>78877</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10744,21 +10750,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10768,10 +10774,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456690</v>
+        <v>456491</v>
       </c>
       <c r="R101" t="n">
-        <v>6800603</v>
+        <v>6800537</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10801,19 +10807,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10828,22 +10824,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128804050</v>
+        <v>128814624</v>
       </c>
       <c r="B102" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10851,34 +10847,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456753</v>
+        <v>456688</v>
       </c>
       <c r="R102" t="n">
-        <v>6800562</v>
+        <v>6800585</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10908,54 +10907,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805203</v>
+        <v>128804050</v>
       </c>
       <c r="B103" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10987,10 +10972,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456650</v>
+        <v>456753</v>
       </c>
       <c r="R103" t="n">
-        <v>6800594</v>
+        <v>6800562</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11033,6 +11018,11 @@
       <c r="AB103" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11059,10 +11049,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128814698</v>
+        <v>128805203</v>
       </c>
       <c r="B104" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11070,21 +11060,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11094,10 +11084,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456491</v>
+        <v>456650</v>
       </c>
       <c r="R104" t="n">
-        <v>6800537</v>
+        <v>6800594</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11127,9 +11117,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11144,12 +11144,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11159,7 +11159,7 @@
         <v>128814737</v>
       </c>
       <c r="B105" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814624</v>
+        <v>128814725</v>
       </c>
       <c r="B106" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11264,37 +11264,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456688</v>
+        <v>456598</v>
       </c>
       <c r="R106" t="n">
-        <v>6800585</v>
+        <v>6800407</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11329,13 +11326,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11354,45 +11355,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814725</v>
+        <v>128814713</v>
       </c>
       <c r="B107" t="n">
-        <v>79116</v>
+        <v>90881</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456598</v>
+        <v>456692</v>
       </c>
       <c r="R107" t="n">
-        <v>6800407</v>
+        <v>6800391</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11427,17 +11431,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128814683</v>
+        <v>128814632</v>
       </c>
       <c r="B108" t="n">
-        <v>78874</v>
+        <v>79710</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11467,37 +11467,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456644</v>
+        <v>456382</v>
       </c>
       <c r="R108" t="n">
-        <v>6800358</v>
+        <v>6800427</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11538,7 +11535,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11560,7 +11556,7 @@
         <v>128804554</v>
       </c>
       <c r="B109" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11664,10 +11660,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814632</v>
+        <v>128814683</v>
       </c>
       <c r="B110" t="n">
-        <v>79706</v>
+        <v>78878</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11675,34 +11671,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456382</v>
+        <v>456644</v>
       </c>
       <c r="R110" t="n">
-        <v>6800427</v>
+        <v>6800358</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11743,6 +11742,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128814646</v>
+        <v>128814679</v>
       </c>
       <c r="B111" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,42 +11772,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456519</v>
+        <v>456753</v>
       </c>
       <c r="R111" t="n">
-        <v>6800414</v>
+        <v>6800533</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11866,10 +11858,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814634</v>
+        <v>128805558</v>
       </c>
       <c r="B112" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11877,42 +11869,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456405</v>
+        <v>456627</v>
       </c>
       <c r="R112" t="n">
-        <v>6800457</v>
+        <v>6800521</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11942,9 +11926,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11959,22 +11953,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128805558</v>
+        <v>128814731</v>
       </c>
       <c r="B113" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12006,10 +12000,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456627</v>
+        <v>456580</v>
       </c>
       <c r="R113" t="n">
-        <v>6800521</v>
+        <v>6800292</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12039,19 +12033,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12066,22 +12050,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814731</v>
+        <v>128814696</v>
       </c>
       <c r="B114" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12089,21 +12073,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12113,10 +12097,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456580</v>
+        <v>456559</v>
       </c>
       <c r="R114" t="n">
-        <v>6800292</v>
+        <v>6800576</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12175,10 +12159,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814696</v>
+        <v>128803369</v>
       </c>
       <c r="B115" t="n">
-        <v>78873</v>
+        <v>79739</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,21 +12170,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12210,10 +12194,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456559</v>
+        <v>456688</v>
       </c>
       <c r="R115" t="n">
-        <v>6800576</v>
+        <v>6800474</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12243,9 +12227,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12260,22 +12254,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128803369</v>
+        <v>128814614</v>
       </c>
       <c r="B116" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12307,10 +12301,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456688</v>
+        <v>456522</v>
       </c>
       <c r="R116" t="n">
-        <v>6800474</v>
+        <v>6800319</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12340,19 +12334,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12367,22 +12351,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814614</v>
+        <v>128814687</v>
       </c>
       <c r="B117" t="n">
-        <v>79735</v>
+        <v>78877</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12390,21 +12374,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12414,10 +12398,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456522</v>
+        <v>456556</v>
       </c>
       <c r="R117" t="n">
-        <v>6800319</v>
+        <v>6800320</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12476,10 +12460,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814687</v>
+        <v>128814646</v>
       </c>
       <c r="B118" t="n">
-        <v>78873</v>
+        <v>57713</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12487,34 +12471,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456556</v>
+        <v>456519</v>
       </c>
       <c r="R118" t="n">
-        <v>6800320</v>
+        <v>6800414</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12573,10 +12565,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814679</v>
+        <v>128814634</v>
       </c>
       <c r="B119" t="n">
-        <v>78874</v>
+        <v>57716</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12584,34 +12576,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456753</v>
+        <v>456405</v>
       </c>
       <c r="R119" t="n">
-        <v>6800533</v>
+        <v>6800457</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12673,7 +12673,7 @@
         <v>128805585</v>
       </c>
       <c r="B120" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>128814706</v>
       </c>
       <c r="B121" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>128804496</v>
       </c>
       <c r="B122" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>128814700</v>
       </c>
       <c r="B123" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>128816339</v>
       </c>
       <c r="B124" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>128816336</v>
       </c>
       <c r="B126" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816338</v>
+        <v>128816353</v>
       </c>
       <c r="B127" t="n">
-        <v>79706</v>
+        <v>78877</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,37 +13392,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456478</v>
+        <v>456522</v>
       </c>
       <c r="R127" t="n">
-        <v>6800591</v>
+        <v>6800357</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13463,7 +13460,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13482,10 +13478,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816353</v>
+        <v>128816338</v>
       </c>
       <c r="B128" t="n">
-        <v>78873</v>
+        <v>79710</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13493,34 +13489,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456522</v>
+        <v>456478</v>
       </c>
       <c r="R128" t="n">
-        <v>6800357</v>
+        <v>6800591</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13561,6 +13560,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13684,10 +13684,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128816349</v>
+        <v>128816347</v>
       </c>
       <c r="B130" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13713,16 +13713,19 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>456688</v>
+        <v>456473</v>
       </c>
       <c r="R130" t="n">
-        <v>6800401</v>
+        <v>6800370</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13763,6 +13766,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13781,10 +13785,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128816347</v>
+        <v>128816349</v>
       </c>
       <c r="B131" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13810,19 +13814,16 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>456473</v>
+        <v>456688</v>
       </c>
       <c r="R131" t="n">
-        <v>6800370</v>
+        <v>6800401</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13863,7 +13864,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>128816354</v>
       </c>
       <c r="B132" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>128816356</v>
       </c>
       <c r="B133" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>128816351</v>
       </c>
       <c r="B134" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>128816340</v>
       </c>
       <c r="B135" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>128816331</v>
       </c>
       <c r="B136" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>128816335</v>
       </c>
       <c r="B137" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>128816352</v>
       </c>
       <c r="B138" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>128816348</v>
       </c>
       <c r="B139" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>128816350</v>
       </c>
       <c r="B140" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>128816334</v>
       </c>
       <c r="B141" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>128816358</v>
       </c>
       <c r="B142" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>128816361</v>
       </c>
       <c r="B143" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>128816332</v>
       </c>
       <c r="B144" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128816359</v>
       </c>
       <c r="B145" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128816333</v>
+        <v>128816346</v>
       </c>
       <c r="B147" t="n">
-        <v>79148</v>
+        <v>78878</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15380,34 +15380,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>456756</v>
+        <v>456521</v>
       </c>
       <c r="R147" t="n">
-        <v>6800522</v>
+        <v>6800343</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15448,6 +15451,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15466,10 +15470,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128816346</v>
+        <v>128816333</v>
       </c>
       <c r="B148" t="n">
-        <v>78874</v>
+        <v>79152</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15477,37 +15481,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>456521</v>
+        <v>456756</v>
       </c>
       <c r="R148" t="n">
-        <v>6800343</v>
+        <v>6800522</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15548,7 +15549,6 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -15570,7 +15570,7 @@
         <v>128816341</v>
       </c>
       <c r="B149" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15668,10 +15668,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128816337</v>
+        <v>128816360</v>
       </c>
       <c r="B150" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15679,21 +15679,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>456758</v>
+        <v>456583</v>
       </c>
       <c r="R150" t="n">
-        <v>6800574</v>
+        <v>6800417</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15765,10 +15765,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128816360</v>
+        <v>128816337</v>
       </c>
       <c r="B151" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15776,21 +15776,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15800,10 +15800,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>456583</v>
+        <v>456758</v>
       </c>
       <c r="R151" t="n">
-        <v>6800417</v>
+        <v>6800574</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128814640</v>
+        <v>128814658</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1029,7 +1029,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456331</v>
+        <v>456645</v>
       </c>
       <c r="R5" t="n">
-        <v>6800312</v>
+        <v>6800444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128803425</v>
+        <v>128803579</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456681</v>
+        <v>456698</v>
       </c>
       <c r="R6" t="n">
-        <v>6800496</v>
+        <v>6800503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1182,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128805128</v>
+        <v>128801339</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456660</v>
+        <v>456742</v>
       </c>
       <c r="R7" t="n">
-        <v>6800603</v>
+        <v>6800421</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128814728</v>
+        <v>128805128</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1350,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456616</v>
+        <v>456660</v>
       </c>
       <c r="R8" t="n">
-        <v>6800533</v>
+        <v>6800603</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,9 +1388,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,19 +1415,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128803579</v>
+        <v>128814728</v>
       </c>
       <c r="B9" t="n">
         <v>79120</v>
@@ -1447,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456698</v>
+        <v>456616</v>
       </c>
       <c r="R9" t="n">
-        <v>6800503</v>
+        <v>6800533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,24 +1495,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,22 +1512,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128801339</v>
+        <v>128814640</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,34 +1535,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456742</v>
+        <v>456331</v>
       </c>
       <c r="R10" t="n">
-        <v>6800421</v>
+        <v>6800312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,19 +1600,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,65 +1617,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128814658</v>
+        <v>128803425</v>
       </c>
       <c r="B11" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456645</v>
+        <v>456681</v>
       </c>
       <c r="R11" t="n">
-        <v>6800444</v>
+        <v>6800496</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,9 +1697,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128804672</v>
+        <v>128814681</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456733</v>
+        <v>456761</v>
       </c>
       <c r="R12" t="n">
-        <v>6800618</v>
+        <v>6800515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,19 +1804,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,22 +1821,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814666</v>
+        <v>128804672</v>
       </c>
       <c r="B13" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,42 +1844,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456659</v>
+        <v>456733</v>
       </c>
       <c r="R13" t="n">
-        <v>6800402</v>
+        <v>6800618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,9 +1901,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,22 +1928,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814681</v>
+        <v>128814666</v>
       </c>
       <c r="B14" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,34 +1951,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456761</v>
+        <v>456659</v>
       </c>
       <c r="R14" t="n">
-        <v>6800515</v>
+        <v>6800402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814744</v>
+        <v>128814693</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456737</v>
+        <v>456515</v>
       </c>
       <c r="R15" t="n">
-        <v>6800417</v>
+        <v>6800380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814729</v>
+        <v>128814715</v>
       </c>
       <c r="B16" t="n">
         <v>79120</v>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456606</v>
+        <v>456589</v>
       </c>
       <c r="R16" t="n">
-        <v>6800334</v>
+        <v>6800303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814715</v>
+        <v>128814654</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,34 +2250,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456589</v>
+        <v>456705</v>
       </c>
       <c r="R17" t="n">
-        <v>6800303</v>
+        <v>6800486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2344,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128804638</v>
+        <v>128814744</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,21 +2355,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2379,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456748</v>
+        <v>456737</v>
       </c>
       <c r="R18" t="n">
-        <v>6800617</v>
+        <v>6800417</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,19 +2412,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,19 +2429,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805619</v>
+        <v>128814729</v>
       </c>
       <c r="B19" t="n">
         <v>79120</v>
@@ -2478,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456600</v>
+        <v>456606</v>
       </c>
       <c r="R19" t="n">
-        <v>6800539</v>
+        <v>6800334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,19 +2509,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2538,19 +2526,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128805376</v>
+        <v>128805619</v>
       </c>
       <c r="B20" t="n">
         <v>79120</v>
@@ -2585,10 +2573,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456589</v>
+        <v>456600</v>
       </c>
       <c r="R20" t="n">
-        <v>6800567</v>
+        <v>6800539</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,10 +2645,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128814654</v>
+        <v>128805376</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,42 +2656,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456705</v>
+        <v>456589</v>
       </c>
       <c r="R21" t="n">
-        <v>6800486</v>
+        <v>6800567</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,9 +2713,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,22 +2740,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814693</v>
+        <v>128804638</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,21 +2763,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2797,10 +2787,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456515</v>
+        <v>456748</v>
       </c>
       <c r="R22" t="n">
-        <v>6800380</v>
+        <v>6800617</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2830,9 +2820,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,12 +2847,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814652</v>
+        <v>128814716</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,42 +2977,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456781</v>
+        <v>456477</v>
       </c>
       <c r="R24" t="n">
-        <v>6800644</v>
+        <v>6800324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,6 +3037,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,10 +3068,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814644</v>
+        <v>128805061</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,42 +3079,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456603</v>
+        <v>456690</v>
       </c>
       <c r="R25" t="n">
-        <v>6800371</v>
+        <v>6800603</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,9 +3136,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3164,22 +3163,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814716</v>
+        <v>128814703</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3186,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3210,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456477</v>
+        <v>456766</v>
       </c>
       <c r="R26" t="n">
-        <v>6800324</v>
+        <v>6800611</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,11 +3246,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3278,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814616</v>
+        <v>128814724</v>
       </c>
       <c r="B27" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456487</v>
+        <v>456520</v>
       </c>
       <c r="R27" t="n">
-        <v>6800546</v>
+        <v>6800367</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128805061</v>
+        <v>128814616</v>
       </c>
       <c r="B28" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3380,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456690</v>
+        <v>456487</v>
       </c>
       <c r="R28" t="n">
-        <v>6800603</v>
+        <v>6800546</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,19 +3437,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3470,22 +3454,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814703</v>
+        <v>128814652</v>
       </c>
       <c r="B29" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,34 +3477,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456766</v>
+        <v>456781</v>
       </c>
       <c r="R29" t="n">
-        <v>6800611</v>
+        <v>6800644</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814724</v>
+        <v>128814644</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,34 +3582,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456520</v>
+        <v>456603</v>
       </c>
       <c r="R30" t="n">
-        <v>6800367</v>
+        <v>6800371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814720</v>
+        <v>128814692</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456446</v>
+        <v>456354</v>
       </c>
       <c r="R32" t="n">
-        <v>6800471</v>
+        <v>6800374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814692</v>
+        <v>128814708</v>
       </c>
       <c r="B33" t="n">
         <v>78877</v>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456354</v>
+        <v>456702</v>
       </c>
       <c r="R33" t="n">
-        <v>6800374</v>
+        <v>6800512</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814626</v>
+        <v>128814720</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456763</v>
+        <v>456446</v>
       </c>
       <c r="R34" t="n">
-        <v>6800617</v>
+        <v>6800471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814708</v>
+        <v>128814626</v>
       </c>
       <c r="B35" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456702</v>
+        <v>456763</v>
       </c>
       <c r="R35" t="n">
-        <v>6800512</v>
+        <v>6800617</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4263,10 +4263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128804553</v>
+        <v>128814727</v>
       </c>
       <c r="B37" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,21 +4274,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456768</v>
+        <v>456600</v>
       </c>
       <c r="R37" t="n">
-        <v>6800626</v>
+        <v>6800519</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,19 +4331,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4358,19 +4348,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814689</v>
+        <v>128814711</v>
       </c>
       <c r="B38" t="n">
         <v>78877</v>
@@ -4405,10 +4395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456495</v>
+        <v>456642</v>
       </c>
       <c r="R38" t="n">
-        <v>6800433</v>
+        <v>6800358</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4467,10 +4457,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814727</v>
+        <v>128804553</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4478,21 +4468,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4502,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456600</v>
+        <v>456768</v>
       </c>
       <c r="R39" t="n">
-        <v>6800519</v>
+        <v>6800626</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4535,9 +4525,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,19 +4552,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128814710</v>
+        <v>128814689</v>
       </c>
       <c r="B40" t="n">
         <v>78877</v>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456770</v>
+        <v>456495</v>
       </c>
       <c r="R40" t="n">
-        <v>6800515</v>
+        <v>6800433</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128814711</v>
+        <v>128814710</v>
       </c>
       <c r="B41" t="n">
         <v>78877</v>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456642</v>
+        <v>456770</v>
       </c>
       <c r="R41" t="n">
-        <v>6800358</v>
+        <v>6800515</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128805352</v>
+        <v>128814733</v>
       </c>
       <c r="B43" t="n">
         <v>79120</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456605</v>
+        <v>456547</v>
       </c>
       <c r="R43" t="n">
-        <v>6800580</v>
+        <v>6800300</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4923,19 +4923,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,19 +4940,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128814733</v>
+        <v>128805352</v>
       </c>
       <c r="B44" t="n">
         <v>79120</v>
@@ -4997,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456547</v>
+        <v>456605</v>
       </c>
       <c r="R44" t="n">
-        <v>6800300</v>
+        <v>6800580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5030,9 +5020,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5047,12 +5047,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B46" t="n">
         <v>79739</v>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R46" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B47" t="n">
         <v>79739</v>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R47" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128799275</v>
+        <v>128814612</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,21 +5692,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456665</v>
+        <v>456539</v>
       </c>
       <c r="R51" t="n">
-        <v>6800399</v>
+        <v>6800496</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,24 +5749,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5781,22 +5766,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814718</v>
+        <v>128814648</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5804,34 +5789,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456559</v>
+        <v>456618</v>
       </c>
       <c r="R52" t="n">
-        <v>6800586</v>
+        <v>6800564</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5890,10 +5883,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814612</v>
+        <v>128802364</v>
       </c>
       <c r="B53" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5901,21 +5894,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5925,10 +5918,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456539</v>
+        <v>456718</v>
       </c>
       <c r="R53" t="n">
-        <v>6800496</v>
+        <v>6800502</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5958,9 +5951,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5975,19 +5978,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814719</v>
+        <v>128799275</v>
       </c>
       <c r="B54" t="n">
         <v>79120</v>
@@ -6022,10 +6025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456527</v>
+        <v>456665</v>
       </c>
       <c r="R54" t="n">
-        <v>6800610</v>
+        <v>6800399</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6055,9 +6058,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6072,19 +6090,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814736</v>
+        <v>128814719</v>
       </c>
       <c r="B55" t="n">
         <v>79120</v>
@@ -6119,10 +6137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456569</v>
+        <v>456527</v>
       </c>
       <c r="R55" t="n">
-        <v>6800599</v>
+        <v>6800610</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6181,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814620</v>
+        <v>128814736</v>
       </c>
       <c r="B56" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6192,37 +6210,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456385</v>
+        <v>456569</v>
       </c>
       <c r="R56" t="n">
-        <v>6800430</v>
+        <v>6800599</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6263,7 +6278,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6282,10 +6296,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814648</v>
+        <v>128814620</v>
       </c>
       <c r="B57" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6293,31 +6307,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6325,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456618</v>
+        <v>456385</v>
       </c>
       <c r="R57" t="n">
-        <v>6800564</v>
+        <v>6800430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6369,6 +6378,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6387,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128802364</v>
+        <v>128814718</v>
       </c>
       <c r="B58" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,21 +6408,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6422,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456718</v>
+        <v>456559</v>
       </c>
       <c r="R58" t="n">
-        <v>6800502</v>
+        <v>6800586</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6455,19 +6465,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,12 +6482,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128804576</v>
+        <v>128814675</v>
       </c>
       <c r="B66" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7219,39 +7219,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456761</v>
+        <v>456513</v>
       </c>
       <c r="R66" t="n">
-        <v>6800606</v>
+        <v>6800383</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7281,46 +7279,37 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128814656</v>
+        <v>128804576</v>
       </c>
       <c r="B67" t="n">
         <v>57713</v>
@@ -7349,24 +7338,21 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456658</v>
+        <v>456761</v>
       </c>
       <c r="R67" t="n">
-        <v>6800419</v>
+        <v>6800606</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7396,9 +7382,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7413,19 +7409,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128814660</v>
+        <v>128814656</v>
       </c>
       <c r="B68" t="n">
         <v>57713</v>
@@ -7458,7 +7454,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7468,10 +7464,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456747</v>
+        <v>456658</v>
       </c>
       <c r="R68" t="n">
-        <v>6800420</v>
+        <v>6800419</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7530,10 +7526,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128814675</v>
+        <v>128814660</v>
       </c>
       <c r="B69" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7541,26 +7537,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7568,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456513</v>
+        <v>456747</v>
       </c>
       <c r="R69" t="n">
-        <v>6800383</v>
+        <v>6800420</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,7 +7613,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>128799394</v>
       </c>
       <c r="B70" t="n">
-        <v>91449</v>
+        <v>91454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7738,10 +7738,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814717</v>
+        <v>128814691</v>
       </c>
       <c r="B71" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456529</v>
+        <v>456385</v>
       </c>
       <c r="R71" t="n">
-        <v>6800501</v>
+        <v>6800430</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128814691</v>
+        <v>128814717</v>
       </c>
       <c r="B72" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,21 +7846,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>456385</v>
+        <v>456529</v>
       </c>
       <c r="R72" t="n">
-        <v>6800430</v>
+        <v>6800501</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8330,48 +8330,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128814722</v>
+        <v>128800812</v>
       </c>
       <c r="B77" t="n">
-        <v>79120</v>
+        <v>58086</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456349</v>
+        <v>456691</v>
       </c>
       <c r="R77" t="n">
-        <v>6800436</v>
+        <v>6800368</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8398,9 +8403,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8415,22 +8430,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128800436</v>
+        <v>128814677</v>
       </c>
       <c r="B78" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8438,21 +8453,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8462,10 +8477,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456671</v>
+        <v>456747</v>
       </c>
       <c r="R78" t="n">
-        <v>6800350</v>
+        <v>6800569</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8495,19 +8510,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,22 +8527,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814709</v>
+        <v>128801262</v>
       </c>
       <c r="B79" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8545,21 +8550,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8574,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456706</v>
+        <v>456703</v>
       </c>
       <c r="R79" t="n">
-        <v>6800520</v>
+        <v>6800429</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8602,9 +8607,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8619,22 +8634,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814702</v>
+        <v>128800436</v>
       </c>
       <c r="B80" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,21 +8657,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8666,10 +8681,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456788</v>
+        <v>456671</v>
       </c>
       <c r="R80" t="n">
-        <v>6800626</v>
+        <v>6800350</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8699,9 +8714,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8716,19 +8741,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814695</v>
+        <v>128814709</v>
       </c>
       <c r="B81" t="n">
         <v>78877</v>
@@ -8763,10 +8788,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456547</v>
+        <v>456706</v>
       </c>
       <c r="R81" t="n">
-        <v>6800403</v>
+        <v>6800520</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8825,10 +8850,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814618</v>
+        <v>128814702</v>
       </c>
       <c r="B82" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8861,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8885,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456450</v>
+        <v>456788</v>
       </c>
       <c r="R82" t="n">
-        <v>6800571</v>
+        <v>6800626</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8922,53 +8947,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128800812</v>
+        <v>128814722</v>
       </c>
       <c r="B83" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456691</v>
+        <v>456349</v>
       </c>
       <c r="R83" t="n">
-        <v>6800368</v>
+        <v>6800436</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8995,19 +9015,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9022,22 +9032,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814677</v>
+        <v>128814695</v>
       </c>
       <c r="B84" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9045,21 +9055,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9069,10 +9079,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456747</v>
+        <v>456547</v>
       </c>
       <c r="R84" t="n">
-        <v>6800569</v>
+        <v>6800403</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9131,10 +9141,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128801262</v>
+        <v>128814618</v>
       </c>
       <c r="B85" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9142,21 +9152,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9166,10 +9176,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456703</v>
+        <v>456450</v>
       </c>
       <c r="R85" t="n">
-        <v>6800429</v>
+        <v>6800571</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9199,19 +9209,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9226,12 +9226,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814723</v>
+        <v>128814726</v>
       </c>
       <c r="B87" t="n">
         <v>79120</v>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456351</v>
+        <v>456524</v>
       </c>
       <c r="R87" t="n">
-        <v>6800371</v>
+        <v>6800431</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814726</v>
+        <v>128814723</v>
       </c>
       <c r="B88" t="n">
         <v>79120</v>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456524</v>
+        <v>456351</v>
       </c>
       <c r="R88" t="n">
-        <v>6800431</v>
+        <v>6800371</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128814732</v>
+        <v>128799696</v>
       </c>
       <c r="B90" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456571</v>
+        <v>456668</v>
       </c>
       <c r="R90" t="n">
-        <v>6800296</v>
+        <v>6800363</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9694,9 +9694,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9711,12 +9721,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9917,10 +9927,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814690</v>
+        <v>128814732</v>
       </c>
       <c r="B93" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9928,21 +9938,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9952,10 +9962,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456465</v>
+        <v>456571</v>
       </c>
       <c r="R93" t="n">
-        <v>6800546</v>
+        <v>6800296</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10014,7 +10024,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814699</v>
+        <v>128814690</v>
       </c>
       <c r="B94" t="n">
         <v>78877</v>
@@ -10049,10 +10059,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456496</v>
+        <v>456465</v>
       </c>
       <c r="R94" t="n">
-        <v>6800549</v>
+        <v>6800546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10121,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814694</v>
+        <v>128814699</v>
       </c>
       <c r="B95" t="n">
         <v>78877</v>
@@ -10146,10 +10156,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456594</v>
+        <v>456496</v>
       </c>
       <c r="R95" t="n">
-        <v>6800423</v>
+        <v>6800549</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10208,10 +10218,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128804256</v>
+        <v>128814694</v>
       </c>
       <c r="B96" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10219,21 +10229,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10243,10 +10253,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456794</v>
+        <v>456594</v>
       </c>
       <c r="R96" t="n">
-        <v>6800605</v>
+        <v>6800423</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10276,19 +10286,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10303,22 +10303,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814664</v>
+        <v>128804256</v>
       </c>
       <c r="B97" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10326,42 +10326,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456676</v>
+        <v>456794</v>
       </c>
       <c r="R97" t="n">
-        <v>6800380</v>
+        <v>6800605</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10391,9 +10383,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10408,22 +10410,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128799696</v>
+        <v>128814664</v>
       </c>
       <c r="B98" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10431,34 +10433,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456668</v>
+        <v>456676</v>
       </c>
       <c r="R98" t="n">
-        <v>6800363</v>
+        <v>6800380</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10488,19 +10498,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10515,12 +10515,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10632,10 +10632,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805054</v>
+        <v>128814632</v>
       </c>
       <c r="B100" t="n">
-        <v>79739</v>
+        <v>79710</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10643,21 +10643,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456690</v>
+        <v>456382</v>
       </c>
       <c r="R100" t="n">
-        <v>6800603</v>
+        <v>6800427</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10700,19 +10700,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10727,22 +10717,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128814698</v>
+        <v>128804554</v>
       </c>
       <c r="B101" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10750,21 +10740,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10774,10 +10764,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456491</v>
+        <v>456768</v>
       </c>
       <c r="R101" t="n">
-        <v>6800537</v>
+        <v>6800626</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10807,9 +10797,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10824,22 +10824,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814624</v>
+        <v>128814683</v>
       </c>
       <c r="B102" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10847,21 +10847,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10874,10 +10874,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456688</v>
+        <v>456644</v>
       </c>
       <c r="R102" t="n">
-        <v>6800585</v>
+        <v>6800358</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10937,45 +10937,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128804050</v>
+        <v>128814713</v>
       </c>
       <c r="B103" t="n">
-        <v>79120</v>
+        <v>90886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456753</v>
+        <v>456692</v>
       </c>
       <c r="R103" t="n">
-        <v>6800562</v>
+        <v>6800391</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11005,54 +11008,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805203</v>
+        <v>128805054</v>
       </c>
       <c r="B104" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11060,21 +11049,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11084,10 +11073,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456650</v>
+        <v>456690</v>
       </c>
       <c r="R104" t="n">
-        <v>6800594</v>
+        <v>6800603</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11156,7 +11145,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814737</v>
+        <v>128804050</v>
       </c>
       <c r="B105" t="n">
         <v>79120</v>
@@ -11191,10 +11180,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456555</v>
+        <v>456753</v>
       </c>
       <c r="R105" t="n">
-        <v>6800627</v>
+        <v>6800562</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11224,9 +11213,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11241,19 +11245,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814725</v>
+        <v>128805203</v>
       </c>
       <c r="B106" t="n">
         <v>79120</v>
@@ -11288,10 +11292,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456598</v>
+        <v>456650</v>
       </c>
       <c r="R106" t="n">
-        <v>6800407</v>
+        <v>6800594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11321,14 +11325,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11343,60 +11352,57 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814713</v>
+        <v>128814698</v>
       </c>
       <c r="B107" t="n">
-        <v>90881</v>
+        <v>78877</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5685</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456692</v>
+        <v>456491</v>
       </c>
       <c r="R107" t="n">
-        <v>6800391</v>
+        <v>6800537</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11437,7 +11443,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11461,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128814632</v>
+        <v>128814737</v>
       </c>
       <c r="B108" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11467,21 +11472,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11491,10 +11496,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456382</v>
+        <v>456555</v>
       </c>
       <c r="R108" t="n">
-        <v>6800427</v>
+        <v>6800627</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11553,10 +11558,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128804554</v>
+        <v>128814725</v>
       </c>
       <c r="B109" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11564,21 +11569,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11588,10 +11593,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456768</v>
+        <v>456598</v>
       </c>
       <c r="R109" t="n">
-        <v>6800626</v>
+        <v>6800407</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11621,19 +11626,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11648,22 +11648,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814683</v>
+        <v>128814624</v>
       </c>
       <c r="B110" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456644</v>
+        <v>456688</v>
       </c>
       <c r="R110" t="n">
-        <v>6800358</v>
+        <v>6800585</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128814679</v>
+        <v>128805558</v>
       </c>
       <c r="B111" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,21 +11772,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456753</v>
+        <v>456627</v>
       </c>
       <c r="R111" t="n">
-        <v>6800533</v>
+        <v>6800521</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11829,9 +11829,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11846,19 +11856,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128805558</v>
+        <v>128814731</v>
       </c>
       <c r="B112" t="n">
         <v>79120</v>
@@ -11893,10 +11903,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456627</v>
+        <v>456580</v>
       </c>
       <c r="R112" t="n">
-        <v>6800521</v>
+        <v>6800292</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11926,19 +11936,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11953,22 +11953,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814731</v>
+        <v>128814696</v>
       </c>
       <c r="B113" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11976,21 +11976,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456580</v>
+        <v>456559</v>
       </c>
       <c r="R113" t="n">
-        <v>6800292</v>
+        <v>6800576</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12062,10 +12062,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814696</v>
+        <v>128803369</v>
       </c>
       <c r="B114" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12073,21 +12073,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12097,10 +12097,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456559</v>
+        <v>456688</v>
       </c>
       <c r="R114" t="n">
-        <v>6800576</v>
+        <v>6800474</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12130,9 +12130,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12147,22 +12157,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128803369</v>
+        <v>128814687</v>
       </c>
       <c r="B115" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12170,21 +12180,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12194,10 +12204,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456688</v>
+        <v>456556</v>
       </c>
       <c r="R115" t="n">
-        <v>6800474</v>
+        <v>6800320</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12227,19 +12237,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12254,12 +12254,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814687</v>
+        <v>128814646</v>
       </c>
       <c r="B117" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12374,34 +12374,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456556</v>
+        <v>456519</v>
       </c>
       <c r="R117" t="n">
-        <v>6800320</v>
+        <v>6800414</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12460,10 +12468,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814646</v>
+        <v>128814634</v>
       </c>
       <c r="B118" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12471,16 +12479,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12503,10 +12511,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456519</v>
+        <v>456405</v>
       </c>
       <c r="R118" t="n">
-        <v>6800414</v>
+        <v>6800457</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12565,10 +12573,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814634</v>
+        <v>128814679</v>
       </c>
       <c r="B119" t="n">
-        <v>57716</v>
+        <v>78878</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12576,42 +12584,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456405</v>
+        <v>456753</v>
       </c>
       <c r="R119" t="n">
-        <v>6800457</v>
+        <v>6800533</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13478,10 +13478,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816338</v>
+        <v>128816343</v>
       </c>
       <c r="B128" t="n">
-        <v>79710</v>
+        <v>57716</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13489,26 +13489,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13516,10 +13521,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456478</v>
+        <v>456341</v>
       </c>
       <c r="R128" t="n">
-        <v>6800591</v>
+        <v>6800306</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13560,7 +13565,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13579,10 +13583,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816343</v>
+        <v>128816338</v>
       </c>
       <c r="B129" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13590,31 +13594,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13622,10 +13621,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456341</v>
+        <v>456478</v>
       </c>
       <c r="R129" t="n">
-        <v>6800306</v>
+        <v>6800591</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13666,6 +13665,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14076,10 +14076,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128816351</v>
+        <v>128816340</v>
       </c>
       <c r="B134" t="n">
-        <v>78877</v>
+        <v>79710</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14087,21 +14087,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14114,10 +14114,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>456472</v>
+        <v>456564</v>
       </c>
       <c r="R134" t="n">
-        <v>6800370</v>
+        <v>6800618</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14177,10 +14177,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128816340</v>
+        <v>128816351</v>
       </c>
       <c r="B135" t="n">
-        <v>79710</v>
+        <v>78877</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14188,21 +14188,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14215,10 +14215,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>456564</v>
+        <v>456472</v>
       </c>
       <c r="R135" t="n">
-        <v>6800618</v>
+        <v>6800370</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15668,10 +15668,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128816360</v>
+        <v>128816337</v>
       </c>
       <c r="B150" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15679,21 +15679,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>456583</v>
+        <v>456758</v>
       </c>
       <c r="R150" t="n">
-        <v>6800417</v>
+        <v>6800574</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15765,10 +15765,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128816337</v>
+        <v>128816360</v>
       </c>
       <c r="B151" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15776,21 +15776,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15800,10 +15800,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>456758</v>
+        <v>456583</v>
       </c>
       <c r="R151" t="n">
-        <v>6800574</v>
+        <v>6800417</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128814701</v>
+        <v>128799069</v>
       </c>
       <c r="B2" t="n">
-        <v>78877</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456547</v>
+        <v>456632</v>
       </c>
       <c r="R2" t="n">
-        <v>6800436</v>
+        <v>6800431</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +748,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128800923</v>
+        <v>128814701</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456692</v>
+        <v>456547</v>
       </c>
       <c r="R3" t="n">
-        <v>6800405</v>
+        <v>6800436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,24 +855,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128799069</v>
+        <v>128800923</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456632</v>
+        <v>456692</v>
       </c>
       <c r="R4" t="n">
-        <v>6800431</v>
+        <v>6800405</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,6 +965,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128814658</v>
+        <v>128803579</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456645</v>
+        <v>456698</v>
       </c>
       <c r="R5" t="n">
-        <v>6800444</v>
+        <v>6800503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,9 +1064,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128803579</v>
+        <v>128801339</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456698</v>
+        <v>456742</v>
       </c>
       <c r="R6" t="n">
-        <v>6800503</v>
+        <v>6800421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,11 +1189,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128801339</v>
+        <v>128805128</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456742</v>
+        <v>456660</v>
       </c>
       <c r="R7" t="n">
-        <v>6800421</v>
+        <v>6800603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128805128</v>
+        <v>128814728</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1355,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456660</v>
+        <v>456616</v>
       </c>
       <c r="R8" t="n">
-        <v>6800603</v>
+        <v>6800533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,19 +1390,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,22 +1407,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814728</v>
+        <v>128814658</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,34 +1430,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456616</v>
+        <v>456645</v>
       </c>
       <c r="R9" t="n">
-        <v>6800533</v>
+        <v>6800444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814681</v>
+        <v>128814666</v>
       </c>
       <c r="B12" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,34 +1747,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456761</v>
+        <v>456659</v>
       </c>
       <c r="R12" t="n">
-        <v>6800515</v>
+        <v>6800402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814666</v>
+        <v>128814681</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,42 +1959,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456659</v>
+        <v>456761</v>
       </c>
       <c r="R14" t="n">
-        <v>6800402</v>
+        <v>6800515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814693</v>
+        <v>128814744</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456515</v>
+        <v>456737</v>
       </c>
       <c r="R15" t="n">
-        <v>6800380</v>
+        <v>6800417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814715</v>
+        <v>128804638</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456589</v>
+        <v>456748</v>
       </c>
       <c r="R16" t="n">
-        <v>6800303</v>
+        <v>6800617</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,9 +2210,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,22 +2237,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814654</v>
+        <v>128814729</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,42 +2260,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456705</v>
+        <v>456606</v>
       </c>
       <c r="R17" t="n">
-        <v>6800486</v>
+        <v>6800334</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,7 +2346,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128814744</v>
+        <v>128805619</v>
       </c>
       <c r="B18" t="n">
         <v>79120</v>
@@ -2379,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456737</v>
+        <v>456600</v>
       </c>
       <c r="R18" t="n">
-        <v>6800417</v>
+        <v>6800539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2412,9 +2414,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,19 +2441,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128814729</v>
+        <v>128805376</v>
       </c>
       <c r="B19" t="n">
         <v>79120</v>
@@ -2476,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456606</v>
+        <v>456589</v>
       </c>
       <c r="R19" t="n">
-        <v>6800334</v>
+        <v>6800567</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,9 +2521,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,22 +2548,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128805619</v>
+        <v>128814693</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,21 +2571,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2573,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456600</v>
+        <v>456515</v>
       </c>
       <c r="R20" t="n">
-        <v>6800539</v>
+        <v>6800380</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2606,19 +2628,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,19 +2645,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128805376</v>
+        <v>128814715</v>
       </c>
       <c r="B21" t="n">
         <v>79120</v>
@@ -2683,7 +2695,7 @@
         <v>456589</v>
       </c>
       <c r="R21" t="n">
-        <v>6800567</v>
+        <v>6800303</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,19 +2725,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,22 +2742,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128804638</v>
+        <v>128814654</v>
       </c>
       <c r="B22" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,34 +2765,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456748</v>
+        <v>456705</v>
       </c>
       <c r="R22" t="n">
-        <v>6800617</v>
+        <v>6800486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,19 +2830,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,12 +2847,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814716</v>
+        <v>128814652</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,34 +2977,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456477</v>
+        <v>456781</v>
       </c>
       <c r="R24" t="n">
-        <v>6800324</v>
+        <v>6800644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,11 +3045,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3068,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128805061</v>
+        <v>128814644</v>
       </c>
       <c r="B25" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3079,34 +3082,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456690</v>
+        <v>456603</v>
       </c>
       <c r="R25" t="n">
-        <v>6800603</v>
+        <v>6800371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,19 +3147,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,22 +3164,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814703</v>
+        <v>128814616</v>
       </c>
       <c r="B26" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,21 +3187,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3210,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456766</v>
+        <v>456487</v>
       </c>
       <c r="R26" t="n">
-        <v>6800611</v>
+        <v>6800546</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,7 +3273,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814724</v>
+        <v>128814716</v>
       </c>
       <c r="B27" t="n">
         <v>79120</v>
@@ -3307,10 +3308,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456520</v>
+        <v>456477</v>
       </c>
       <c r="R27" t="n">
-        <v>6800367</v>
+        <v>6800324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,6 +3344,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,10 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814616</v>
+        <v>128805061</v>
       </c>
       <c r="B28" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456487</v>
+        <v>456690</v>
       </c>
       <c r="R28" t="n">
-        <v>6800546</v>
+        <v>6800603</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,9 +3443,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3454,22 +3470,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814652</v>
+        <v>128814703</v>
       </c>
       <c r="B29" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,42 +3493,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456781</v>
+        <v>456766</v>
       </c>
       <c r="R29" t="n">
-        <v>6800644</v>
+        <v>6800611</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,10 +3579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814644</v>
+        <v>128814724</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,42 +3590,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456603</v>
+        <v>456520</v>
       </c>
       <c r="R30" t="n">
-        <v>6800371</v>
+        <v>6800367</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814708</v>
+        <v>128814626</v>
       </c>
       <c r="B33" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456702</v>
+        <v>456763</v>
       </c>
       <c r="R33" t="n">
-        <v>6800512</v>
+        <v>6800617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814720</v>
+        <v>128814708</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456446</v>
+        <v>456702</v>
       </c>
       <c r="R34" t="n">
-        <v>6800471</v>
+        <v>6800512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814626</v>
+        <v>128814720</v>
       </c>
       <c r="B35" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456763</v>
+        <v>456446</v>
       </c>
       <c r="R35" t="n">
-        <v>6800617</v>
+        <v>6800471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814743</v>
+        <v>128814710</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456566</v>
+        <v>456770</v>
       </c>
       <c r="R36" t="n">
-        <v>6800498</v>
+        <v>6800515</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,11 +4232,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4263,10 +4258,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814727</v>
+        <v>128804553</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,21 +4269,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4293,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456600</v>
+        <v>456768</v>
       </c>
       <c r="R37" t="n">
-        <v>6800519</v>
+        <v>6800626</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,9 +4326,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4348,19 +4353,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814711</v>
+        <v>128814689</v>
       </c>
       <c r="B38" t="n">
         <v>78877</v>
@@ -4395,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456642</v>
+        <v>456495</v>
       </c>
       <c r="R38" t="n">
-        <v>6800358</v>
+        <v>6800433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,10 +4462,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128804553</v>
+        <v>128814743</v>
       </c>
       <c r="B39" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,21 +4473,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4492,10 +4497,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456768</v>
+        <v>456566</v>
       </c>
       <c r="R39" t="n">
-        <v>6800626</v>
+        <v>6800498</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4525,19 +4530,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,22 +4552,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128814689</v>
+        <v>128814727</v>
       </c>
       <c r="B40" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456495</v>
+        <v>456600</v>
       </c>
       <c r="R40" t="n">
-        <v>6800433</v>
+        <v>6800519</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128814710</v>
+        <v>128814711</v>
       </c>
       <c r="B41" t="n">
         <v>78877</v>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456770</v>
+        <v>456642</v>
       </c>
       <c r="R41" t="n">
-        <v>6800515</v>
+        <v>6800358</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128814739</v>
+        <v>128805036</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456351</v>
+        <v>456690</v>
       </c>
       <c r="R42" t="n">
-        <v>6800353</v>
+        <v>6800603</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4826,9 +4826,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4843,19 +4853,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814733</v>
+        <v>128814739</v>
       </c>
       <c r="B43" t="n">
         <v>79120</v>
@@ -4890,10 +4900,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456547</v>
+        <v>456351</v>
       </c>
       <c r="R43" t="n">
-        <v>6800300</v>
+        <v>6800353</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4952,7 +4962,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128805352</v>
+        <v>128814733</v>
       </c>
       <c r="B44" t="n">
         <v>79120</v>
@@ -4987,10 +4997,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456605</v>
+        <v>456547</v>
       </c>
       <c r="R44" t="n">
-        <v>6800580</v>
+        <v>6800300</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5020,19 +5030,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5047,22 +5047,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128805036</v>
+        <v>128805352</v>
       </c>
       <c r="B45" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5070,21 +5070,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456690</v>
+        <v>456605</v>
       </c>
       <c r="R45" t="n">
-        <v>6800603</v>
+        <v>6800580</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128814612</v>
+        <v>128802364</v>
       </c>
       <c r="B51" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,21 +5692,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456539</v>
+        <v>456718</v>
       </c>
       <c r="R51" t="n">
-        <v>6800496</v>
+        <v>6800502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,9 +5749,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5766,22 +5776,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814648</v>
+        <v>128799275</v>
       </c>
       <c r="B52" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5789,42 +5799,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456618</v>
+        <v>456665</v>
       </c>
       <c r="R52" t="n">
-        <v>6800564</v>
+        <v>6800399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5854,9 +5856,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5871,22 +5888,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128802364</v>
+        <v>128814612</v>
       </c>
       <c r="B53" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5894,21 +5911,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5918,10 +5935,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456718</v>
+        <v>456539</v>
       </c>
       <c r="R53" t="n">
-        <v>6800502</v>
+        <v>6800496</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5951,19 +5968,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5978,19 +5985,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128799275</v>
+        <v>128814719</v>
       </c>
       <c r="B54" t="n">
         <v>79120</v>
@@ -6025,10 +6032,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456665</v>
+        <v>456527</v>
       </c>
       <c r="R54" t="n">
-        <v>6800399</v>
+        <v>6800610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6058,24 +6065,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6090,19 +6082,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814719</v>
+        <v>128814736</v>
       </c>
       <c r="B55" t="n">
         <v>79120</v>
@@ -6137,10 +6129,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456527</v>
+        <v>456569</v>
       </c>
       <c r="R55" t="n">
-        <v>6800610</v>
+        <v>6800599</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6199,10 +6191,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814736</v>
+        <v>128814620</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6210,34 +6202,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456569</v>
+        <v>456385</v>
       </c>
       <c r="R56" t="n">
-        <v>6800599</v>
+        <v>6800430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6278,6 +6273,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6296,10 +6292,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814620</v>
+        <v>128814718</v>
       </c>
       <c r="B57" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6307,37 +6303,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456385</v>
+        <v>456559</v>
       </c>
       <c r="R57" t="n">
-        <v>6800430</v>
+        <v>6800586</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6378,7 +6371,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6397,10 +6389,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128814718</v>
+        <v>128814648</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6408,34 +6400,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456559</v>
+        <v>456618</v>
       </c>
       <c r="R58" t="n">
-        <v>6800586</v>
+        <v>6800564</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128802133</v>
+        <v>128804576</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,34 +6903,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456775</v>
+        <v>456761</v>
       </c>
       <c r="R63" t="n">
-        <v>6800500</v>
+        <v>6800606</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6973,11 +6978,6 @@
       <c r="AB63" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7004,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128802369</v>
+        <v>128814660</v>
       </c>
       <c r="B64" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7015,34 +7015,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456718</v>
+        <v>456747</v>
       </c>
       <c r="R64" t="n">
-        <v>6800502</v>
+        <v>6800420</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7072,19 +7080,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7099,19 +7097,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128814721</v>
+        <v>128802133</v>
       </c>
       <c r="B65" t="n">
         <v>79120</v>
@@ -7146,10 +7144,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456414</v>
+        <v>456775</v>
       </c>
       <c r="R65" t="n">
-        <v>6800442</v>
+        <v>6800500</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7179,9 +7177,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7196,22 +7209,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128814675</v>
+        <v>128802369</v>
       </c>
       <c r="B66" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7219,37 +7232,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456513</v>
+        <v>456718</v>
       </c>
       <c r="R66" t="n">
-        <v>6800383</v>
+        <v>6800502</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7279,40 +7289,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128804576</v>
+        <v>128814721</v>
       </c>
       <c r="B67" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7320,39 +7339,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456761</v>
+        <v>456414</v>
       </c>
       <c r="R67" t="n">
-        <v>6800606</v>
+        <v>6800442</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7382,19 +7396,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7409,12 +7413,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7526,10 +7530,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128814660</v>
+        <v>128814675</v>
       </c>
       <c r="B69" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7537,31 +7541,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7569,10 +7568,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456747</v>
+        <v>456513</v>
       </c>
       <c r="R69" t="n">
-        <v>6800420</v>
+        <v>6800383</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7613,6 +7612,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8330,53 +8330,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128800812</v>
+        <v>128800436</v>
       </c>
       <c r="B77" t="n">
-        <v>58086</v>
+        <v>79739</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456691</v>
+        <v>456671</v>
       </c>
       <c r="R77" t="n">
-        <v>6800368</v>
+        <v>6800350</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8442,10 +8437,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128814677</v>
+        <v>128814709</v>
       </c>
       <c r="B78" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8453,21 +8448,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8477,10 +8472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456747</v>
+        <v>456706</v>
       </c>
       <c r="R78" t="n">
-        <v>6800569</v>
+        <v>6800520</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8539,10 +8534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128801262</v>
+        <v>128814702</v>
       </c>
       <c r="B79" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8550,21 +8545,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8574,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456703</v>
+        <v>456788</v>
       </c>
       <c r="R79" t="n">
-        <v>6800429</v>
+        <v>6800626</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8607,19 +8602,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8634,22 +8619,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128800436</v>
+        <v>128814722</v>
       </c>
       <c r="B80" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8657,21 +8642,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8681,10 +8666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456671</v>
+        <v>456349</v>
       </c>
       <c r="R80" t="n">
-        <v>6800350</v>
+        <v>6800436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8714,19 +8699,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8741,19 +8716,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814709</v>
+        <v>128814695</v>
       </c>
       <c r="B81" t="n">
         <v>78877</v>
@@ -8788,10 +8763,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456706</v>
+        <v>456547</v>
       </c>
       <c r="R81" t="n">
-        <v>6800520</v>
+        <v>6800403</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8850,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814702</v>
+        <v>128814618</v>
       </c>
       <c r="B82" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8861,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8885,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456788</v>
+        <v>456450</v>
       </c>
       <c r="R82" t="n">
-        <v>6800626</v>
+        <v>6800571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8947,48 +8922,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128814722</v>
+        <v>128800812</v>
       </c>
       <c r="B83" t="n">
-        <v>79120</v>
+        <v>58086</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456349</v>
+        <v>456691</v>
       </c>
       <c r="R83" t="n">
-        <v>6800436</v>
+        <v>6800368</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9015,9 +8995,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9032,22 +9022,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814695</v>
+        <v>128814677</v>
       </c>
       <c r="B84" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9055,21 +9045,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9079,10 +9069,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456547</v>
+        <v>456747</v>
       </c>
       <c r="R84" t="n">
-        <v>6800403</v>
+        <v>6800569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9141,10 +9131,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128814618</v>
+        <v>128801262</v>
       </c>
       <c r="B85" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9152,21 +9142,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9176,10 +9166,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456450</v>
+        <v>456703</v>
       </c>
       <c r="R85" t="n">
-        <v>6800571</v>
+        <v>6800429</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9209,9 +9199,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9226,12 +9226,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128799696</v>
+        <v>128814705</v>
       </c>
       <c r="B90" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456668</v>
+        <v>456749</v>
       </c>
       <c r="R90" t="n">
-        <v>6800363</v>
+        <v>6800566</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9694,19 +9694,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9721,22 +9711,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814705</v>
+        <v>128814622</v>
       </c>
       <c r="B91" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9744,21 +9734,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9768,10 +9758,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456749</v>
+        <v>456546</v>
       </c>
       <c r="R91" t="n">
-        <v>6800566</v>
+        <v>6800434</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9830,10 +9820,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814622</v>
+        <v>128814732</v>
       </c>
       <c r="B92" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9841,21 +9831,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9865,10 +9855,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456546</v>
+        <v>456571</v>
       </c>
       <c r="R92" t="n">
-        <v>6800434</v>
+        <v>6800296</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9927,10 +9917,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814732</v>
+        <v>128814690</v>
       </c>
       <c r="B93" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9938,21 +9928,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9962,10 +9952,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456571</v>
+        <v>456465</v>
       </c>
       <c r="R93" t="n">
-        <v>6800296</v>
+        <v>6800546</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10024,7 +10014,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814690</v>
+        <v>128814699</v>
       </c>
       <c r="B94" t="n">
         <v>78877</v>
@@ -10059,10 +10049,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456465</v>
+        <v>456496</v>
       </c>
       <c r="R94" t="n">
-        <v>6800546</v>
+        <v>6800549</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10121,7 +10111,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814699</v>
+        <v>128814694</v>
       </c>
       <c r="B95" t="n">
         <v>78877</v>
@@ -10156,10 +10146,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456496</v>
+        <v>456594</v>
       </c>
       <c r="R95" t="n">
-        <v>6800549</v>
+        <v>6800423</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,10 +10208,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814694</v>
+        <v>128804256</v>
       </c>
       <c r="B96" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10229,21 +10219,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10253,10 +10243,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456594</v>
+        <v>456794</v>
       </c>
       <c r="R96" t="n">
-        <v>6800423</v>
+        <v>6800605</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10286,9 +10276,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10303,22 +10303,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128804256</v>
+        <v>128799696</v>
       </c>
       <c r="B97" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10326,21 +10326,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456794</v>
+        <v>456668</v>
       </c>
       <c r="R97" t="n">
-        <v>6800605</v>
+        <v>6800363</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10632,45 +10632,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128814632</v>
+        <v>128814713</v>
       </c>
       <c r="B100" t="n">
-        <v>79710</v>
+        <v>90886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>5685</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456382</v>
+        <v>456692</v>
       </c>
       <c r="R100" t="n">
-        <v>6800427</v>
+        <v>6800391</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10711,6 +10714,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10729,10 +10733,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128804554</v>
+        <v>128814632</v>
       </c>
       <c r="B101" t="n">
-        <v>78878</v>
+        <v>79710</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10740,21 +10744,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10764,10 +10768,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456768</v>
+        <v>456382</v>
       </c>
       <c r="R101" t="n">
-        <v>6800626</v>
+        <v>6800427</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10797,19 +10801,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10824,19 +10818,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814683</v>
+        <v>128804554</v>
       </c>
       <c r="B102" t="n">
         <v>78878</v>
@@ -10865,19 +10859,16 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456644</v>
+        <v>456768</v>
       </c>
       <c r="R102" t="n">
-        <v>6800358</v>
+        <v>6800626</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10907,62 +10898,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814713</v>
+        <v>128814683</v>
       </c>
       <c r="B103" t="n">
-        <v>90886</v>
+        <v>78878</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456692</v>
+        <v>456644</v>
       </c>
       <c r="R103" t="n">
-        <v>6800391</v>
+        <v>6800358</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11558,10 +11558,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128814725</v>
+        <v>128814624</v>
       </c>
       <c r="B109" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11569,34 +11569,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456598</v>
+        <v>456688</v>
       </c>
       <c r="R109" t="n">
-        <v>6800407</v>
+        <v>6800585</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11631,17 +11634,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11660,10 +11659,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814624</v>
+        <v>128814725</v>
       </c>
       <c r="B110" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11671,37 +11670,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456688</v>
+        <v>456598</v>
       </c>
       <c r="R110" t="n">
-        <v>6800585</v>
+        <v>6800407</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11736,13 +11732,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128805558</v>
+        <v>128814634</v>
       </c>
       <c r="B111" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,34 +11772,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456627</v>
+        <v>456405</v>
       </c>
       <c r="R111" t="n">
-        <v>6800521</v>
+        <v>6800457</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11829,19 +11837,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11856,19 +11854,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814731</v>
+        <v>128805558</v>
       </c>
       <c r="B112" t="n">
         <v>79120</v>
@@ -11903,10 +11901,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456580</v>
+        <v>456627</v>
       </c>
       <c r="R112" t="n">
-        <v>6800292</v>
+        <v>6800521</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11936,9 +11934,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11953,22 +11961,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814696</v>
+        <v>128814731</v>
       </c>
       <c r="B113" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11976,21 +11984,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12000,10 +12008,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456559</v>
+        <v>456580</v>
       </c>
       <c r="R113" t="n">
-        <v>6800576</v>
+        <v>6800292</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12062,10 +12070,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128803369</v>
+        <v>128814696</v>
       </c>
       <c r="B114" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12073,21 +12081,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12097,10 +12105,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456688</v>
+        <v>456559</v>
       </c>
       <c r="R114" t="n">
-        <v>6800474</v>
+        <v>6800576</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12130,19 +12138,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12157,22 +12155,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814687</v>
+        <v>128803369</v>
       </c>
       <c r="B115" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12180,21 +12178,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12204,10 +12202,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456556</v>
+        <v>456688</v>
       </c>
       <c r="R115" t="n">
-        <v>6800320</v>
+        <v>6800474</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12237,9 +12235,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12254,12 +12262,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -12363,10 +12371,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814646</v>
+        <v>128814687</v>
       </c>
       <c r="B117" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12374,42 +12382,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456519</v>
+        <v>456556</v>
       </c>
       <c r="R117" t="n">
-        <v>6800414</v>
+        <v>6800320</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12468,10 +12468,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814634</v>
+        <v>128814646</v>
       </c>
       <c r="B118" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12479,16 +12479,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456405</v>
+        <v>456519</v>
       </c>
       <c r="R118" t="n">
-        <v>6800457</v>
+        <v>6800414</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816353</v>
+        <v>128816343</v>
       </c>
       <c r="B127" t="n">
-        <v>78877</v>
+        <v>57716</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,34 +13392,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456522</v>
+        <v>456341</v>
       </c>
       <c r="R127" t="n">
-        <v>6800357</v>
+        <v>6800306</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13478,10 +13486,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816343</v>
+        <v>128816338</v>
       </c>
       <c r="B128" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13489,31 +13497,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13521,10 +13524,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456341</v>
+        <v>456478</v>
       </c>
       <c r="R128" t="n">
-        <v>6800306</v>
+        <v>6800591</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,6 +13568,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13583,10 +13587,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816338</v>
+        <v>128816353</v>
       </c>
       <c r="B129" t="n">
-        <v>79710</v>
+        <v>78877</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13594,37 +13598,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456478</v>
+        <v>456522</v>
       </c>
       <c r="R129" t="n">
-        <v>6800591</v>
+        <v>6800357</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13665,7 +13666,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13979,10 +13979,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128816356</v>
+        <v>128816340</v>
       </c>
       <c r="B133" t="n">
-        <v>78877</v>
+        <v>79710</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13990,34 +13990,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>456672</v>
+        <v>456564</v>
       </c>
       <c r="R133" t="n">
-        <v>6800413</v>
+        <v>6800618</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14058,6 +14061,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14076,10 +14080,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128816340</v>
+        <v>128816356</v>
       </c>
       <c r="B134" t="n">
-        <v>79710</v>
+        <v>78877</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14087,37 +14091,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>456564</v>
+        <v>456672</v>
       </c>
       <c r="R134" t="n">
-        <v>6800618</v>
+        <v>6800413</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14158,7 +14159,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14278,10 +14278,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128816331</v>
+        <v>128816335</v>
       </c>
       <c r="B136" t="n">
-        <v>79152</v>
+        <v>79739</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14289,37 +14289,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>456376</v>
+        <v>456564</v>
       </c>
       <c r="R136" t="n">
-        <v>6800472</v>
+        <v>6800617</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14360,7 +14357,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14379,10 +14375,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128816335</v>
+        <v>128816331</v>
       </c>
       <c r="B137" t="n">
-        <v>79739</v>
+        <v>79152</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14390,34 +14386,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>456564</v>
+        <v>456376</v>
       </c>
       <c r="R137" t="n">
-        <v>6800617</v>
+        <v>6800472</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14458,6 +14457,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15066,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816332</v>
+        <v>128816359</v>
       </c>
       <c r="B144" t="n">
-        <v>79152</v>
+        <v>79120</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15077,37 +15077,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456355</v>
+        <v>456335</v>
       </c>
       <c r="R144" t="n">
-        <v>6800454</v>
+        <v>6800427</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15148,7 +15145,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15167,10 +15163,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816359</v>
+        <v>128816332</v>
       </c>
       <c r="B145" t="n">
-        <v>79120</v>
+        <v>79152</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15178,34 +15174,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456335</v>
+        <v>456355</v>
       </c>
       <c r="R145" t="n">
-        <v>6800427</v>
+        <v>6800454</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15246,6 +15245,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128799069</v>
+        <v>128800923</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456632</v>
+        <v>456692</v>
       </c>
       <c r="R2" t="n">
-        <v>6800431</v>
+        <v>6800405</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,6 +756,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128800923</v>
+        <v>128799069</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456692</v>
+        <v>456632</v>
       </c>
       <c r="R4" t="n">
-        <v>6800405</v>
+        <v>6800431</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,11 +970,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128803579</v>
+        <v>128814658</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456698</v>
+        <v>456645</v>
       </c>
       <c r="R5" t="n">
-        <v>6800503</v>
+        <v>6800444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,24 +1072,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,44 +1089,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128801339</v>
+        <v>128803425</v>
       </c>
       <c r="B6" t="n">
-        <v>79739</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456742</v>
+        <v>456681</v>
       </c>
       <c r="R6" t="n">
-        <v>6800421</v>
+        <v>6800496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128805128</v>
+        <v>128803579</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1250,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456660</v>
+        <v>456698</v>
       </c>
       <c r="R7" t="n">
-        <v>6800603</v>
+        <v>6800503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1289,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128814728</v>
+        <v>128805128</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1357,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456616</v>
+        <v>456660</v>
       </c>
       <c r="R8" t="n">
-        <v>6800533</v>
+        <v>6800603</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,9 +1388,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,22 +1415,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814658</v>
+        <v>128814728</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,42 +1438,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456645</v>
+        <v>456616</v>
       </c>
       <c r="R9" t="n">
-        <v>6800444</v>
+        <v>6800533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814640</v>
+        <v>128801339</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,42 +1535,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456331</v>
+        <v>456742</v>
       </c>
       <c r="R10" t="n">
-        <v>6800312</v>
+        <v>6800421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,9 +1592,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,57 +1619,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128803425</v>
+        <v>128814640</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456681</v>
+        <v>456331</v>
       </c>
       <c r="R11" t="n">
-        <v>6800496</v>
+        <v>6800312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,19 +1707,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814666</v>
+        <v>128814681</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,42 +1747,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456659</v>
+        <v>456761</v>
       </c>
       <c r="R12" t="n">
-        <v>6800402</v>
+        <v>6800515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814681</v>
+        <v>128814666</v>
       </c>
       <c r="B14" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,34 +1951,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456761</v>
+        <v>456659</v>
       </c>
       <c r="R14" t="n">
-        <v>6800515</v>
+        <v>6800402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814744</v>
+        <v>128814654</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,34 +2056,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456737</v>
+        <v>456705</v>
       </c>
       <c r="R15" t="n">
-        <v>6800417</v>
+        <v>6800486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128804638</v>
+        <v>128814744</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,21 +2161,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456748</v>
+        <v>456737</v>
       </c>
       <c r="R16" t="n">
-        <v>6800617</v>
+        <v>6800417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,19 +2218,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,12 +2235,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2560,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128814693</v>
+        <v>128814715</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2595,10 +2593,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456515</v>
+        <v>456589</v>
       </c>
       <c r="R20" t="n">
-        <v>6800380</v>
+        <v>6800303</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128814715</v>
+        <v>128804638</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,21 +2666,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2692,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456589</v>
+        <v>456748</v>
       </c>
       <c r="R21" t="n">
-        <v>6800303</v>
+        <v>6800617</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,9 +2723,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2742,22 +2750,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814654</v>
+        <v>128814693</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,42 +2773,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456705</v>
+        <v>456515</v>
       </c>
       <c r="R22" t="n">
-        <v>6800486</v>
+        <v>6800380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814652</v>
+        <v>128814673</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,42 +2977,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456781</v>
+        <v>456469</v>
       </c>
       <c r="R24" t="n">
-        <v>6800644</v>
+        <v>6800542</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814644</v>
+        <v>128814616</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,42 +3074,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456603</v>
+        <v>456487</v>
       </c>
       <c r="R25" t="n">
-        <v>6800371</v>
+        <v>6800546</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814616</v>
+        <v>128805061</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3171,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456487</v>
+        <v>456690</v>
       </c>
       <c r="R26" t="n">
-        <v>6800546</v>
+        <v>6800603</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,9 +3228,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3261,22 +3255,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814716</v>
+        <v>128814703</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,21 +3278,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3308,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456477</v>
+        <v>456766</v>
       </c>
       <c r="R27" t="n">
-        <v>6800324</v>
+        <v>6800611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3344,11 +3338,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128805061</v>
+        <v>128814716</v>
       </c>
       <c r="B28" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3375,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3399,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456690</v>
+        <v>456477</v>
       </c>
       <c r="R28" t="n">
-        <v>6800603</v>
+        <v>6800324</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,19 +3432,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3470,22 +3454,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814703</v>
+        <v>128814724</v>
       </c>
       <c r="B29" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,21 +3477,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3517,10 +3501,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456766</v>
+        <v>456520</v>
       </c>
       <c r="R29" t="n">
-        <v>6800611</v>
+        <v>6800367</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,10 +3563,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814724</v>
+        <v>128814652</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,34 +3574,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456520</v>
+        <v>456781</v>
       </c>
       <c r="R30" t="n">
-        <v>6800367</v>
+        <v>6800644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3676,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128814673</v>
+        <v>128814644</v>
       </c>
       <c r="B31" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,34 +3679,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456469</v>
+        <v>456603</v>
       </c>
       <c r="R31" t="n">
-        <v>6800542</v>
+        <v>6800371</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814710</v>
+        <v>128814743</v>
       </c>
       <c r="B36" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456770</v>
+        <v>456566</v>
       </c>
       <c r="R36" t="n">
-        <v>6800515</v>
+        <v>6800498</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,6 +4232,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4258,10 +4263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128804553</v>
+        <v>128814727</v>
       </c>
       <c r="B37" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4269,21 +4274,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4293,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456768</v>
+        <v>456600</v>
       </c>
       <c r="R37" t="n">
-        <v>6800626</v>
+        <v>6800519</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,19 +4331,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4353,22 +4348,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814689</v>
+        <v>128804553</v>
       </c>
       <c r="B38" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,21 +4371,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4400,10 +4395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456495</v>
+        <v>456768</v>
       </c>
       <c r="R38" t="n">
-        <v>6800433</v>
+        <v>6800626</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4433,9 +4428,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4450,22 +4455,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814743</v>
+        <v>128814689</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4473,21 +4478,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4497,10 +4502,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456566</v>
+        <v>456495</v>
       </c>
       <c r="R39" t="n">
-        <v>6800498</v>
+        <v>6800433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,11 +4538,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4564,10 +4564,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128814727</v>
+        <v>128814710</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456600</v>
+        <v>456770</v>
       </c>
       <c r="R40" t="n">
-        <v>6800519</v>
+        <v>6800515</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128805036</v>
+        <v>128814739</v>
       </c>
       <c r="B42" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456690</v>
+        <v>456351</v>
       </c>
       <c r="R42" t="n">
-        <v>6800603</v>
+        <v>6800353</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4826,19 +4826,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4853,19 +4843,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814739</v>
+        <v>128814733</v>
       </c>
       <c r="B43" t="n">
         <v>79120</v>
@@ -4900,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456351</v>
+        <v>456547</v>
       </c>
       <c r="R43" t="n">
-        <v>6800353</v>
+        <v>6800300</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4962,7 +4952,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128814733</v>
+        <v>128805352</v>
       </c>
       <c r="B44" t="n">
         <v>79120</v>
@@ -4997,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456547</v>
+        <v>456605</v>
       </c>
       <c r="R44" t="n">
-        <v>6800300</v>
+        <v>6800580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5030,9 +5020,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5047,22 +5047,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128805352</v>
+        <v>128805036</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5070,21 +5070,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456605</v>
+        <v>456690</v>
       </c>
       <c r="R45" t="n">
-        <v>6800580</v>
+        <v>6800603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B46" t="n">
         <v>79739</v>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R46" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B47" t="n">
         <v>79739</v>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R47" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,10 +5380,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128814742</v>
+        <v>128805326</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5391,21 +5391,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456590</v>
+        <v>456636</v>
       </c>
       <c r="R48" t="n">
-        <v>6800535</v>
+        <v>6800557</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,9 +5448,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5465,19 +5475,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128814730</v>
+        <v>128814742</v>
       </c>
       <c r="B49" t="n">
         <v>79120</v>
@@ -5512,10 +5522,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456589</v>
+        <v>456590</v>
       </c>
       <c r="R49" t="n">
-        <v>6800302</v>
+        <v>6800535</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5574,10 +5584,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128805326</v>
+        <v>128814730</v>
       </c>
       <c r="B50" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5585,21 +5595,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5609,10 +5619,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456636</v>
+        <v>456589</v>
       </c>
       <c r="R50" t="n">
-        <v>6800557</v>
+        <v>6800302</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5642,19 +5652,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5669,22 +5669,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128802364</v>
+        <v>128814719</v>
       </c>
       <c r="B51" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,21 +5692,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456718</v>
+        <v>456527</v>
       </c>
       <c r="R51" t="n">
-        <v>6800502</v>
+        <v>6800610</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,19 +5749,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5776,19 +5766,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128799275</v>
+        <v>128814736</v>
       </c>
       <c r="B52" t="n">
         <v>79120</v>
@@ -5823,10 +5813,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456665</v>
+        <v>456569</v>
       </c>
       <c r="R52" t="n">
-        <v>6800399</v>
+        <v>6800599</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5856,24 +5846,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5888,22 +5863,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814612</v>
+        <v>128814718</v>
       </c>
       <c r="B53" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5911,21 +5886,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5935,10 +5910,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456539</v>
+        <v>456559</v>
       </c>
       <c r="R53" t="n">
-        <v>6800496</v>
+        <v>6800586</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,10 +5972,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814719</v>
+        <v>128814612</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6008,21 +5983,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6032,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456527</v>
+        <v>456539</v>
       </c>
       <c r="R54" t="n">
-        <v>6800610</v>
+        <v>6800496</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6094,10 +6069,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814736</v>
+        <v>128814620</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6105,34 +6080,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456569</v>
+        <v>456385</v>
       </c>
       <c r="R55" t="n">
-        <v>6800599</v>
+        <v>6800430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6173,6 +6151,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6191,10 +6170,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814620</v>
+        <v>128814648</v>
       </c>
       <c r="B56" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6202,26 +6181,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6229,10 +6213,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456385</v>
+        <v>456618</v>
       </c>
       <c r="R56" t="n">
-        <v>6800430</v>
+        <v>6800564</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6273,7 +6257,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6292,7 +6275,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814718</v>
+        <v>128799275</v>
       </c>
       <c r="B57" t="n">
         <v>79120</v>
@@ -6327,10 +6310,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456559</v>
+        <v>456665</v>
       </c>
       <c r="R57" t="n">
-        <v>6800586</v>
+        <v>6800399</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6360,9 +6343,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6377,22 +6375,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128814648</v>
+        <v>128802364</v>
       </c>
       <c r="B58" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6400,42 +6398,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456618</v>
+        <v>456718</v>
       </c>
       <c r="R58" t="n">
-        <v>6800564</v>
+        <v>6800502</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6465,9 +6455,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,22 +6482,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128799700</v>
+        <v>128814735</v>
       </c>
       <c r="B59" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456668</v>
+        <v>456477</v>
       </c>
       <c r="R59" t="n">
-        <v>6800363</v>
+        <v>6800413</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,19 +6562,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6589,19 +6579,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814735</v>
+        <v>128814734</v>
       </c>
       <c r="B60" t="n">
         <v>79120</v>
@@ -6636,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456477</v>
+        <v>456472</v>
       </c>
       <c r="R60" t="n">
-        <v>6800413</v>
+        <v>6800343</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6688,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814734</v>
+        <v>128799700</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6699,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6723,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456472</v>
+        <v>456668</v>
       </c>
       <c r="R61" t="n">
-        <v>6800343</v>
+        <v>6800363</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6766,9 +6756,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,12 +6783,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128804576</v>
+        <v>128802369</v>
       </c>
       <c r="B63" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,39 +6903,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456761</v>
+        <v>456718</v>
       </c>
       <c r="R63" t="n">
-        <v>6800606</v>
+        <v>6800502</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7004,7 +6999,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128814660</v>
+        <v>128804576</v>
       </c>
       <c r="B64" t="n">
         <v>57713</v>
@@ -7033,24 +7028,21 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456747</v>
+        <v>456761</v>
       </c>
       <c r="R64" t="n">
-        <v>6800420</v>
+        <v>6800606</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7080,9 +7072,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7097,12 +7099,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7221,10 +7223,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128802369</v>
+        <v>128814721</v>
       </c>
       <c r="B66" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7232,21 +7234,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7256,10 +7258,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456718</v>
+        <v>456414</v>
       </c>
       <c r="R66" t="n">
-        <v>6800502</v>
+        <v>6800442</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7289,19 +7291,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7316,22 +7308,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128814721</v>
+        <v>128814656</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7339,34 +7331,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456414</v>
+        <v>456658</v>
       </c>
       <c r="R67" t="n">
-        <v>6800442</v>
+        <v>6800419</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7425,7 +7425,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128814656</v>
+        <v>128814660</v>
       </c>
       <c r="B68" t="n">
         <v>57713</v>
@@ -7458,7 +7458,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456658</v>
+        <v>456747</v>
       </c>
       <c r="R68" t="n">
-        <v>6800419</v>
+        <v>6800420</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7738,10 +7738,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814691</v>
+        <v>128803330</v>
       </c>
       <c r="B71" t="n">
-        <v>78877</v>
+        <v>79710</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456385</v>
+        <v>456690</v>
       </c>
       <c r="R71" t="n">
-        <v>6800430</v>
+        <v>6800454</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,9 +7806,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7823,12 +7833,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7932,10 +7942,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814707</v>
+        <v>128814714</v>
       </c>
       <c r="B73" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,21 +7953,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7967,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456665</v>
+        <v>456599</v>
       </c>
       <c r="R73" t="n">
-        <v>6800450</v>
+        <v>6800361</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8029,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128814714</v>
+        <v>128814691</v>
       </c>
       <c r="B74" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8040,21 +8050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8064,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456599</v>
+        <v>456385</v>
       </c>
       <c r="R74" t="n">
-        <v>6800361</v>
+        <v>6800430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8126,7 +8136,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128814697</v>
+        <v>128814707</v>
       </c>
       <c r="B75" t="n">
         <v>78877</v>
@@ -8161,10 +8171,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456499</v>
+        <v>456665</v>
       </c>
       <c r="R75" t="n">
-        <v>6800562</v>
+        <v>6800450</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8223,10 +8233,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128803330</v>
+        <v>128814697</v>
       </c>
       <c r="B76" t="n">
-        <v>79710</v>
+        <v>78877</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8234,21 +8244,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8258,10 +8268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456690</v>
+        <v>456499</v>
       </c>
       <c r="R76" t="n">
-        <v>6800454</v>
+        <v>6800562</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8291,19 +8301,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,22 +8318,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128800436</v>
+        <v>128814722</v>
       </c>
       <c r="B77" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456671</v>
+        <v>456349</v>
       </c>
       <c r="R77" t="n">
-        <v>6800350</v>
+        <v>6800436</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8398,19 +8398,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8425,22 +8415,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128814709</v>
+        <v>128800436</v>
       </c>
       <c r="B78" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8448,21 +8438,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8472,10 +8462,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456706</v>
+        <v>456671</v>
       </c>
       <c r="R78" t="n">
-        <v>6800520</v>
+        <v>6800350</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8505,9 +8495,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,19 +8522,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814702</v>
+        <v>128814709</v>
       </c>
       <c r="B79" t="n">
         <v>78877</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456788</v>
+        <v>456706</v>
       </c>
       <c r="R79" t="n">
-        <v>6800626</v>
+        <v>6800520</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814722</v>
+        <v>128814702</v>
       </c>
       <c r="B80" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,21 +8642,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456349</v>
+        <v>456788</v>
       </c>
       <c r="R80" t="n">
-        <v>6800436</v>
+        <v>6800626</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8922,53 +8922,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128800812</v>
+        <v>128814677</v>
       </c>
       <c r="B83" t="n">
-        <v>58086</v>
+        <v>78878</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456691</v>
+        <v>456747</v>
       </c>
       <c r="R83" t="n">
-        <v>6800368</v>
+        <v>6800569</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8995,19 +8990,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9022,19 +9007,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814677</v>
+        <v>128801262</v>
       </c>
       <c r="B84" t="n">
         <v>78878</v>
@@ -9069,10 +9054,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456747</v>
+        <v>456703</v>
       </c>
       <c r="R84" t="n">
-        <v>6800569</v>
+        <v>6800429</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9102,9 +9087,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9119,60 +9114,65 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128801262</v>
+        <v>128800812</v>
       </c>
       <c r="B85" t="n">
-        <v>78878</v>
+        <v>58086</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456703</v>
+        <v>456691</v>
       </c>
       <c r="R85" t="n">
-        <v>6800429</v>
+        <v>6800368</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814723</v>
+        <v>128814630</v>
       </c>
       <c r="B88" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9443,21 +9443,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456351</v>
+        <v>456496</v>
       </c>
       <c r="R88" t="n">
-        <v>6800371</v>
+        <v>6800554</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814630</v>
+        <v>128814723</v>
       </c>
       <c r="B89" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456496</v>
+        <v>456351</v>
       </c>
       <c r="R89" t="n">
-        <v>6800554</v>
+        <v>6800371</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128814705</v>
+        <v>128814732</v>
       </c>
       <c r="B90" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456749</v>
+        <v>456571</v>
       </c>
       <c r="R90" t="n">
-        <v>6800566</v>
+        <v>6800296</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9723,10 +9723,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814622</v>
+        <v>128814705</v>
       </c>
       <c r="B91" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9734,21 +9734,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456546</v>
+        <v>456749</v>
       </c>
       <c r="R91" t="n">
-        <v>6800434</v>
+        <v>6800566</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9820,10 +9820,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814732</v>
+        <v>128814622</v>
       </c>
       <c r="B92" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9831,21 +9831,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456571</v>
+        <v>456546</v>
       </c>
       <c r="R92" t="n">
-        <v>6800296</v>
+        <v>6800434</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10315,10 +10315,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128799696</v>
+        <v>128814664</v>
       </c>
       <c r="B97" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10326,34 +10326,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456668</v>
+        <v>456676</v>
       </c>
       <c r="R97" t="n">
-        <v>6800363</v>
+        <v>6800380</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10383,19 +10391,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10410,22 +10408,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128814664</v>
+        <v>128814637</v>
       </c>
       <c r="B98" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10433,16 +10431,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10465,10 +10463,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456676</v>
+        <v>456352</v>
       </c>
       <c r="R98" t="n">
-        <v>6800380</v>
+        <v>6800325</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10527,10 +10525,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128814637</v>
+        <v>128799696</v>
       </c>
       <c r="B99" t="n">
-        <v>57716</v>
+        <v>78878</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10538,42 +10536,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456352</v>
+        <v>456668</v>
       </c>
       <c r="R99" t="n">
-        <v>6800325</v>
+        <v>6800363</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10603,9 +10593,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10620,12 +10620,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128814632</v>
+        <v>128805054</v>
       </c>
       <c r="B101" t="n">
-        <v>79710</v>
+        <v>79739</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10744,21 +10744,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456382</v>
+        <v>456690</v>
       </c>
       <c r="R101" t="n">
-        <v>6800427</v>
+        <v>6800603</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10801,9 +10801,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10818,22 +10828,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128804554</v>
+        <v>128814698</v>
       </c>
       <c r="B102" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10841,21 +10851,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10865,10 +10875,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456768</v>
+        <v>456491</v>
       </c>
       <c r="R102" t="n">
-        <v>6800626</v>
+        <v>6800537</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10898,19 +10908,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10925,22 +10925,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814683</v>
+        <v>128814624</v>
       </c>
       <c r="B103" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10948,21 +10948,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456644</v>
+        <v>456688</v>
       </c>
       <c r="R103" t="n">
-        <v>6800358</v>
+        <v>6800585</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805054</v>
+        <v>128804050</v>
       </c>
       <c r="B104" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456690</v>
+        <v>456753</v>
       </c>
       <c r="R104" t="n">
-        <v>6800603</v>
+        <v>6800562</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11119,6 +11119,11 @@
       <c r="AB104" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11145,7 +11150,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128804050</v>
+        <v>128805203</v>
       </c>
       <c r="B105" t="n">
         <v>79120</v>
@@ -11180,10 +11185,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456753</v>
+        <v>456650</v>
       </c>
       <c r="R105" t="n">
-        <v>6800562</v>
+        <v>6800594</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11226,11 +11231,6 @@
       <c r="AB105" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11257,7 +11257,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128805203</v>
+        <v>128814737</v>
       </c>
       <c r="B106" t="n">
         <v>79120</v>
@@ -11292,10 +11292,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456650</v>
+        <v>456555</v>
       </c>
       <c r="R106" t="n">
-        <v>6800594</v>
+        <v>6800627</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11325,19 +11325,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11352,22 +11342,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814698</v>
+        <v>128814725</v>
       </c>
       <c r="B107" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11375,21 +11365,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11399,10 +11389,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456491</v>
+        <v>456598</v>
       </c>
       <c r="R107" t="n">
-        <v>6800537</v>
+        <v>6800407</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11435,6 +11425,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11461,10 +11456,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128814737</v>
+        <v>128814632</v>
       </c>
       <c r="B108" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11472,21 +11467,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11496,10 +11491,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456555</v>
+        <v>456382</v>
       </c>
       <c r="R108" t="n">
-        <v>6800627</v>
+        <v>6800427</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11558,10 +11553,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128814624</v>
+        <v>128804554</v>
       </c>
       <c r="B109" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11569,37 +11564,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456688</v>
+        <v>456768</v>
       </c>
       <c r="R109" t="n">
-        <v>6800585</v>
+        <v>6800626</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11629,40 +11621,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814725</v>
+        <v>128814683</v>
       </c>
       <c r="B110" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11670,34 +11671,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456598</v>
+        <v>456644</v>
       </c>
       <c r="R110" t="n">
-        <v>6800407</v>
+        <v>6800358</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11732,17 +11736,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128814634</v>
+        <v>128814696</v>
       </c>
       <c r="B111" t="n">
-        <v>57716</v>
+        <v>78877</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,42 +11772,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456405</v>
+        <v>456559</v>
       </c>
       <c r="R111" t="n">
-        <v>6800457</v>
+        <v>6800576</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11866,10 +11858,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128805558</v>
+        <v>128803369</v>
       </c>
       <c r="B112" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11877,21 +11869,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11901,10 +11893,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456627</v>
+        <v>456688</v>
       </c>
       <c r="R112" t="n">
-        <v>6800521</v>
+        <v>6800474</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11973,10 +11965,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814731</v>
+        <v>128814614</v>
       </c>
       <c r="B113" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11984,21 +11976,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12008,10 +12000,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456580</v>
+        <v>456522</v>
       </c>
       <c r="R113" t="n">
-        <v>6800292</v>
+        <v>6800319</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12070,7 +12062,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814696</v>
+        <v>128814687</v>
       </c>
       <c r="B114" t="n">
         <v>78877</v>
@@ -12105,10 +12097,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456559</v>
+        <v>456556</v>
       </c>
       <c r="R114" t="n">
-        <v>6800576</v>
+        <v>6800320</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12167,10 +12159,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128803369</v>
+        <v>128814679</v>
       </c>
       <c r="B115" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12178,21 +12170,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12202,10 +12194,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456688</v>
+        <v>456753</v>
       </c>
       <c r="R115" t="n">
-        <v>6800474</v>
+        <v>6800533</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12235,19 +12227,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12262,22 +12244,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814614</v>
+        <v>128805558</v>
       </c>
       <c r="B116" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12285,21 +12267,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12309,10 +12291,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456522</v>
+        <v>456627</v>
       </c>
       <c r="R116" t="n">
-        <v>6800319</v>
+        <v>6800521</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12342,9 +12324,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12359,22 +12351,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814687</v>
+        <v>128814731</v>
       </c>
       <c r="B117" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12382,21 +12374,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12406,10 +12398,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456556</v>
+        <v>456580</v>
       </c>
       <c r="R117" t="n">
-        <v>6800320</v>
+        <v>6800292</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12573,10 +12565,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814679</v>
+        <v>128814634</v>
       </c>
       <c r="B119" t="n">
-        <v>78878</v>
+        <v>57716</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12584,34 +12576,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456753</v>
+        <v>456405</v>
       </c>
       <c r="R119" t="n">
-        <v>6800533</v>
+        <v>6800457</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816343</v>
+        <v>128816353</v>
       </c>
       <c r="B127" t="n">
-        <v>57716</v>
+        <v>78877</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,42 +13392,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456341</v>
+        <v>456522</v>
       </c>
       <c r="R127" t="n">
-        <v>6800306</v>
+        <v>6800357</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13486,10 +13478,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816338</v>
+        <v>128816343</v>
       </c>
       <c r="B128" t="n">
-        <v>79710</v>
+        <v>57716</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13497,26 +13489,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13524,10 +13521,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456478</v>
+        <v>456341</v>
       </c>
       <c r="R128" t="n">
-        <v>6800591</v>
+        <v>6800306</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13568,7 +13565,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13587,10 +13583,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816353</v>
+        <v>128816338</v>
       </c>
       <c r="B129" t="n">
-        <v>78877</v>
+        <v>79710</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13598,34 +13594,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456522</v>
+        <v>456478</v>
       </c>
       <c r="R129" t="n">
-        <v>6800357</v>
+        <v>6800591</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13666,6 +13665,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13979,10 +13979,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128816340</v>
+        <v>128816356</v>
       </c>
       <c r="B133" t="n">
-        <v>79710</v>
+        <v>78877</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13990,37 +13990,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>456564</v>
+        <v>456672</v>
       </c>
       <c r="R133" t="n">
-        <v>6800618</v>
+        <v>6800413</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14061,7 +14058,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14080,7 +14076,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128816356</v>
+        <v>128816351</v>
       </c>
       <c r="B134" t="n">
         <v>78877</v>
@@ -14109,16 +14105,19 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>456672</v>
+        <v>456472</v>
       </c>
       <c r="R134" t="n">
-        <v>6800413</v>
+        <v>6800370</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14159,6 +14158,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14177,10 +14177,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128816351</v>
+        <v>128816340</v>
       </c>
       <c r="B135" t="n">
-        <v>78877</v>
+        <v>79710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14188,21 +14188,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14215,10 +14215,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>456472</v>
+        <v>456564</v>
       </c>
       <c r="R135" t="n">
-        <v>6800370</v>
+        <v>6800618</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14278,10 +14278,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128816335</v>
+        <v>128816331</v>
       </c>
       <c r="B136" t="n">
-        <v>79739</v>
+        <v>79152</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14289,34 +14289,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>456564</v>
+        <v>456376</v>
       </c>
       <c r="R136" t="n">
-        <v>6800617</v>
+        <v>6800472</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14357,6 +14360,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14375,10 +14379,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128816331</v>
+        <v>128816335</v>
       </c>
       <c r="B137" t="n">
-        <v>79152</v>
+        <v>79739</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14386,37 +14390,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>456376</v>
+        <v>456564</v>
       </c>
       <c r="R137" t="n">
-        <v>6800472</v>
+        <v>6800617</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14457,7 +14458,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14476,10 +14476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128816352</v>
+        <v>128816348</v>
       </c>
       <c r="B138" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14487,37 +14487,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>456483</v>
+        <v>456703</v>
       </c>
       <c r="R138" t="n">
-        <v>6800432</v>
+        <v>6800475</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14558,7 +14555,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14577,10 +14573,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128816348</v>
+        <v>128816352</v>
       </c>
       <c r="B139" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14588,34 +14584,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456703</v>
+        <v>456483</v>
       </c>
       <c r="R139" t="n">
-        <v>6800475</v>
+        <v>6800432</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14656,6 +14655,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15163,10 +15163,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816332</v>
+        <v>128816345</v>
       </c>
       <c r="B145" t="n">
-        <v>79152</v>
+        <v>57713</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15174,26 +15174,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15201,10 +15206,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456355</v>
+        <v>456606</v>
       </c>
       <c r="R145" t="n">
-        <v>6800454</v>
+        <v>6800517</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15245,7 +15250,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15264,10 +15268,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816345</v>
+        <v>128816332</v>
       </c>
       <c r="B146" t="n">
-        <v>57713</v>
+        <v>79152</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15275,31 +15279,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15307,10 +15306,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456606</v>
+        <v>456355</v>
       </c>
       <c r="R146" t="n">
-        <v>6800517</v>
+        <v>6800454</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15351,6 +15350,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15369,10 +15369,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128816346</v>
+        <v>128816333</v>
       </c>
       <c r="B147" t="n">
-        <v>78878</v>
+        <v>79152</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15380,37 +15380,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>456521</v>
+        <v>456756</v>
       </c>
       <c r="R147" t="n">
-        <v>6800343</v>
+        <v>6800522</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15451,7 +15448,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15470,10 +15466,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128816333</v>
+        <v>128816346</v>
       </c>
       <c r="B148" t="n">
-        <v>79152</v>
+        <v>78878</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15481,34 +15477,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>456756</v>
+        <v>456521</v>
       </c>
       <c r="R148" t="n">
-        <v>6800522</v>
+        <v>6800343</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15549,6 +15548,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -15668,10 +15668,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128816337</v>
+        <v>128816360</v>
       </c>
       <c r="B150" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15679,21 +15679,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>456758</v>
+        <v>456583</v>
       </c>
       <c r="R150" t="n">
-        <v>6800574</v>
+        <v>6800417</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15765,10 +15765,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128816360</v>
+        <v>128816337</v>
       </c>
       <c r="B151" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15776,21 +15776,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15800,10 +15800,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>456583</v>
+        <v>456758</v>
       </c>
       <c r="R151" t="n">
-        <v>6800417</v>
+        <v>6800574</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128800923</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128814701</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128799069</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128814658</v>
+        <v>128803579</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456645</v>
+        <v>456698</v>
       </c>
       <c r="R5" t="n">
-        <v>6800444</v>
+        <v>6800503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,9 +1064,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,44 +1096,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128803425</v>
+        <v>128814728</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456681</v>
+        <v>456616</v>
       </c>
       <c r="R6" t="n">
-        <v>6800496</v>
+        <v>6800533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,19 +1176,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128803579</v>
+        <v>128801339</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456698</v>
+        <v>456742</v>
       </c>
       <c r="R7" t="n">
-        <v>6800503</v>
+        <v>6800421</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,11 +1286,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,7 +1315,7 @@
         <v>128805128</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814728</v>
+        <v>128814640</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,34 +1430,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456616</v>
+        <v>456331</v>
       </c>
       <c r="R9" t="n">
-        <v>6800533</v>
+        <v>6800312</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128801339</v>
+        <v>128814658</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,34 +1535,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456742</v>
+        <v>456645</v>
       </c>
       <c r="R10" t="n">
-        <v>6800421</v>
+        <v>6800444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,19 +1600,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,65 +1617,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128814640</v>
+        <v>128803425</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456331</v>
+        <v>456681</v>
       </c>
       <c r="R11" t="n">
-        <v>6800312</v>
+        <v>6800496</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,9 +1697,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814681</v>
+        <v>128804672</v>
       </c>
       <c r="B12" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456761</v>
+        <v>456733</v>
       </c>
       <c r="R12" t="n">
-        <v>6800515</v>
+        <v>6800618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,9 +1804,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,22 +1831,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128804672</v>
+        <v>128814666</v>
       </c>
       <c r="B13" t="n">
-        <v>79739</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,34 +1854,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456733</v>
+        <v>456659</v>
       </c>
       <c r="R13" t="n">
-        <v>6800618</v>
+        <v>6800402</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,19 +1919,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,22 +1936,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814666</v>
+        <v>128814681</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>78882</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,42 +1959,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456659</v>
+        <v>456761</v>
       </c>
       <c r="R14" t="n">
-        <v>6800402</v>
+        <v>6800515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814654</v>
+        <v>128814715</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,42 +2056,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456705</v>
+        <v>456589</v>
       </c>
       <c r="R15" t="n">
-        <v>6800486</v>
+        <v>6800303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2145,7 @@
         <v>128814744</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814729</v>
+        <v>128805619</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456606</v>
+        <v>456600</v>
       </c>
       <c r="R17" t="n">
-        <v>6800334</v>
+        <v>6800539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,9 +2307,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,22 +2334,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128805619</v>
+        <v>128805376</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456600</v>
+        <v>456589</v>
       </c>
       <c r="R18" t="n">
-        <v>6800539</v>
+        <v>6800567</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,10 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805376</v>
+        <v>128814729</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2486,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456589</v>
+        <v>456606</v>
       </c>
       <c r="R19" t="n">
-        <v>6800567</v>
+        <v>6800334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,19 +2521,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,22 +2538,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128814715</v>
+        <v>128804638</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2561,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456589</v>
+        <v>456748</v>
       </c>
       <c r="R20" t="n">
-        <v>6800303</v>
+        <v>6800617</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,9 +2618,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,22 +2645,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128804638</v>
+        <v>128814693</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,21 +2668,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2690,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456748</v>
+        <v>456515</v>
       </c>
       <c r="R21" t="n">
-        <v>6800617</v>
+        <v>6800380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,19 +2725,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,22 +2742,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814693</v>
+        <v>128814654</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,34 +2765,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456515</v>
+        <v>456705</v>
       </c>
       <c r="R22" t="n">
-        <v>6800380</v>
+        <v>6800486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,7 +2862,7 @@
         <v>128804261</v>
       </c>
       <c r="B23" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814673</v>
+        <v>128814652</v>
       </c>
       <c r="B24" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,34 +2977,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456469</v>
+        <v>456781</v>
       </c>
       <c r="R24" t="n">
-        <v>6800542</v>
+        <v>6800644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814616</v>
+        <v>128814644</v>
       </c>
       <c r="B25" t="n">
-        <v>79739</v>
+        <v>57717</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,34 +3082,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456487</v>
+        <v>456603</v>
       </c>
       <c r="R25" t="n">
-        <v>6800546</v>
+        <v>6800371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3160,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128805061</v>
+        <v>128814673</v>
       </c>
       <c r="B26" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,21 +3187,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3195,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456690</v>
+        <v>456469</v>
       </c>
       <c r="R26" t="n">
-        <v>6800603</v>
+        <v>6800542</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3228,19 +3244,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3255,12 +3261,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3270,7 +3276,7 @@
         <v>128814703</v>
       </c>
       <c r="B27" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814716</v>
+        <v>128814616</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456477</v>
+        <v>456487</v>
       </c>
       <c r="R28" t="n">
-        <v>6800324</v>
+        <v>6800546</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,11 +3441,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3466,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814724</v>
+        <v>128814716</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3501,10 +3502,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456520</v>
+        <v>456477</v>
       </c>
       <c r="R29" t="n">
-        <v>6800367</v>
+        <v>6800324</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,6 +3538,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3563,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814652</v>
+        <v>128814724</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3574,42 +3580,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456781</v>
+        <v>456520</v>
       </c>
       <c r="R30" t="n">
-        <v>6800644</v>
+        <v>6800367</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,10 +3666,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128814644</v>
+        <v>128805061</v>
       </c>
       <c r="B31" t="n">
-        <v>57713</v>
+        <v>78881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3679,42 +3677,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456603</v>
+        <v>456690</v>
       </c>
       <c r="R31" t="n">
-        <v>6800371</v>
+        <v>6800603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,9 +3734,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3761,22 +3761,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814692</v>
+        <v>128814626</v>
       </c>
       <c r="B32" t="n">
-        <v>78877</v>
+        <v>79743</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456354</v>
+        <v>456763</v>
       </c>
       <c r="R32" t="n">
-        <v>6800374</v>
+        <v>6800617</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814626</v>
+        <v>128814692</v>
       </c>
       <c r="B33" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456763</v>
+        <v>456354</v>
       </c>
       <c r="R33" t="n">
-        <v>6800617</v>
+        <v>6800374</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3970,7 +3970,7 @@
         <v>128814708</v>
       </c>
       <c r="B34" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>128814720</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814743</v>
+        <v>128814727</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456566</v>
+        <v>456600</v>
       </c>
       <c r="R36" t="n">
-        <v>6800498</v>
+        <v>6800519</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,11 +4232,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4263,10 +4258,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814727</v>
+        <v>128804553</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,21 +4269,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4293,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456600</v>
+        <v>456768</v>
       </c>
       <c r="R37" t="n">
-        <v>6800519</v>
+        <v>6800626</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,9 +4326,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4348,22 +4353,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128804553</v>
+        <v>128814711</v>
       </c>
       <c r="B38" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,21 +4376,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4395,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456768</v>
+        <v>456642</v>
       </c>
       <c r="R38" t="n">
-        <v>6800626</v>
+        <v>6800358</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4428,19 +4433,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,22 +4450,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814689</v>
+        <v>128814710</v>
       </c>
       <c r="B39" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4502,10 +4497,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456495</v>
+        <v>456770</v>
       </c>
       <c r="R39" t="n">
-        <v>6800433</v>
+        <v>6800515</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4564,10 +4559,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128814710</v>
+        <v>128814689</v>
       </c>
       <c r="B40" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4599,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456770</v>
+        <v>456495</v>
       </c>
       <c r="R40" t="n">
-        <v>6800515</v>
+        <v>6800433</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128814711</v>
+        <v>128814743</v>
       </c>
       <c r="B41" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4672,21 +4667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4696,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456642</v>
+        <v>456566</v>
       </c>
       <c r="R41" t="n">
-        <v>6800358</v>
+        <v>6800498</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4732,6 +4727,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128814739</v>
+        <v>128814733</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456351</v>
+        <v>456547</v>
       </c>
       <c r="R42" t="n">
-        <v>6800353</v>
+        <v>6800300</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814733</v>
+        <v>128814739</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456547</v>
+        <v>456351</v>
       </c>
       <c r="R43" t="n">
-        <v>6800300</v>
+        <v>6800353</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
         <v>128805352</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>128805036</v>
       </c>
       <c r="B45" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B46" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R46" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B47" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R47" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,10 +5380,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128805326</v>
+        <v>128814730</v>
       </c>
       <c r="B48" t="n">
-        <v>79710</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5391,21 +5391,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456636</v>
+        <v>456589</v>
       </c>
       <c r="R48" t="n">
-        <v>6800557</v>
+        <v>6800302</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,19 +5448,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5475,12 +5465,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5490,7 +5480,7 @@
         <v>128814742</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5584,10 +5574,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128814730</v>
+        <v>128805326</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79714</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5595,21 +5585,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5619,10 +5609,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456589</v>
+        <v>456636</v>
       </c>
       <c r="R50" t="n">
-        <v>6800302</v>
+        <v>6800557</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5652,9 +5642,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5669,22 +5669,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128814719</v>
+        <v>128799275</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456527</v>
+        <v>456665</v>
       </c>
       <c r="R51" t="n">
-        <v>6800610</v>
+        <v>6800399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,9 +5749,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5766,22 +5781,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814736</v>
+        <v>128814612</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5789,21 +5804,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5813,10 +5828,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456569</v>
+        <v>456539</v>
       </c>
       <c r="R52" t="n">
-        <v>6800599</v>
+        <v>6800496</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5875,10 +5890,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814718</v>
+        <v>128814620</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5886,34 +5901,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456559</v>
+        <v>456385</v>
       </c>
       <c r="R53" t="n">
-        <v>6800586</v>
+        <v>6800430</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5954,6 +5972,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5972,10 +5991,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814612</v>
+        <v>128814719</v>
       </c>
       <c r="B54" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5983,21 +6002,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6007,10 +6026,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456539</v>
+        <v>456527</v>
       </c>
       <c r="R54" t="n">
-        <v>6800496</v>
+        <v>6800610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6069,10 +6088,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814620</v>
+        <v>128814736</v>
       </c>
       <c r="B55" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6080,37 +6099,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456385</v>
+        <v>456569</v>
       </c>
       <c r="R55" t="n">
-        <v>6800430</v>
+        <v>6800599</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6151,7 +6167,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6170,10 +6185,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814648</v>
+        <v>128814718</v>
       </c>
       <c r="B56" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6181,42 +6196,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456618</v>
+        <v>456559</v>
       </c>
       <c r="R56" t="n">
-        <v>6800564</v>
+        <v>6800586</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6275,10 +6282,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128799275</v>
+        <v>128814648</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6286,34 +6293,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456665</v>
+        <v>456618</v>
       </c>
       <c r="R57" t="n">
-        <v>6800399</v>
+        <v>6800564</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6343,24 +6358,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6375,12 +6375,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6390,7 +6390,7 @@
         <v>128802364</v>
       </c>
       <c r="B58" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128814735</v>
+        <v>128814628</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79714</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456477</v>
+        <v>456549</v>
       </c>
       <c r="R59" t="n">
-        <v>6800413</v>
+        <v>6800517</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6591,10 +6591,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814734</v>
+        <v>128799700</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79714</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6602,21 +6602,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456472</v>
+        <v>456668</v>
       </c>
       <c r="R60" t="n">
-        <v>6800343</v>
+        <v>6800363</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6659,9 +6659,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6676,22 +6686,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128799700</v>
+        <v>128814735</v>
       </c>
       <c r="B61" t="n">
-        <v>79710</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6699,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6723,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456668</v>
+        <v>456477</v>
       </c>
       <c r="R61" t="n">
-        <v>6800363</v>
+        <v>6800413</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6756,19 +6766,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,22 +6783,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128814628</v>
+        <v>128814734</v>
       </c>
       <c r="B62" t="n">
-        <v>79710</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6806,21 +6806,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456549</v>
+        <v>456472</v>
       </c>
       <c r="R62" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128802369</v>
+        <v>128814721</v>
       </c>
       <c r="B63" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456718</v>
+        <v>456414</v>
       </c>
       <c r="R63" t="n">
-        <v>6800502</v>
+        <v>6800442</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,19 +6960,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,22 +6977,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128804576</v>
+        <v>128802369</v>
       </c>
       <c r="B64" t="n">
-        <v>57713</v>
+        <v>79743</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7010,39 +7000,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456761</v>
+        <v>456718</v>
       </c>
       <c r="R64" t="n">
-        <v>6800606</v>
+        <v>6800502</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7114,7 +7099,7 @@
         <v>128802133</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7223,10 +7208,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128814721</v>
+        <v>128804576</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7234,34 +7219,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456414</v>
+        <v>456761</v>
       </c>
       <c r="R66" t="n">
-        <v>6800442</v>
+        <v>6800606</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7291,9 +7281,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7308,12 +7308,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
         <v>128814656</v>
       </c>
       <c r="B67" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>128814660</v>
       </c>
       <c r="B68" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>128814675</v>
       </c>
       <c r="B69" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128799394</v>
+        <v>128814707</v>
       </c>
       <c r="B70" t="n">
-        <v>91454</v>
+        <v>78881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456679</v>
+        <v>456665</v>
       </c>
       <c r="R70" t="n">
-        <v>6800380</v>
+        <v>6800450</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7699,19 +7699,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7726,22 +7716,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128803330</v>
+        <v>128814691</v>
       </c>
       <c r="B71" t="n">
-        <v>79710</v>
+        <v>78881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456690</v>
+        <v>456385</v>
       </c>
       <c r="R71" t="n">
-        <v>6800454</v>
+        <v>6800430</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,19 +7796,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7833,22 +7813,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128814717</v>
+        <v>128814697</v>
       </c>
       <c r="B72" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7856,21 +7836,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7880,10 +7860,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>456529</v>
+        <v>456499</v>
       </c>
       <c r="R72" t="n">
-        <v>6800501</v>
+        <v>6800562</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7942,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814714</v>
+        <v>128814717</v>
       </c>
       <c r="B73" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7977,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456599</v>
+        <v>456529</v>
       </c>
       <c r="R73" t="n">
-        <v>6800361</v>
+        <v>6800501</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128814691</v>
+        <v>128814714</v>
       </c>
       <c r="B74" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8050,21 +8030,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8074,10 +8054,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456385</v>
+        <v>456599</v>
       </c>
       <c r="R74" t="n">
-        <v>6800430</v>
+        <v>6800361</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8136,10 +8116,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128814707</v>
+        <v>128803330</v>
       </c>
       <c r="B75" t="n">
-        <v>78877</v>
+        <v>79714</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8147,21 +8127,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8171,10 +8151,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456665</v>
+        <v>456690</v>
       </c>
       <c r="R75" t="n">
-        <v>6800450</v>
+        <v>6800454</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8204,9 +8184,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8221,22 +8211,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128814697</v>
+        <v>128799394</v>
       </c>
       <c r="B76" t="n">
-        <v>78877</v>
+        <v>91458</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8244,21 +8234,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8268,10 +8258,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456499</v>
+        <v>456679</v>
       </c>
       <c r="R76" t="n">
-        <v>6800562</v>
+        <v>6800380</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,9 +8291,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,22 +8318,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128814722</v>
+        <v>128814677</v>
       </c>
       <c r="B77" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456349</v>
+        <v>456747</v>
       </c>
       <c r="R77" t="n">
-        <v>6800436</v>
+        <v>6800569</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128800436</v>
+        <v>128801262</v>
       </c>
       <c r="B78" t="n">
-        <v>79739</v>
+        <v>78882</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8438,21 +8438,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456671</v>
+        <v>456703</v>
       </c>
       <c r="R78" t="n">
-        <v>6800350</v>
+        <v>6800429</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814709</v>
+        <v>128814722</v>
       </c>
       <c r="B79" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456706</v>
+        <v>456349</v>
       </c>
       <c r="R79" t="n">
-        <v>6800520</v>
+        <v>6800436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8634,7 +8634,7 @@
         <v>128814702</v>
       </c>
       <c r="B80" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>128814695</v>
       </c>
       <c r="B81" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8825,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814618</v>
+        <v>128814709</v>
       </c>
       <c r="B82" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456450</v>
+        <v>456706</v>
       </c>
       <c r="R82" t="n">
-        <v>6800571</v>
+        <v>6800520</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8922,10 +8922,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128814677</v>
+        <v>128814618</v>
       </c>
       <c r="B83" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8933,21 +8933,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456747</v>
+        <v>456450</v>
       </c>
       <c r="R83" t="n">
-        <v>6800569</v>
+        <v>6800571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9019,10 +9019,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128801262</v>
+        <v>128800436</v>
       </c>
       <c r="B84" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9030,21 +9030,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456703</v>
+        <v>456671</v>
       </c>
       <c r="R84" t="n">
-        <v>6800429</v>
+        <v>6800350</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9129,7 +9129,7 @@
         <v>128800812</v>
       </c>
       <c r="B85" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>128814741</v>
       </c>
       <c r="B86" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814726</v>
+        <v>128814723</v>
       </c>
       <c r="B87" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456524</v>
+        <v>456351</v>
       </c>
       <c r="R87" t="n">
-        <v>6800431</v>
+        <v>6800371</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814630</v>
+        <v>128814726</v>
       </c>
       <c r="B88" t="n">
-        <v>79710</v>
+        <v>79124</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9443,21 +9443,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456496</v>
+        <v>456524</v>
       </c>
       <c r="R88" t="n">
-        <v>6800554</v>
+        <v>6800431</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814723</v>
+        <v>128814630</v>
       </c>
       <c r="B89" t="n">
-        <v>79120</v>
+        <v>79714</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456351</v>
+        <v>456496</v>
       </c>
       <c r="R89" t="n">
-        <v>6800371</v>
+        <v>6800554</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128814732</v>
+        <v>128814664</v>
       </c>
       <c r="B90" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,34 +9637,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456571</v>
+        <v>456676</v>
       </c>
       <c r="R90" t="n">
-        <v>6800296</v>
+        <v>6800380</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9723,10 +9731,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814705</v>
+        <v>128814694</v>
       </c>
       <c r="B91" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9758,10 +9766,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456749</v>
+        <v>456594</v>
       </c>
       <c r="R91" t="n">
-        <v>6800566</v>
+        <v>6800423</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9820,10 +9828,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814622</v>
+        <v>128814690</v>
       </c>
       <c r="B92" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9831,21 +9839,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9855,10 +9863,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456546</v>
+        <v>456465</v>
       </c>
       <c r="R92" t="n">
-        <v>6800434</v>
+        <v>6800546</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9917,10 +9925,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814690</v>
+        <v>128814732</v>
       </c>
       <c r="B93" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9928,21 +9936,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9952,10 +9960,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456465</v>
+        <v>456571</v>
       </c>
       <c r="R93" t="n">
-        <v>6800546</v>
+        <v>6800296</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10017,7 +10025,7 @@
         <v>128814699</v>
       </c>
       <c r="B94" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10111,10 +10119,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814694</v>
+        <v>128814705</v>
       </c>
       <c r="B95" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10146,10 +10154,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456594</v>
+        <v>456749</v>
       </c>
       <c r="R95" t="n">
-        <v>6800423</v>
+        <v>6800566</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10208,10 +10216,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128804256</v>
+        <v>128814622</v>
       </c>
       <c r="B96" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10243,10 +10251,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456794</v>
+        <v>456546</v>
       </c>
       <c r="R96" t="n">
-        <v>6800605</v>
+        <v>6800434</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10276,19 +10284,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10303,22 +10301,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814664</v>
+        <v>128804256</v>
       </c>
       <c r="B97" t="n">
-        <v>57713</v>
+        <v>79743</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10326,42 +10324,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456676</v>
+        <v>456794</v>
       </c>
       <c r="R97" t="n">
-        <v>6800380</v>
+        <v>6800605</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10391,9 +10381,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10408,12 +10408,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10423,7 +10423,7 @@
         <v>128814637</v>
       </c>
       <c r="B98" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>128799696</v>
       </c>
       <c r="B99" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>128814713</v>
       </c>
       <c r="B100" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805054</v>
+        <v>128814624</v>
       </c>
       <c r="B101" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10762,16 +10762,19 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456690</v>
+        <v>456688</v>
       </c>
       <c r="R101" t="n">
-        <v>6800603</v>
+        <v>6800585</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10801,49 +10804,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814698</v>
+        <v>128805203</v>
       </c>
       <c r="B102" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10851,21 +10845,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10875,10 +10869,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456491</v>
+        <v>456650</v>
       </c>
       <c r="R102" t="n">
-        <v>6800537</v>
+        <v>6800594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10908,9 +10902,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10925,22 +10929,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814624</v>
+        <v>128814737</v>
       </c>
       <c r="B103" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10948,37 +10952,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456688</v>
+        <v>456555</v>
       </c>
       <c r="R103" t="n">
-        <v>6800585</v>
+        <v>6800627</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11019,7 +11020,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128804050</v>
+        <v>128814698</v>
       </c>
       <c r="B104" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456753</v>
+        <v>456491</v>
       </c>
       <c r="R104" t="n">
-        <v>6800562</v>
+        <v>6800537</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11106,24 +11106,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11138,22 +11123,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128805203</v>
+        <v>128805054</v>
       </c>
       <c r="B105" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11161,21 +11146,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11185,10 +11170,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456650</v>
+        <v>456690</v>
       </c>
       <c r="R105" t="n">
-        <v>6800594</v>
+        <v>6800603</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11257,10 +11242,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814737</v>
+        <v>128804050</v>
       </c>
       <c r="B106" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11292,10 +11277,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456555</v>
+        <v>456753</v>
       </c>
       <c r="R106" t="n">
-        <v>6800627</v>
+        <v>6800562</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11325,9 +11310,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11342,12 +11342,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11357,7 +11357,7 @@
         <v>128814725</v>
       </c>
       <c r="B107" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>128814632</v>
       </c>
       <c r="B108" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>128804554</v>
       </c>
       <c r="B109" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>128814683</v>
       </c>
       <c r="B110" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128814696</v>
+        <v>128814646</v>
       </c>
       <c r="B111" t="n">
-        <v>78877</v>
+        <v>57717</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,34 +11772,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456559</v>
+        <v>456519</v>
       </c>
       <c r="R111" t="n">
-        <v>6800576</v>
+        <v>6800414</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11858,10 +11866,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128803369</v>
+        <v>128814679</v>
       </c>
       <c r="B112" t="n">
-        <v>79739</v>
+        <v>78882</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11869,21 +11877,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11893,10 +11901,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456688</v>
+        <v>456753</v>
       </c>
       <c r="R112" t="n">
-        <v>6800474</v>
+        <v>6800533</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11926,19 +11934,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11953,22 +11951,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814614</v>
+        <v>128803369</v>
       </c>
       <c r="B113" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12000,10 +11998,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456522</v>
+        <v>456688</v>
       </c>
       <c r="R113" t="n">
-        <v>6800319</v>
+        <v>6800474</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12033,9 +12031,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12050,12 +12058,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12065,7 +12073,7 @@
         <v>128814687</v>
       </c>
       <c r="B114" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12159,10 +12167,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814679</v>
+        <v>128805558</v>
       </c>
       <c r="B115" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12170,21 +12178,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12194,10 +12202,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456753</v>
+        <v>456627</v>
       </c>
       <c r="R115" t="n">
-        <v>6800533</v>
+        <v>6800521</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12227,9 +12235,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12244,22 +12262,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128805558</v>
+        <v>128814614</v>
       </c>
       <c r="B116" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12267,21 +12285,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12291,10 +12309,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456627</v>
+        <v>456522</v>
       </c>
       <c r="R116" t="n">
-        <v>6800521</v>
+        <v>6800319</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12324,19 +12342,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12351,12 +12359,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12366,7 +12374,7 @@
         <v>128814731</v>
       </c>
       <c r="B117" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12460,10 +12468,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814646</v>
+        <v>128814696</v>
       </c>
       <c r="B118" t="n">
-        <v>57713</v>
+        <v>78881</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12471,42 +12479,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456519</v>
+        <v>456559</v>
       </c>
       <c r="R118" t="n">
-        <v>6800414</v>
+        <v>6800576</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12568,7 +12568,7 @@
         <v>128814634</v>
       </c>
       <c r="B119" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>128805585</v>
       </c>
       <c r="B120" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>128814706</v>
       </c>
       <c r="B121" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>128804496</v>
       </c>
       <c r="B122" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>128814700</v>
       </c>
       <c r="B123" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>128816339</v>
       </c>
       <c r="B124" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>128816342</v>
       </c>
       <c r="B125" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>128816336</v>
       </c>
       <c r="B126" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>128816353</v>
       </c>
       <c r="B127" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>128816343</v>
       </c>
       <c r="B128" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>128816338</v>
       </c>
       <c r="B129" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>128816347</v>
       </c>
       <c r="B130" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>128816349</v>
       </c>
       <c r="B131" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>128816354</v>
       </c>
       <c r="B132" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>128816356</v>
       </c>
       <c r="B133" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>128816351</v>
       </c>
       <c r="B134" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>128816340</v>
       </c>
       <c r="B135" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>128816331</v>
       </c>
       <c r="B136" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>128816335</v>
       </c>
       <c r="B137" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14476,10 +14476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128816348</v>
+        <v>128816352</v>
       </c>
       <c r="B138" t="n">
-        <v>78878</v>
+        <v>78881</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14487,34 +14487,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>456703</v>
+        <v>456483</v>
       </c>
       <c r="R138" t="n">
-        <v>6800475</v>
+        <v>6800432</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14555,6 +14558,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14573,10 +14577,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128816352</v>
+        <v>128816348</v>
       </c>
       <c r="B139" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14584,37 +14588,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456483</v>
+        <v>456703</v>
       </c>
       <c r="R139" t="n">
-        <v>6800432</v>
+        <v>6800475</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14655,7 +14656,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14677,7 +14677,7 @@
         <v>128816350</v>
       </c>
       <c r="B140" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>128816334</v>
       </c>
       <c r="B141" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>128816358</v>
       </c>
       <c r="B142" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>128816361</v>
       </c>
       <c r="B143" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15066,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816359</v>
+        <v>128816332</v>
       </c>
       <c r="B144" t="n">
-        <v>79120</v>
+        <v>79156</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15077,34 +15077,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456335</v>
+        <v>456355</v>
       </c>
       <c r="R144" t="n">
-        <v>6800427</v>
+        <v>6800454</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15145,6 +15148,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15166,7 +15170,7 @@
         <v>128816345</v>
       </c>
       <c r="B145" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15268,10 +15272,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816332</v>
+        <v>128816359</v>
       </c>
       <c r="B146" t="n">
-        <v>79152</v>
+        <v>79124</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15279,37 +15283,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456355</v>
+        <v>456335</v>
       </c>
       <c r="R146" t="n">
-        <v>6800454</v>
+        <v>6800427</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15350,7 +15351,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15372,7 +15372,7 @@
         <v>128816333</v>
       </c>
       <c r="B147" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>128816346</v>
       </c>
       <c r="B148" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>128816341</v>
       </c>
       <c r="B149" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>128816360</v>
       </c>
       <c r="B150" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>128816337</v>
       </c>
       <c r="B151" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128800923</v>
+        <v>128814701</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456692</v>
+        <v>456547</v>
       </c>
       <c r="R2" t="n">
-        <v>6800405</v>
+        <v>6800436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,24 +743,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128814701</v>
+        <v>128800923</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456547</v>
+        <v>456692</v>
       </c>
       <c r="R3" t="n">
-        <v>6800436</v>
+        <v>6800405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,9 +840,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128803579</v>
+        <v>128814658</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456698</v>
+        <v>456645</v>
       </c>
       <c r="R5" t="n">
-        <v>6800503</v>
+        <v>6800444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,24 +1072,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128814728</v>
+        <v>128814640</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1112,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456616</v>
+        <v>456331</v>
       </c>
       <c r="R6" t="n">
-        <v>6800533</v>
+        <v>6800312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128801339</v>
+        <v>128803579</v>
       </c>
       <c r="B7" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456742</v>
+        <v>456698</v>
       </c>
       <c r="R7" t="n">
-        <v>6800421</v>
+        <v>6800503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1287,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128805128</v>
+        <v>128801339</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456660</v>
+        <v>456742</v>
       </c>
       <c r="R8" t="n">
-        <v>6800603</v>
+        <v>6800421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814640</v>
+        <v>128805128</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,42 +1436,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456331</v>
+        <v>456660</v>
       </c>
       <c r="R9" t="n">
-        <v>6800312</v>
+        <v>6800603</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,9 +1493,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,22 +1520,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814658</v>
+        <v>128814728</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,42 +1543,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456645</v>
+        <v>456616</v>
       </c>
       <c r="R10" t="n">
-        <v>6800444</v>
+        <v>6800533</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128804672</v>
+        <v>128814681</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456733</v>
+        <v>456761</v>
       </c>
       <c r="R12" t="n">
-        <v>6800618</v>
+        <v>6800515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,19 +1804,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,22 +1821,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814666</v>
+        <v>128804672</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>79743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,42 +1844,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456659</v>
+        <v>456733</v>
       </c>
       <c r="R13" t="n">
-        <v>6800402</v>
+        <v>6800618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,9 +1901,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,22 +1928,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814681</v>
+        <v>128814666</v>
       </c>
       <c r="B14" t="n">
-        <v>78882</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,34 +1951,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456761</v>
+        <v>456659</v>
       </c>
       <c r="R14" t="n">
-        <v>6800515</v>
+        <v>6800402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814715</v>
+        <v>128814654</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,34 +2056,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456589</v>
+        <v>456705</v>
       </c>
       <c r="R15" t="n">
-        <v>6800303</v>
+        <v>6800486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128805619</v>
+        <v>128804638</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2258,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456600</v>
+        <v>456748</v>
       </c>
       <c r="R17" t="n">
-        <v>6800539</v>
+        <v>6800617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,7 +2354,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128805376</v>
+        <v>128814729</v>
       </c>
       <c r="B18" t="n">
         <v>79124</v>
@@ -2381,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456589</v>
+        <v>456606</v>
       </c>
       <c r="R18" t="n">
-        <v>6800567</v>
+        <v>6800334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,19 +2422,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,19 +2439,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128814729</v>
+        <v>128805619</v>
       </c>
       <c r="B19" t="n">
         <v>79124</v>
@@ -2488,10 +2486,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456606</v>
+        <v>456600</v>
       </c>
       <c r="R19" t="n">
-        <v>6800334</v>
+        <v>6800539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,9 +2519,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2538,22 +2546,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128804638</v>
+        <v>128805376</v>
       </c>
       <c r="B20" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2593,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456748</v>
+        <v>456589</v>
       </c>
       <c r="R20" t="n">
-        <v>6800617</v>
+        <v>6800567</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2754,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814654</v>
+        <v>128814715</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,42 +2773,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456705</v>
+        <v>456589</v>
       </c>
       <c r="R22" t="n">
-        <v>6800486</v>
+        <v>6800303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814652</v>
+        <v>128805061</v>
       </c>
       <c r="B24" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,42 +2977,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456781</v>
+        <v>456690</v>
       </c>
       <c r="R24" t="n">
-        <v>6800644</v>
+        <v>6800603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,9 +3034,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3059,22 +3061,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814644</v>
+        <v>128814724</v>
       </c>
       <c r="B25" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,42 +3084,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456603</v>
+        <v>456520</v>
       </c>
       <c r="R25" t="n">
-        <v>6800371</v>
+        <v>6800367</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,10 +3170,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814673</v>
+        <v>128814616</v>
       </c>
       <c r="B26" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3181,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3205,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456469</v>
+        <v>456487</v>
       </c>
       <c r="R26" t="n">
-        <v>6800542</v>
+        <v>6800546</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3273,10 +3267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814703</v>
+        <v>128814716</v>
       </c>
       <c r="B27" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,21 +3278,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3308,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456766</v>
+        <v>456477</v>
       </c>
       <c r="R27" t="n">
-        <v>6800611</v>
+        <v>6800324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3344,6 +3338,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3370,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814616</v>
+        <v>128814703</v>
       </c>
       <c r="B28" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,21 +3380,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456487</v>
+        <v>456766</v>
       </c>
       <c r="R28" t="n">
-        <v>6800546</v>
+        <v>6800611</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814716</v>
+        <v>128814652</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,34 +3477,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456477</v>
+        <v>456781</v>
       </c>
       <c r="R29" t="n">
-        <v>6800324</v>
+        <v>6800644</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,11 +3545,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814724</v>
+        <v>128814644</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,34 +3582,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456520</v>
+        <v>456603</v>
       </c>
       <c r="R30" t="n">
-        <v>6800367</v>
+        <v>6800371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3666,10 +3676,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128805061</v>
+        <v>128814673</v>
       </c>
       <c r="B31" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3677,21 +3687,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3701,10 +3711,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456690</v>
+        <v>456469</v>
       </c>
       <c r="R31" t="n">
-        <v>6800603</v>
+        <v>6800542</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,19 +3744,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3761,22 +3761,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814626</v>
+        <v>128814692</v>
       </c>
       <c r="B32" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456763</v>
+        <v>456354</v>
       </c>
       <c r="R32" t="n">
-        <v>6800617</v>
+        <v>6800374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814692</v>
+        <v>128814626</v>
       </c>
       <c r="B33" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456354</v>
+        <v>456763</v>
       </c>
       <c r="R33" t="n">
-        <v>6800374</v>
+        <v>6800617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814727</v>
+        <v>128804553</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456600</v>
+        <v>456768</v>
       </c>
       <c r="R36" t="n">
-        <v>6800519</v>
+        <v>6800626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,9 +4229,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4246,22 +4256,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128804553</v>
+        <v>128814689</v>
       </c>
       <c r="B37" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4269,21 +4279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4293,10 +4303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456768</v>
+        <v>456495</v>
       </c>
       <c r="R37" t="n">
-        <v>6800626</v>
+        <v>6800433</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,19 +4336,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4353,22 +4353,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814711</v>
+        <v>128814743</v>
       </c>
       <c r="B38" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,21 +4376,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4400,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456642</v>
+        <v>456566</v>
       </c>
       <c r="R38" t="n">
-        <v>6800358</v>
+        <v>6800498</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,6 +4436,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4462,10 +4467,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814710</v>
+        <v>128814727</v>
       </c>
       <c r="B39" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4473,21 +4478,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4497,10 +4502,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456770</v>
+        <v>456600</v>
       </c>
       <c r="R39" t="n">
-        <v>6800515</v>
+        <v>6800519</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4559,7 +4564,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128814689</v>
+        <v>128814710</v>
       </c>
       <c r="B40" t="n">
         <v>78881</v>
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456495</v>
+        <v>456770</v>
       </c>
       <c r="R40" t="n">
-        <v>6800433</v>
+        <v>6800515</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,10 +4661,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128814743</v>
+        <v>128814711</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,21 +4672,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4691,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456566</v>
+        <v>456642</v>
       </c>
       <c r="R41" t="n">
-        <v>6800498</v>
+        <v>6800358</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4727,11 +4732,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,7 +4758,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128814733</v>
+        <v>128814739</v>
       </c>
       <c r="B42" t="n">
         <v>79124</v>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456547</v>
+        <v>456351</v>
       </c>
       <c r="R42" t="n">
-        <v>6800300</v>
+        <v>6800353</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814739</v>
+        <v>128814733</v>
       </c>
       <c r="B43" t="n">
         <v>79124</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456351</v>
+        <v>456547</v>
       </c>
       <c r="R43" t="n">
-        <v>6800353</v>
+        <v>6800300</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B46" t="n">
         <v>79743</v>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R46" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B47" t="n">
         <v>79743</v>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R47" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128814730</v>
+        <v>128814742</v>
       </c>
       <c r="B48" t="n">
         <v>79124</v>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456589</v>
+        <v>456590</v>
       </c>
       <c r="R48" t="n">
-        <v>6800302</v>
+        <v>6800535</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128814742</v>
+        <v>128814730</v>
       </c>
       <c r="B49" t="n">
         <v>79124</v>
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456590</v>
+        <v>456589</v>
       </c>
       <c r="R49" t="n">
-        <v>6800535</v>
+        <v>6800302</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128799275</v>
+        <v>128814648</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,34 +5692,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456665</v>
+        <v>456618</v>
       </c>
       <c r="R51" t="n">
-        <v>6800399</v>
+        <v>6800564</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,24 +5757,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5781,22 +5774,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814612</v>
+        <v>128799275</v>
       </c>
       <c r="B52" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5804,21 +5797,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5828,10 +5821,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456539</v>
+        <v>456665</v>
       </c>
       <c r="R52" t="n">
-        <v>6800496</v>
+        <v>6800399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5861,9 +5854,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5878,19 +5886,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814620</v>
+        <v>128814612</v>
       </c>
       <c r="B53" t="n">
         <v>79743</v>
@@ -5919,19 +5927,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456385</v>
+        <v>456539</v>
       </c>
       <c r="R53" t="n">
-        <v>6800430</v>
+        <v>6800496</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5972,7 +5977,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6185,10 +6189,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814718</v>
+        <v>128814620</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6196,34 +6200,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456559</v>
+        <v>456385</v>
       </c>
       <c r="R56" t="n">
-        <v>6800586</v>
+        <v>6800430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6264,6 +6271,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6282,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814648</v>
+        <v>128814718</v>
       </c>
       <c r="B57" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6293,42 +6301,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456618</v>
+        <v>456559</v>
       </c>
       <c r="R57" t="n">
-        <v>6800564</v>
+        <v>6800586</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128814628</v>
+        <v>128799700</v>
       </c>
       <c r="B59" t="n">
         <v>79714</v>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456549</v>
+        <v>456668</v>
       </c>
       <c r="R59" t="n">
-        <v>6800517</v>
+        <v>6800363</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,9 +6562,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6579,19 +6589,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128799700</v>
+        <v>128814628</v>
       </c>
       <c r="B60" t="n">
         <v>79714</v>
@@ -6626,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456668</v>
+        <v>456549</v>
       </c>
       <c r="R60" t="n">
-        <v>6800363</v>
+        <v>6800517</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6659,19 +6669,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6686,12 +6686,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6892,7 +6892,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128814721</v>
+        <v>128802133</v>
       </c>
       <c r="B63" t="n">
         <v>79124</v>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456414</v>
+        <v>456775</v>
       </c>
       <c r="R63" t="n">
-        <v>6800442</v>
+        <v>6800500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,9 +6960,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6977,12 +6992,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7096,7 +7111,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128802133</v>
+        <v>128814721</v>
       </c>
       <c r="B65" t="n">
         <v>79124</v>
@@ -7131,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456775</v>
+        <v>456414</v>
       </c>
       <c r="R65" t="n">
-        <v>6800500</v>
+        <v>6800442</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7164,24 +7179,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7196,12 +7196,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128814707</v>
+        <v>128799394</v>
       </c>
       <c r="B70" t="n">
-        <v>78881</v>
+        <v>91458</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456665</v>
+        <v>456679</v>
       </c>
       <c r="R70" t="n">
-        <v>6800450</v>
+        <v>6800380</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7699,9 +7699,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,12 +7726,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7825,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128814697</v>
+        <v>128814717</v>
       </c>
       <c r="B72" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7836,21 +7846,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7860,10 +7870,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>456499</v>
+        <v>456529</v>
       </c>
       <c r="R72" t="n">
-        <v>6800562</v>
+        <v>6800501</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,10 +7932,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814717</v>
+        <v>128814707</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7943,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7967,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456529</v>
+        <v>456665</v>
       </c>
       <c r="R73" t="n">
-        <v>6800501</v>
+        <v>6800450</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8223,10 +8233,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128799394</v>
+        <v>128814697</v>
       </c>
       <c r="B76" t="n">
-        <v>91458</v>
+        <v>78881</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8234,21 +8244,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8258,10 +8268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456679</v>
+        <v>456499</v>
       </c>
       <c r="R76" t="n">
-        <v>6800380</v>
+        <v>6800562</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8291,19 +8301,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,12 +8318,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814722</v>
+        <v>128800436</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456349</v>
+        <v>456671</v>
       </c>
       <c r="R79" t="n">
-        <v>6800436</v>
+        <v>6800350</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8602,9 +8602,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8619,19 +8629,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814702</v>
+        <v>128814709</v>
       </c>
       <c r="B80" t="n">
         <v>78881</v>
@@ -8666,10 +8676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456788</v>
+        <v>456706</v>
       </c>
       <c r="R80" t="n">
-        <v>6800626</v>
+        <v>6800520</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8728,7 +8738,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814695</v>
+        <v>128814702</v>
       </c>
       <c r="B81" t="n">
         <v>78881</v>
@@ -8763,10 +8773,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456547</v>
+        <v>456788</v>
       </c>
       <c r="R81" t="n">
-        <v>6800403</v>
+        <v>6800626</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8825,10 +8835,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814709</v>
+        <v>128814722</v>
       </c>
       <c r="B82" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8846,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8870,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456706</v>
+        <v>456349</v>
       </c>
       <c r="R82" t="n">
-        <v>6800520</v>
+        <v>6800436</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8922,10 +8932,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128814618</v>
+        <v>128814695</v>
       </c>
       <c r="B83" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8933,21 +8943,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8957,10 +8967,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456450</v>
+        <v>456547</v>
       </c>
       <c r="R83" t="n">
-        <v>6800571</v>
+        <v>6800403</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9019,7 +9029,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128800436</v>
+        <v>128814618</v>
       </c>
       <c r="B84" t="n">
         <v>79743</v>
@@ -9054,10 +9064,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456671</v>
+        <v>456450</v>
       </c>
       <c r="R84" t="n">
-        <v>6800350</v>
+        <v>6800571</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9087,19 +9097,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9114,12 +9114,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814741</v>
+        <v>128814630</v>
       </c>
       <c r="B86" t="n">
-        <v>79124</v>
+        <v>79714</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456637</v>
+        <v>456496</v>
       </c>
       <c r="R86" t="n">
-        <v>6800536</v>
+        <v>6800554</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814723</v>
+        <v>128814741</v>
       </c>
       <c r="B87" t="n">
         <v>79124</v>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456351</v>
+        <v>456637</v>
       </c>
       <c r="R87" t="n">
-        <v>6800371</v>
+        <v>6800536</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814630</v>
+        <v>128814723</v>
       </c>
       <c r="B89" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456496</v>
+        <v>456351</v>
       </c>
       <c r="R89" t="n">
-        <v>6800554</v>
+        <v>6800371</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128814664</v>
+        <v>128799696</v>
       </c>
       <c r="B90" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,42 +9637,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456676</v>
+        <v>456668</v>
       </c>
       <c r="R90" t="n">
-        <v>6800380</v>
+        <v>6800363</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9702,9 +9694,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9719,22 +9721,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814694</v>
+        <v>128814732</v>
       </c>
       <c r="B91" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9742,21 +9744,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9766,10 +9768,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456594</v>
+        <v>456571</v>
       </c>
       <c r="R91" t="n">
-        <v>6800423</v>
+        <v>6800296</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9828,7 +9830,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814690</v>
+        <v>128814699</v>
       </c>
       <c r="B92" t="n">
         <v>78881</v>
@@ -9863,10 +9865,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456465</v>
+        <v>456496</v>
       </c>
       <c r="R92" t="n">
-        <v>6800546</v>
+        <v>6800549</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9925,10 +9927,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814732</v>
+        <v>128814637</v>
       </c>
       <c r="B93" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9936,34 +9938,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456571</v>
+        <v>456352</v>
       </c>
       <c r="R93" t="n">
-        <v>6800296</v>
+        <v>6800325</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10022,7 +10032,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814699</v>
+        <v>128814705</v>
       </c>
       <c r="B94" t="n">
         <v>78881</v>
@@ -10057,10 +10067,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456496</v>
+        <v>456749</v>
       </c>
       <c r="R94" t="n">
-        <v>6800549</v>
+        <v>6800566</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10119,10 +10129,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814705</v>
+        <v>128814622</v>
       </c>
       <c r="B95" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10130,21 +10140,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10154,10 +10164,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456749</v>
+        <v>456546</v>
       </c>
       <c r="R95" t="n">
-        <v>6800566</v>
+        <v>6800434</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10216,10 +10226,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814622</v>
+        <v>128814690</v>
       </c>
       <c r="B96" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10227,21 +10237,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10251,10 +10261,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456546</v>
+        <v>456465</v>
       </c>
       <c r="R96" t="n">
-        <v>6800434</v>
+        <v>6800546</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10313,10 +10323,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128804256</v>
+        <v>128814694</v>
       </c>
       <c r="B97" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10324,21 +10334,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10348,10 +10358,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456794</v>
+        <v>456594</v>
       </c>
       <c r="R97" t="n">
-        <v>6800605</v>
+        <v>6800423</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10381,19 +10391,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10408,22 +10408,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128814637</v>
+        <v>128804256</v>
       </c>
       <c r="B98" t="n">
-        <v>57720</v>
+        <v>79743</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10431,42 +10431,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456352</v>
+        <v>456794</v>
       </c>
       <c r="R98" t="n">
-        <v>6800325</v>
+        <v>6800605</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10496,9 +10488,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10513,22 +10515,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128799696</v>
+        <v>128814664</v>
       </c>
       <c r="B99" t="n">
-        <v>78882</v>
+        <v>57717</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10536,34 +10538,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456668</v>
+        <v>456676</v>
       </c>
       <c r="R99" t="n">
-        <v>6800363</v>
+        <v>6800380</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10593,19 +10603,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10620,12 +10620,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128814624</v>
+        <v>128814632</v>
       </c>
       <c r="B101" t="n">
-        <v>79743</v>
+        <v>79714</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10744,37 +10744,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456688</v>
+        <v>456382</v>
       </c>
       <c r="R101" t="n">
-        <v>6800585</v>
+        <v>6800427</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10815,7 +10812,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10834,10 +10830,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805203</v>
+        <v>128804554</v>
       </c>
       <c r="B102" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10845,21 +10841,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10869,10 +10865,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456650</v>
+        <v>456768</v>
       </c>
       <c r="R102" t="n">
-        <v>6800594</v>
+        <v>6800626</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10941,10 +10937,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814737</v>
+        <v>128814683</v>
       </c>
       <c r="B103" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10952,34 +10948,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456555</v>
+        <v>456644</v>
       </c>
       <c r="R103" t="n">
-        <v>6800627</v>
+        <v>6800358</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11020,6 +11019,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128814698</v>
+        <v>128805054</v>
       </c>
       <c r="B104" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456491</v>
+        <v>456690</v>
       </c>
       <c r="R104" t="n">
-        <v>6800537</v>
+        <v>6800603</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11106,9 +11106,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11123,22 +11133,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128805054</v>
+        <v>128804050</v>
       </c>
       <c r="B105" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11146,21 +11156,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11170,10 +11180,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456690</v>
+        <v>456753</v>
       </c>
       <c r="R105" t="n">
-        <v>6800603</v>
+        <v>6800562</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11216,6 +11226,11 @@
       <c r="AB105" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11242,7 +11257,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128804050</v>
+        <v>128805203</v>
       </c>
       <c r="B106" t="n">
         <v>79124</v>
@@ -11277,10 +11292,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456753</v>
+        <v>456650</v>
       </c>
       <c r="R106" t="n">
-        <v>6800562</v>
+        <v>6800594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11323,11 +11338,6 @@
       <c r="AB106" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11354,10 +11364,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814725</v>
+        <v>128814698</v>
       </c>
       <c r="B107" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11365,21 +11375,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11389,10 +11399,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456598</v>
+        <v>456491</v>
       </c>
       <c r="R107" t="n">
-        <v>6800407</v>
+        <v>6800537</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11425,11 +11435,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11456,10 +11461,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128814632</v>
+        <v>128814737</v>
       </c>
       <c r="B108" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11467,21 +11472,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11491,10 +11496,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456382</v>
+        <v>456555</v>
       </c>
       <c r="R108" t="n">
-        <v>6800427</v>
+        <v>6800627</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11553,10 +11558,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128804554</v>
+        <v>128814624</v>
       </c>
       <c r="B109" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11564,34 +11569,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456768</v>
+        <v>456688</v>
       </c>
       <c r="R109" t="n">
-        <v>6800626</v>
+        <v>6800585</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11621,49 +11629,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814683</v>
+        <v>128814725</v>
       </c>
       <c r="B110" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11671,37 +11670,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456644</v>
+        <v>456598</v>
       </c>
       <c r="R110" t="n">
-        <v>6800358</v>
+        <v>6800407</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11736,13 +11732,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11866,10 +11866,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814679</v>
+        <v>128814634</v>
       </c>
       <c r="B112" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11877,34 +11877,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456753</v>
+        <v>456405</v>
       </c>
       <c r="R112" t="n">
-        <v>6800533</v>
+        <v>6800457</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11963,10 +11971,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128803369</v>
+        <v>128814679</v>
       </c>
       <c r="B113" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11974,21 +11982,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11998,10 +12006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456688</v>
+        <v>456753</v>
       </c>
       <c r="R113" t="n">
-        <v>6800474</v>
+        <v>6800533</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,19 +12039,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12058,22 +12056,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814687</v>
+        <v>128805558</v>
       </c>
       <c r="B114" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12081,21 +12079,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12105,10 +12103,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456556</v>
+        <v>456627</v>
       </c>
       <c r="R114" t="n">
-        <v>6800320</v>
+        <v>6800521</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12138,9 +12136,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12155,19 +12163,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128805558</v>
+        <v>128814731</v>
       </c>
       <c r="B115" t="n">
         <v>79124</v>
@@ -12202,10 +12210,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456627</v>
+        <v>456580</v>
       </c>
       <c r="R115" t="n">
-        <v>6800521</v>
+        <v>6800292</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12235,19 +12243,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12262,22 +12260,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814614</v>
+        <v>128814696</v>
       </c>
       <c r="B116" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12285,21 +12283,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12309,10 +12307,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456522</v>
+        <v>456559</v>
       </c>
       <c r="R116" t="n">
-        <v>6800319</v>
+        <v>6800576</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12371,10 +12369,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814731</v>
+        <v>128803369</v>
       </c>
       <c r="B117" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12382,21 +12380,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12406,10 +12404,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456580</v>
+        <v>456688</v>
       </c>
       <c r="R117" t="n">
-        <v>6800292</v>
+        <v>6800474</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12439,9 +12437,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12456,22 +12464,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814696</v>
+        <v>128814614</v>
       </c>
       <c r="B118" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12479,21 +12487,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12503,10 +12511,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456559</v>
+        <v>456522</v>
       </c>
       <c r="R118" t="n">
-        <v>6800576</v>
+        <v>6800319</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12565,10 +12573,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814634</v>
+        <v>128814687</v>
       </c>
       <c r="B119" t="n">
-        <v>57720</v>
+        <v>78881</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12576,42 +12584,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456405</v>
+        <v>456556</v>
       </c>
       <c r="R119" t="n">
-        <v>6800457</v>
+        <v>6800320</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13478,10 +13478,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816343</v>
+        <v>128816338</v>
       </c>
       <c r="B128" t="n">
-        <v>57720</v>
+        <v>79714</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13489,31 +13489,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13521,10 +13516,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456341</v>
+        <v>456478</v>
       </c>
       <c r="R128" t="n">
-        <v>6800306</v>
+        <v>6800591</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,6 +13560,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13583,10 +13579,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816338</v>
+        <v>128816343</v>
       </c>
       <c r="B129" t="n">
-        <v>79714</v>
+        <v>57720</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13594,26 +13590,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13621,10 +13622,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456478</v>
+        <v>456341</v>
       </c>
       <c r="R129" t="n">
-        <v>6800591</v>
+        <v>6800306</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13665,7 +13666,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14278,10 +14278,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128816331</v>
+        <v>128816335</v>
       </c>
       <c r="B136" t="n">
-        <v>79156</v>
+        <v>79743</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14289,37 +14289,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>456376</v>
+        <v>456564</v>
       </c>
       <c r="R136" t="n">
-        <v>6800472</v>
+        <v>6800617</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14360,7 +14357,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14379,10 +14375,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128816335</v>
+        <v>128816331</v>
       </c>
       <c r="B137" t="n">
-        <v>79743</v>
+        <v>79156</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14390,34 +14386,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>456564</v>
+        <v>456376</v>
       </c>
       <c r="R137" t="n">
-        <v>6800617</v>
+        <v>6800472</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14458,6 +14457,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15167,10 +15167,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816345</v>
+        <v>128816359</v>
       </c>
       <c r="B145" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15178,42 +15178,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456606</v>
+        <v>456335</v>
       </c>
       <c r="R145" t="n">
-        <v>6800517</v>
+        <v>6800427</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15272,10 +15264,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816359</v>
+        <v>128816345</v>
       </c>
       <c r="B146" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15283,34 +15275,42 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456335</v>
+        <v>456606</v>
       </c>
       <c r="R146" t="n">
-        <v>6800427</v>
+        <v>6800517</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15668,10 +15668,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128816360</v>
+        <v>128816337</v>
       </c>
       <c r="B150" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15679,21 +15679,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>456583</v>
+        <v>456758</v>
       </c>
       <c r="R150" t="n">
-        <v>6800417</v>
+        <v>6800574</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15765,10 +15765,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128816337</v>
+        <v>128816360</v>
       </c>
       <c r="B151" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15776,21 +15776,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15800,10 +15800,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>456758</v>
+        <v>456583</v>
       </c>
       <c r="R151" t="n">
-        <v>6800574</v>
+        <v>6800417</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128814701</v>
+        <v>128799069</v>
       </c>
       <c r="B2" t="n">
-        <v>78881</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456547</v>
+        <v>456632</v>
       </c>
       <c r="R2" t="n">
-        <v>6800436</v>
+        <v>6800431</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +748,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -884,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128799069</v>
+        <v>128814701</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456632</v>
+        <v>456547</v>
       </c>
       <c r="R4" t="n">
-        <v>6800431</v>
+        <v>6800436</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +967,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128814658</v>
+        <v>128803579</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456645</v>
+        <v>456698</v>
       </c>
       <c r="R5" t="n">
-        <v>6800444</v>
+        <v>6800503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,9 +1064,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128814640</v>
+        <v>128805128</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,42 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456331</v>
+        <v>456660</v>
       </c>
       <c r="R6" t="n">
-        <v>6800312</v>
+        <v>6800603</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,9 +1176,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128803579</v>
+        <v>128814640</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,34 +1226,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456698</v>
+        <v>456331</v>
       </c>
       <c r="R7" t="n">
-        <v>6800503</v>
+        <v>6800312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,24 +1291,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,12 +1308,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1425,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128805128</v>
+        <v>128814728</v>
       </c>
       <c r="B9" t="n">
         <v>79124</v>
@@ -1460,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456660</v>
+        <v>456616</v>
       </c>
       <c r="R9" t="n">
-        <v>6800603</v>
+        <v>6800533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,19 +1495,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,22 +1512,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814728</v>
+        <v>128814658</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,34 +1535,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456616</v>
+        <v>456645</v>
       </c>
       <c r="R10" t="n">
-        <v>6800533</v>
+        <v>6800444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814681</v>
+        <v>128804672</v>
       </c>
       <c r="B12" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456761</v>
+        <v>456733</v>
       </c>
       <c r="R12" t="n">
-        <v>6800515</v>
+        <v>6800618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,9 +1804,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,22 +1831,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128804672</v>
+        <v>128814666</v>
       </c>
       <c r="B13" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,34 +1854,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456733</v>
+        <v>456659</v>
       </c>
       <c r="R13" t="n">
-        <v>6800618</v>
+        <v>6800402</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,19 +1919,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,22 +1936,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814666</v>
+        <v>128814681</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,42 +1959,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456659</v>
+        <v>456761</v>
       </c>
       <c r="R14" t="n">
-        <v>6800402</v>
+        <v>6800515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814654</v>
+        <v>128814744</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,42 +2056,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456705</v>
+        <v>456737</v>
       </c>
       <c r="R15" t="n">
-        <v>6800486</v>
+        <v>6800417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814744</v>
+        <v>128804638</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456737</v>
+        <v>456748</v>
       </c>
       <c r="R16" t="n">
-        <v>6800417</v>
+        <v>6800617</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,9 +2210,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,22 +2237,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128804638</v>
+        <v>128814729</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2258,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2282,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456748</v>
+        <v>456606</v>
       </c>
       <c r="R17" t="n">
-        <v>6800617</v>
+        <v>6800334</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,19 +2317,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,22 +2334,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128814729</v>
+        <v>128814693</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456606</v>
+        <v>456515</v>
       </c>
       <c r="R18" t="n">
-        <v>6800334</v>
+        <v>6800380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,7 +2443,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805619</v>
+        <v>128814715</v>
       </c>
       <c r="B19" t="n">
         <v>79124</v>
@@ -2486,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456600</v>
+        <v>456589</v>
       </c>
       <c r="R19" t="n">
-        <v>6800539</v>
+        <v>6800303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,19 +2511,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,22 +2528,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128805376</v>
+        <v>128804261</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2551,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456589</v>
+        <v>456794</v>
       </c>
       <c r="R20" t="n">
-        <v>6800567</v>
+        <v>6800605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128814693</v>
+        <v>128805619</v>
       </c>
       <c r="B21" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456515</v>
+        <v>456600</v>
       </c>
       <c r="R21" t="n">
-        <v>6800380</v>
+        <v>6800539</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,9 +2715,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,19 +2742,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814715</v>
+        <v>128805376</v>
       </c>
       <c r="B22" t="n">
         <v>79124</v>
@@ -2800,7 +2792,7 @@
         <v>456589</v>
       </c>
       <c r="R22" t="n">
-        <v>6800303</v>
+        <v>6800567</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2830,9 +2822,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,22 +2849,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128804261</v>
+        <v>128814654</v>
       </c>
       <c r="B23" t="n">
-        <v>78882</v>
+        <v>57717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,34 +2872,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456794</v>
+        <v>456705</v>
       </c>
       <c r="R23" t="n">
-        <v>6800605</v>
+        <v>6800486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,19 +2937,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,22 +2954,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128805061</v>
+        <v>128814616</v>
       </c>
       <c r="B24" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456690</v>
+        <v>456487</v>
       </c>
       <c r="R24" t="n">
-        <v>6800603</v>
+        <v>6800546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,19 +3034,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,19 +3051,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814724</v>
+        <v>128814716</v>
       </c>
       <c r="B25" t="n">
         <v>79124</v>
@@ -3108,10 +3098,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456520</v>
+        <v>456477</v>
       </c>
       <c r="R25" t="n">
-        <v>6800367</v>
+        <v>6800324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3144,6 +3134,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3170,10 +3165,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814616</v>
+        <v>128805061</v>
       </c>
       <c r="B26" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3181,21 +3176,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3205,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456487</v>
+        <v>456690</v>
       </c>
       <c r="R26" t="n">
-        <v>6800546</v>
+        <v>6800603</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,9 +3233,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3255,22 +3260,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814716</v>
+        <v>128814703</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456477</v>
+        <v>456766</v>
       </c>
       <c r="R27" t="n">
-        <v>6800324</v>
+        <v>6800611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3338,11 +3343,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814703</v>
+        <v>128814724</v>
       </c>
       <c r="B28" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456766</v>
+        <v>456520</v>
       </c>
       <c r="R28" t="n">
-        <v>6800611</v>
+        <v>6800367</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814652</v>
+        <v>128814644</v>
       </c>
       <c r="B29" t="n">
         <v>57717</v>
@@ -3499,7 +3499,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456781</v>
+        <v>456603</v>
       </c>
       <c r="R29" t="n">
-        <v>6800644</v>
+        <v>6800371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814644</v>
+        <v>128814652</v>
       </c>
       <c r="B30" t="n">
         <v>57717</v>
@@ -3604,7 +3604,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456603</v>
+        <v>456781</v>
       </c>
       <c r="R30" t="n">
-        <v>6800371</v>
+        <v>6800644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814692</v>
+        <v>128814720</v>
       </c>
       <c r="B32" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456354</v>
+        <v>456446</v>
       </c>
       <c r="R32" t="n">
-        <v>6800374</v>
+        <v>6800471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814626</v>
+        <v>128814692</v>
       </c>
       <c r="B33" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456763</v>
+        <v>456354</v>
       </c>
       <c r="R33" t="n">
-        <v>6800617</v>
+        <v>6800374</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814708</v>
+        <v>128814626</v>
       </c>
       <c r="B34" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456702</v>
+        <v>456763</v>
       </c>
       <c r="R34" t="n">
-        <v>6800512</v>
+        <v>6800617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814720</v>
+        <v>128814708</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456446</v>
+        <v>456702</v>
       </c>
       <c r="R35" t="n">
-        <v>6800471</v>
+        <v>6800512</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128804553</v>
+        <v>128814743</v>
       </c>
       <c r="B36" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456768</v>
+        <v>456566</v>
       </c>
       <c r="R36" t="n">
-        <v>6800626</v>
+        <v>6800498</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,19 +4229,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,22 +4251,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814689</v>
+        <v>128804553</v>
       </c>
       <c r="B37" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4279,21 +4274,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4303,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456495</v>
+        <v>456768</v>
       </c>
       <c r="R37" t="n">
-        <v>6800433</v>
+        <v>6800626</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,9 +4331,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4353,22 +4358,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814743</v>
+        <v>128814689</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,21 +4381,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4400,10 +4405,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456566</v>
+        <v>456495</v>
       </c>
       <c r="R38" t="n">
-        <v>6800498</v>
+        <v>6800433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,11 +4441,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128814648</v>
+        <v>128799275</v>
       </c>
       <c r="B51" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,42 +5692,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456618</v>
+        <v>456665</v>
       </c>
       <c r="R51" t="n">
-        <v>6800564</v>
+        <v>6800399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5757,9 +5749,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5774,22 +5781,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128799275</v>
+        <v>128814612</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5797,21 +5804,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5821,10 +5828,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456665</v>
+        <v>456539</v>
       </c>
       <c r="R52" t="n">
-        <v>6800399</v>
+        <v>6800496</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5854,24 +5861,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5886,22 +5878,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814612</v>
+        <v>128814719</v>
       </c>
       <c r="B53" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,21 +5901,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5925,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456539</v>
+        <v>456527</v>
       </c>
       <c r="R53" t="n">
-        <v>6800496</v>
+        <v>6800610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,7 +5987,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814719</v>
+        <v>128814736</v>
       </c>
       <c r="B54" t="n">
         <v>79124</v>
@@ -6030,10 +6022,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456527</v>
+        <v>456569</v>
       </c>
       <c r="R54" t="n">
-        <v>6800610</v>
+        <v>6800599</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6092,10 +6084,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814736</v>
+        <v>128814620</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,34 +6095,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456569</v>
+        <v>456385</v>
       </c>
       <c r="R55" t="n">
-        <v>6800599</v>
+        <v>6800430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6171,6 +6166,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6189,10 +6185,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814620</v>
+        <v>128814718</v>
       </c>
       <c r="B56" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6200,37 +6196,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456385</v>
+        <v>456559</v>
       </c>
       <c r="R56" t="n">
-        <v>6800430</v>
+        <v>6800586</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6271,7 +6264,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6290,10 +6282,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814718</v>
+        <v>128814648</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6301,34 +6293,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456559</v>
+        <v>456618</v>
       </c>
       <c r="R57" t="n">
-        <v>6800586</v>
+        <v>6800564</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128799700</v>
+        <v>128814734</v>
       </c>
       <c r="B59" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456668</v>
+        <v>456472</v>
       </c>
       <c r="R59" t="n">
-        <v>6800363</v>
+        <v>6800343</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,19 +6562,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6589,12 +6579,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6698,10 +6688,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814735</v>
+        <v>128799700</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79714</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6699,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6723,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456477</v>
+        <v>456668</v>
       </c>
       <c r="R61" t="n">
-        <v>6800413</v>
+        <v>6800363</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6766,9 +6756,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,19 +6783,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128814734</v>
+        <v>128814735</v>
       </c>
       <c r="B62" t="n">
         <v>79124</v>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456472</v>
+        <v>456477</v>
       </c>
       <c r="R62" t="n">
-        <v>6800343</v>
+        <v>6800413</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7738,10 +7738,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814691</v>
+        <v>128814717</v>
       </c>
       <c r="B71" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456385</v>
+        <v>456529</v>
       </c>
       <c r="R71" t="n">
-        <v>6800430</v>
+        <v>6800501</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128814717</v>
+        <v>128814691</v>
       </c>
       <c r="B72" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,21 +7846,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>456529</v>
+        <v>456385</v>
       </c>
       <c r="R72" t="n">
-        <v>6800501</v>
+        <v>6800430</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8126,10 +8126,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128803330</v>
+        <v>128814697</v>
       </c>
       <c r="B75" t="n">
-        <v>79714</v>
+        <v>78881</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8137,21 +8137,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456690</v>
+        <v>456499</v>
       </c>
       <c r="R75" t="n">
-        <v>6800454</v>
+        <v>6800562</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8194,19 +8194,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8221,22 +8211,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128814697</v>
+        <v>128803330</v>
       </c>
       <c r="B76" t="n">
-        <v>78881</v>
+        <v>79714</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8244,21 +8234,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8268,10 +8258,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456499</v>
+        <v>456690</v>
       </c>
       <c r="R76" t="n">
-        <v>6800562</v>
+        <v>6800454</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,9 +8291,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,22 +8318,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128814677</v>
+        <v>128814722</v>
       </c>
       <c r="B77" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456747</v>
+        <v>456349</v>
       </c>
       <c r="R77" t="n">
-        <v>6800569</v>
+        <v>6800436</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128801262</v>
+        <v>128800436</v>
       </c>
       <c r="B78" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8438,21 +8438,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456703</v>
+        <v>456671</v>
       </c>
       <c r="R78" t="n">
-        <v>6800429</v>
+        <v>6800350</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128800436</v>
+        <v>128814709</v>
       </c>
       <c r="B79" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456671</v>
+        <v>456706</v>
       </c>
       <c r="R79" t="n">
-        <v>6800350</v>
+        <v>6800520</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8602,19 +8602,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8629,19 +8619,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814709</v>
+        <v>128814702</v>
       </c>
       <c r="B80" t="n">
         <v>78881</v>
@@ -8676,10 +8666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456706</v>
+        <v>456788</v>
       </c>
       <c r="R80" t="n">
-        <v>6800520</v>
+        <v>6800626</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8738,7 +8728,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814702</v>
+        <v>128814695</v>
       </c>
       <c r="B81" t="n">
         <v>78881</v>
@@ -8773,10 +8763,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456788</v>
+        <v>456547</v>
       </c>
       <c r="R81" t="n">
-        <v>6800626</v>
+        <v>6800403</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8835,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814722</v>
+        <v>128814618</v>
       </c>
       <c r="B82" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8846,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8870,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456349</v>
+        <v>456450</v>
       </c>
       <c r="R82" t="n">
-        <v>6800436</v>
+        <v>6800571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8932,48 +8922,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128814695</v>
+        <v>128800812</v>
       </c>
       <c r="B83" t="n">
-        <v>78881</v>
+        <v>58090</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456547</v>
+        <v>456691</v>
       </c>
       <c r="R83" t="n">
-        <v>6800403</v>
+        <v>6800368</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9000,9 +8995,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9017,22 +9022,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814618</v>
+        <v>128814677</v>
       </c>
       <c r="B84" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9040,21 +9045,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9064,10 +9069,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456450</v>
+        <v>456747</v>
       </c>
       <c r="R84" t="n">
-        <v>6800571</v>
+        <v>6800569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9126,53 +9131,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128800812</v>
+        <v>128801262</v>
       </c>
       <c r="B85" t="n">
-        <v>58090</v>
+        <v>78882</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456691</v>
+        <v>456703</v>
       </c>
       <c r="R85" t="n">
-        <v>6800368</v>
+        <v>6800429</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814630</v>
+        <v>128814741</v>
       </c>
       <c r="B86" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456496</v>
+        <v>456637</v>
       </c>
       <c r="R86" t="n">
-        <v>6800554</v>
+        <v>6800536</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814741</v>
+        <v>128814726</v>
       </c>
       <c r="B87" t="n">
         <v>79124</v>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456637</v>
+        <v>456524</v>
       </c>
       <c r="R87" t="n">
-        <v>6800536</v>
+        <v>6800431</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814726</v>
+        <v>128814723</v>
       </c>
       <c r="B88" t="n">
         <v>79124</v>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456524</v>
+        <v>456351</v>
       </c>
       <c r="R88" t="n">
-        <v>6800431</v>
+        <v>6800371</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814723</v>
+        <v>128814630</v>
       </c>
       <c r="B89" t="n">
-        <v>79124</v>
+        <v>79714</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456351</v>
+        <v>456496</v>
       </c>
       <c r="R89" t="n">
-        <v>6800371</v>
+        <v>6800554</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128799696</v>
+        <v>128814705</v>
       </c>
       <c r="B90" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456668</v>
+        <v>456749</v>
       </c>
       <c r="R90" t="n">
-        <v>6800363</v>
+        <v>6800566</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9694,19 +9694,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9721,22 +9711,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814732</v>
+        <v>128814622</v>
       </c>
       <c r="B91" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9744,21 +9734,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9768,10 +9758,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456571</v>
+        <v>456546</v>
       </c>
       <c r="R91" t="n">
-        <v>6800296</v>
+        <v>6800434</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9830,10 +9820,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814699</v>
+        <v>128814732</v>
       </c>
       <c r="B92" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9841,21 +9831,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9865,10 +9855,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456496</v>
+        <v>456571</v>
       </c>
       <c r="R92" t="n">
-        <v>6800549</v>
+        <v>6800296</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9927,10 +9917,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814637</v>
+        <v>128814690</v>
       </c>
       <c r="B93" t="n">
-        <v>57720</v>
+        <v>78881</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9938,42 +9928,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456352</v>
+        <v>456465</v>
       </c>
       <c r="R93" t="n">
-        <v>6800325</v>
+        <v>6800546</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10032,7 +10014,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814705</v>
+        <v>128814699</v>
       </c>
       <c r="B94" t="n">
         <v>78881</v>
@@ -10067,10 +10049,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456749</v>
+        <v>456496</v>
       </c>
       <c r="R94" t="n">
-        <v>6800566</v>
+        <v>6800549</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10129,10 +10111,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814622</v>
+        <v>128814694</v>
       </c>
       <c r="B95" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10140,21 +10122,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10164,10 +10146,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456546</v>
+        <v>456594</v>
       </c>
       <c r="R95" t="n">
-        <v>6800434</v>
+        <v>6800423</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10226,10 +10208,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814690</v>
+        <v>128804256</v>
       </c>
       <c r="B96" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10237,21 +10219,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10261,10 +10243,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456465</v>
+        <v>456794</v>
       </c>
       <c r="R96" t="n">
-        <v>6800546</v>
+        <v>6800605</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10294,9 +10276,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10311,22 +10303,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814694</v>
+        <v>128814664</v>
       </c>
       <c r="B97" t="n">
-        <v>78881</v>
+        <v>57717</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10334,34 +10326,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456594</v>
+        <v>456676</v>
       </c>
       <c r="R97" t="n">
-        <v>6800423</v>
+        <v>6800380</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128804256</v>
+        <v>128799696</v>
       </c>
       <c r="B98" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456794</v>
+        <v>456668</v>
       </c>
       <c r="R98" t="n">
-        <v>6800605</v>
+        <v>6800363</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10527,10 +10527,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128814664</v>
+        <v>128814637</v>
       </c>
       <c r="B99" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10538,16 +10538,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456676</v>
+        <v>456352</v>
       </c>
       <c r="R99" t="n">
-        <v>6800380</v>
+        <v>6800325</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10632,48 +10632,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128814713</v>
+        <v>128804050</v>
       </c>
       <c r="B100" t="n">
-        <v>90890</v>
+        <v>79124</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456692</v>
+        <v>456753</v>
       </c>
       <c r="R100" t="n">
-        <v>6800391</v>
+        <v>6800562</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10703,40 +10700,54 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128814632</v>
+        <v>128805203</v>
       </c>
       <c r="B101" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10744,21 +10755,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10768,10 +10779,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456382</v>
+        <v>456650</v>
       </c>
       <c r="R101" t="n">
-        <v>6800427</v>
+        <v>6800594</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10801,9 +10812,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10818,22 +10839,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128804554</v>
+        <v>128814737</v>
       </c>
       <c r="B102" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10841,21 +10862,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10865,10 +10886,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456768</v>
+        <v>456555</v>
       </c>
       <c r="R102" t="n">
-        <v>6800626</v>
+        <v>6800627</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10898,19 +10919,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10925,22 +10936,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814683</v>
+        <v>128814725</v>
       </c>
       <c r="B103" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10948,37 +10959,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456644</v>
+        <v>456598</v>
       </c>
       <c r="R103" t="n">
-        <v>6800358</v>
+        <v>6800407</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11013,13 +11021,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11145,10 +11157,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128804050</v>
+        <v>128814698</v>
       </c>
       <c r="B105" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11156,21 +11168,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11180,10 +11192,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456753</v>
+        <v>456491</v>
       </c>
       <c r="R105" t="n">
-        <v>6800562</v>
+        <v>6800537</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11213,24 +11225,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11245,22 +11242,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128805203</v>
+        <v>128814624</v>
       </c>
       <c r="B106" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11268,34 +11265,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456650</v>
+        <v>456688</v>
       </c>
       <c r="R106" t="n">
-        <v>6800594</v>
+        <v>6800585</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11325,84 +11325,78 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814698</v>
+        <v>128814713</v>
       </c>
       <c r="B107" t="n">
-        <v>78881</v>
+        <v>90890</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>5685</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456491</v>
+        <v>456692</v>
       </c>
       <c r="R107" t="n">
-        <v>6800537</v>
+        <v>6800391</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11443,6 +11437,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11461,10 +11456,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128814737</v>
+        <v>128814632</v>
       </c>
       <c r="B108" t="n">
-        <v>79124</v>
+        <v>79714</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11472,21 +11467,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11496,10 +11491,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456555</v>
+        <v>456382</v>
       </c>
       <c r="R108" t="n">
-        <v>6800627</v>
+        <v>6800427</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11558,10 +11553,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128814624</v>
+        <v>128804554</v>
       </c>
       <c r="B109" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11569,37 +11564,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456688</v>
+        <v>456768</v>
       </c>
       <c r="R109" t="n">
-        <v>6800585</v>
+        <v>6800626</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11629,40 +11621,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814725</v>
+        <v>128814683</v>
       </c>
       <c r="B110" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11670,34 +11671,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456598</v>
+        <v>456644</v>
       </c>
       <c r="R110" t="n">
-        <v>6800407</v>
+        <v>6800358</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11732,17 +11736,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128814646</v>
+        <v>128805558</v>
       </c>
       <c r="B111" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,42 +11772,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456519</v>
+        <v>456627</v>
       </c>
       <c r="R111" t="n">
-        <v>6800414</v>
+        <v>6800521</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11837,9 +11829,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,22 +11856,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814634</v>
+        <v>128814731</v>
       </c>
       <c r="B112" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11877,42 +11879,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456405</v>
+        <v>456580</v>
       </c>
       <c r="R112" t="n">
-        <v>6800457</v>
+        <v>6800292</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11971,10 +11965,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814679</v>
+        <v>128814696</v>
       </c>
       <c r="B113" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11982,21 +11976,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12006,10 +12000,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456753</v>
+        <v>456559</v>
       </c>
       <c r="R113" t="n">
-        <v>6800533</v>
+        <v>6800576</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12068,10 +12062,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128805558</v>
+        <v>128803369</v>
       </c>
       <c r="B114" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12079,21 +12073,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12103,10 +12097,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456627</v>
+        <v>456688</v>
       </c>
       <c r="R114" t="n">
-        <v>6800521</v>
+        <v>6800474</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12175,10 +12169,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814731</v>
+        <v>128814614</v>
       </c>
       <c r="B115" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,21 +12180,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12210,10 +12204,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456580</v>
+        <v>456522</v>
       </c>
       <c r="R115" t="n">
-        <v>6800292</v>
+        <v>6800319</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12272,7 +12266,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814696</v>
+        <v>128814687</v>
       </c>
       <c r="B116" t="n">
         <v>78881</v>
@@ -12307,10 +12301,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456559</v>
+        <v>456556</v>
       </c>
       <c r="R116" t="n">
-        <v>6800576</v>
+        <v>6800320</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12369,10 +12363,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128803369</v>
+        <v>128814646</v>
       </c>
       <c r="B117" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12380,34 +12374,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456688</v>
+        <v>456519</v>
       </c>
       <c r="R117" t="n">
-        <v>6800474</v>
+        <v>6800414</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12437,19 +12439,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12464,22 +12456,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814614</v>
+        <v>128814634</v>
       </c>
       <c r="B118" t="n">
-        <v>79743</v>
+        <v>57720</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12487,34 +12479,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456522</v>
+        <v>456405</v>
       </c>
       <c r="R118" t="n">
-        <v>6800319</v>
+        <v>6800457</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12573,10 +12573,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814687</v>
+        <v>128814679</v>
       </c>
       <c r="B119" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12584,21 +12584,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12608,10 +12608,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456556</v>
+        <v>456753</v>
       </c>
       <c r="R119" t="n">
-        <v>6800320</v>
+        <v>6800533</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816353</v>
+        <v>128816343</v>
       </c>
       <c r="B127" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,34 +13392,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456522</v>
+        <v>456341</v>
       </c>
       <c r="R127" t="n">
-        <v>6800357</v>
+        <v>6800306</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13579,10 +13587,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816343</v>
+        <v>128816353</v>
       </c>
       <c r="B129" t="n">
-        <v>57720</v>
+        <v>78881</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13590,42 +13598,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456341</v>
+        <v>456522</v>
       </c>
       <c r="R129" t="n">
-        <v>6800306</v>
+        <v>6800357</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15066,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816332</v>
+        <v>128816359</v>
       </c>
       <c r="B144" t="n">
-        <v>79156</v>
+        <v>79124</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15077,37 +15077,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456355</v>
+        <v>456335</v>
       </c>
       <c r="R144" t="n">
-        <v>6800454</v>
+        <v>6800427</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15148,7 +15145,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15167,10 +15163,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816359</v>
+        <v>128816345</v>
       </c>
       <c r="B145" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15178,34 +15174,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456335</v>
+        <v>456606</v>
       </c>
       <c r="R145" t="n">
-        <v>6800427</v>
+        <v>6800517</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15264,10 +15268,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816345</v>
+        <v>128816332</v>
       </c>
       <c r="B146" t="n">
-        <v>57717</v>
+        <v>79156</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15275,31 +15279,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15307,10 +15306,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456606</v>
+        <v>456355</v>
       </c>
       <c r="R146" t="n">
-        <v>6800517</v>
+        <v>6800454</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15351,6 +15350,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128799069</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128800923</v>
+        <v>128814701</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456692</v>
+        <v>456547</v>
       </c>
       <c r="R3" t="n">
-        <v>6800405</v>
+        <v>6800436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,24 +855,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128814701</v>
+        <v>128800923</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456547</v>
+        <v>456692</v>
       </c>
       <c r="R4" t="n">
-        <v>6800436</v>
+        <v>6800405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,9 +952,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>128803579</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128805128</v>
+        <v>128801339</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456660</v>
+        <v>456742</v>
       </c>
       <c r="R6" t="n">
-        <v>6800603</v>
+        <v>6800421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128814640</v>
+        <v>128805128</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,42 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456331</v>
+        <v>456660</v>
       </c>
       <c r="R7" t="n">
-        <v>6800312</v>
+        <v>6800603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,9 +1283,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,22 +1310,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128801339</v>
+        <v>128814728</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456742</v>
+        <v>456616</v>
       </c>
       <c r="R8" t="n">
-        <v>6800421</v>
+        <v>6800533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,19 +1390,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,22 +1407,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814728</v>
+        <v>128814658</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,34 +1430,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456616</v>
+        <v>456645</v>
       </c>
       <c r="R9" t="n">
-        <v>6800533</v>
+        <v>6800444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814658</v>
+        <v>128814640</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,16 +1535,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,7 +1557,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456645</v>
+        <v>456331</v>
       </c>
       <c r="R10" t="n">
-        <v>6800444</v>
+        <v>6800312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128804672</v>
+        <v>128814681</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456733</v>
+        <v>456761</v>
       </c>
       <c r="R12" t="n">
-        <v>6800618</v>
+        <v>6800515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,19 +1804,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,22 +1821,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814666</v>
+        <v>128804672</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,42 +1844,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456659</v>
+        <v>456733</v>
       </c>
       <c r="R13" t="n">
-        <v>6800402</v>
+        <v>6800618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,9 +1901,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,22 +1928,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814681</v>
+        <v>128814666</v>
       </c>
       <c r="B14" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,34 +1951,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456761</v>
+        <v>456659</v>
       </c>
       <c r="R14" t="n">
-        <v>6800515</v>
+        <v>6800402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814744</v>
+        <v>128814654</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,34 +2056,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456737</v>
+        <v>456705</v>
       </c>
       <c r="R15" t="n">
-        <v>6800417</v>
+        <v>6800486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128804638</v>
+        <v>128814744</v>
       </c>
       <c r="B16" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,21 +2161,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456748</v>
+        <v>456737</v>
       </c>
       <c r="R16" t="n">
-        <v>6800617</v>
+        <v>6800417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,19 +2218,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,22 +2235,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814729</v>
+        <v>128804638</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2258,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2284,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456606</v>
+        <v>456748</v>
       </c>
       <c r="R17" t="n">
-        <v>6800334</v>
+        <v>6800617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,9 +2315,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,22 +2342,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128814693</v>
+        <v>128814729</v>
       </c>
       <c r="B18" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,21 +2365,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456515</v>
+        <v>456606</v>
       </c>
       <c r="R18" t="n">
-        <v>6800380</v>
+        <v>6800334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128814715</v>
+        <v>128805619</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,10 +2486,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456589</v>
+        <v>456600</v>
       </c>
       <c r="R19" t="n">
-        <v>6800303</v>
+        <v>6800539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,9 +2519,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,22 +2546,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128804261</v>
+        <v>128805376</v>
       </c>
       <c r="B20" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2593,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456794</v>
+        <v>456589</v>
       </c>
       <c r="R20" t="n">
-        <v>6800605</v>
+        <v>6800567</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128805619</v>
+        <v>128814693</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456600</v>
+        <v>456515</v>
       </c>
       <c r="R21" t="n">
-        <v>6800539</v>
+        <v>6800380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,19 +2733,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2742,22 +2750,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128805376</v>
+        <v>128814715</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,7 +2800,7 @@
         <v>456589</v>
       </c>
       <c r="R22" t="n">
-        <v>6800567</v>
+        <v>6800303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,19 +2830,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128814654</v>
+        <v>128804261</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,42 +2870,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456705</v>
+        <v>456794</v>
       </c>
       <c r="R23" t="n">
-        <v>6800486</v>
+        <v>6800605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,9 +2927,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,12 +2954,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
         <v>128814616</v>
       </c>
       <c r="B24" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128814716</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>128805061</v>
       </c>
       <c r="B26" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128814703</v>
       </c>
       <c r="B27" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128814724</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814644</v>
+        <v>128814652</v>
       </c>
       <c r="B29" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456603</v>
+        <v>456781</v>
       </c>
       <c r="R29" t="n">
-        <v>6800371</v>
+        <v>6800644</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814652</v>
+        <v>128814644</v>
       </c>
       <c r="B30" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456781</v>
+        <v>456603</v>
       </c>
       <c r="R30" t="n">
-        <v>6800644</v>
+        <v>6800371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
         <v>128814673</v>
       </c>
       <c r="B31" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814720</v>
+        <v>128814692</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456446</v>
+        <v>456354</v>
       </c>
       <c r="R32" t="n">
-        <v>6800471</v>
+        <v>6800374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814692</v>
+        <v>128814626</v>
       </c>
       <c r="B33" t="n">
-        <v>78881</v>
+        <v>79648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456354</v>
+        <v>456763</v>
       </c>
       <c r="R33" t="n">
-        <v>6800374</v>
+        <v>6800617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814626</v>
+        <v>128814708</v>
       </c>
       <c r="B34" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456763</v>
+        <v>456702</v>
       </c>
       <c r="R34" t="n">
-        <v>6800617</v>
+        <v>6800512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814708</v>
+        <v>128814720</v>
       </c>
       <c r="B35" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456702</v>
+        <v>456446</v>
       </c>
       <c r="R35" t="n">
-        <v>6800512</v>
+        <v>6800471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814743</v>
+        <v>128804553</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456566</v>
+        <v>456768</v>
       </c>
       <c r="R36" t="n">
-        <v>6800498</v>
+        <v>6800626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,14 +4229,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,22 +4256,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128804553</v>
+        <v>128814689</v>
       </c>
       <c r="B37" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,21 +4279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456768</v>
+        <v>456495</v>
       </c>
       <c r="R37" t="n">
-        <v>6800626</v>
+        <v>6800433</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,19 +4336,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4358,22 +4353,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814689</v>
+        <v>128814743</v>
       </c>
       <c r="B38" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4381,21 +4376,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4405,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456495</v>
+        <v>456566</v>
       </c>
       <c r="R38" t="n">
-        <v>6800433</v>
+        <v>6800498</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4441,6 +4436,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4470,7 +4470,7 @@
         <v>128814727</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>128814710</v>
       </c>
       <c r="B40" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>128814711</v>
       </c>
       <c r="B41" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128814739</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>128814733</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>128805352</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>128805036</v>
       </c>
       <c r="B45" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>128799698</v>
       </c>
       <c r="B46" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>128801266</v>
       </c>
       <c r="B47" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>128814742</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>128814730</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>128805326</v>
       </c>
       <c r="B50" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128799275</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5793,10 +5793,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814612</v>
+        <v>128814648</v>
       </c>
       <c r="B52" t="n">
-        <v>79743</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5804,34 +5804,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456539</v>
+        <v>456618</v>
       </c>
       <c r="R52" t="n">
-        <v>6800496</v>
+        <v>6800564</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5890,10 +5898,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814719</v>
+        <v>128814612</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5901,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5925,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456527</v>
+        <v>456539</v>
       </c>
       <c r="R53" t="n">
-        <v>6800610</v>
+        <v>6800496</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5987,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814736</v>
+        <v>128814719</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6022,10 +6030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456569</v>
+        <v>456527</v>
       </c>
       <c r="R54" t="n">
-        <v>6800599</v>
+        <v>6800610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6084,10 +6092,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814620</v>
+        <v>128814736</v>
       </c>
       <c r="B55" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6095,37 +6103,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456385</v>
+        <v>456569</v>
       </c>
       <c r="R55" t="n">
-        <v>6800430</v>
+        <v>6800599</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6166,7 +6171,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6185,10 +6189,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814718</v>
+        <v>128814620</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6196,34 +6200,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456559</v>
+        <v>456385</v>
       </c>
       <c r="R56" t="n">
-        <v>6800586</v>
+        <v>6800430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6264,6 +6271,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6282,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814648</v>
+        <v>128814718</v>
       </c>
       <c r="B57" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6293,42 +6301,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456618</v>
+        <v>456559</v>
       </c>
       <c r="R57" t="n">
-        <v>6800564</v>
+        <v>6800586</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6390,7 +6390,7 @@
         <v>128802364</v>
       </c>
       <c r="B58" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128814734</v>
+        <v>128814735</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456472</v>
+        <v>456477</v>
       </c>
       <c r="R59" t="n">
-        <v>6800343</v>
+        <v>6800413</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6591,10 +6591,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814628</v>
+        <v>128814734</v>
       </c>
       <c r="B60" t="n">
-        <v>79714</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6602,21 +6602,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456549</v>
+        <v>456472</v>
       </c>
       <c r="R60" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6688,10 +6688,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128799700</v>
+        <v>128814628</v>
       </c>
       <c r="B61" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456668</v>
+        <v>456549</v>
       </c>
       <c r="R61" t="n">
-        <v>6800363</v>
+        <v>6800517</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6756,19 +6756,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,22 +6773,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128814735</v>
+        <v>128799700</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79619</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6806,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6830,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456477</v>
+        <v>456668</v>
       </c>
       <c r="R62" t="n">
-        <v>6800413</v>
+        <v>6800363</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6863,9 +6853,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,22 +6880,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128802133</v>
+        <v>128814675</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,34 +6903,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456775</v>
+        <v>456513</v>
       </c>
       <c r="R63" t="n">
-        <v>6800500</v>
+        <v>6800383</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,54 +6963,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128802369</v>
+        <v>128802133</v>
       </c>
       <c r="B64" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7015,21 +7004,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7039,10 +7028,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456718</v>
+        <v>456775</v>
       </c>
       <c r="R64" t="n">
-        <v>6800502</v>
+        <v>6800500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7085,6 +7074,11 @@
       <c r="AB64" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7111,10 +7105,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128814721</v>
+        <v>128802369</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7122,21 +7116,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7140,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456414</v>
+        <v>456718</v>
       </c>
       <c r="R65" t="n">
-        <v>6800442</v>
+        <v>6800502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7179,9 +7173,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7196,22 +7200,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128804576</v>
+        <v>128814721</v>
       </c>
       <c r="B66" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7219,39 +7223,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456761</v>
+        <v>456414</v>
       </c>
       <c r="R66" t="n">
-        <v>6800606</v>
+        <v>6800442</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7281,19 +7280,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7308,22 +7297,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128814656</v>
+        <v>128804576</v>
       </c>
       <c r="B67" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7349,24 +7338,21 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456658</v>
+        <v>456761</v>
       </c>
       <c r="R67" t="n">
-        <v>6800419</v>
+        <v>6800606</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7396,9 +7382,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7413,22 +7409,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128814660</v>
+        <v>128814656</v>
       </c>
       <c r="B68" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7454,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7468,10 +7464,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456747</v>
+        <v>456658</v>
       </c>
       <c r="R68" t="n">
-        <v>6800420</v>
+        <v>6800419</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7530,10 +7526,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128814675</v>
+        <v>128814660</v>
       </c>
       <c r="B69" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7541,26 +7537,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7568,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456513</v>
+        <v>456747</v>
       </c>
       <c r="R69" t="n">
-        <v>6800383</v>
+        <v>6800420</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,7 +7613,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>128799394</v>
       </c>
       <c r="B70" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7738,10 +7738,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814717</v>
+        <v>128814691</v>
       </c>
       <c r="B71" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456529</v>
+        <v>456385</v>
       </c>
       <c r="R71" t="n">
-        <v>6800501</v>
+        <v>6800430</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128814691</v>
+        <v>128814717</v>
       </c>
       <c r="B72" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,21 +7846,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>456385</v>
+        <v>456529</v>
       </c>
       <c r="R72" t="n">
-        <v>6800430</v>
+        <v>6800501</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7935,7 +7935,7 @@
         <v>128814707</v>
       </c>
       <c r="B73" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>128814714</v>
       </c>
       <c r="B74" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>128814697</v>
       </c>
       <c r="B75" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>128803330</v>
       </c>
       <c r="B76" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128814722</v>
+        <v>128800436</v>
       </c>
       <c r="B77" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456349</v>
+        <v>456671</v>
       </c>
       <c r="R77" t="n">
-        <v>6800436</v>
+        <v>6800350</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8398,9 +8398,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8415,22 +8425,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128800436</v>
+        <v>128814709</v>
       </c>
       <c r="B78" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8438,21 +8448,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8462,10 +8472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456671</v>
+        <v>456706</v>
       </c>
       <c r="R78" t="n">
-        <v>6800350</v>
+        <v>6800520</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8495,19 +8505,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,22 +8522,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814709</v>
+        <v>128814702</v>
       </c>
       <c r="B79" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456706</v>
+        <v>456788</v>
       </c>
       <c r="R79" t="n">
-        <v>6800520</v>
+        <v>6800626</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814702</v>
+        <v>128814722</v>
       </c>
       <c r="B80" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,21 +8642,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456788</v>
+        <v>456349</v>
       </c>
       <c r="R80" t="n">
-        <v>6800626</v>
+        <v>6800436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8731,7 +8731,7 @@
         <v>128814695</v>
       </c>
       <c r="B81" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>128814618</v>
       </c>
       <c r="B82" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>128800812</v>
       </c>
       <c r="B83" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>128814677</v>
       </c>
       <c r="B84" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>128801262</v>
       </c>
       <c r="B85" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814741</v>
+        <v>128814630</v>
       </c>
       <c r="B86" t="n">
-        <v>79124</v>
+        <v>79619</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456637</v>
+        <v>456496</v>
       </c>
       <c r="R86" t="n">
-        <v>6800536</v>
+        <v>6800554</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814726</v>
+        <v>128814741</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456524</v>
+        <v>456637</v>
       </c>
       <c r="R87" t="n">
-        <v>6800431</v>
+        <v>6800536</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814723</v>
+        <v>128814726</v>
       </c>
       <c r="B88" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456351</v>
+        <v>456524</v>
       </c>
       <c r="R88" t="n">
-        <v>6800371</v>
+        <v>6800431</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814630</v>
+        <v>128814723</v>
       </c>
       <c r="B89" t="n">
-        <v>79714</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456496</v>
+        <v>456351</v>
       </c>
       <c r="R89" t="n">
-        <v>6800554</v>
+        <v>6800371</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9629,7 +9629,7 @@
         <v>128814705</v>
       </c>
       <c r="B90" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>128814622</v>
       </c>
       <c r="B91" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>128814732</v>
       </c>
       <c r="B92" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>128814690</v>
       </c>
       <c r="B93" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>128814699</v>
       </c>
       <c r="B94" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>128814694</v>
       </c>
       <c r="B95" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>128804256</v>
       </c>
       <c r="B96" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10315,10 +10315,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814664</v>
+        <v>128814637</v>
       </c>
       <c r="B97" t="n">
-        <v>57717</v>
+        <v>57723</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10326,16 +10326,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456676</v>
+        <v>456352</v>
       </c>
       <c r="R97" t="n">
-        <v>6800380</v>
+        <v>6800325</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10423,7 +10423,7 @@
         <v>128799696</v>
       </c>
       <c r="B98" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128814637</v>
+        <v>128814664</v>
       </c>
       <c r="B99" t="n">
         <v>57720</v>
@@ -10538,16 +10538,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456352</v>
+        <v>456676</v>
       </c>
       <c r="R99" t="n">
-        <v>6800325</v>
+        <v>6800380</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10632,45 +10632,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128804050</v>
+        <v>128814713</v>
       </c>
       <c r="B100" t="n">
-        <v>79124</v>
+        <v>90895</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456753</v>
+        <v>456692</v>
       </c>
       <c r="R100" t="n">
-        <v>6800562</v>
+        <v>6800391</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10700,54 +10703,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805203</v>
+        <v>128805054</v>
       </c>
       <c r="B101" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10755,21 +10744,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10779,10 +10768,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456650</v>
+        <v>456690</v>
       </c>
       <c r="R101" t="n">
-        <v>6800594</v>
+        <v>6800603</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10851,10 +10840,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814737</v>
+        <v>128804050</v>
       </c>
       <c r="B102" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10886,10 +10875,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456555</v>
+        <v>456753</v>
       </c>
       <c r="R102" t="n">
-        <v>6800627</v>
+        <v>6800562</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,9 +10908,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10936,22 +10940,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814725</v>
+        <v>128805203</v>
       </c>
       <c r="B103" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10983,10 +10987,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456598</v>
+        <v>456650</v>
       </c>
       <c r="R103" t="n">
-        <v>6800407</v>
+        <v>6800594</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11016,14 +11020,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11038,22 +11047,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805054</v>
+        <v>128814698</v>
       </c>
       <c r="B104" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11061,21 +11070,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11085,10 +11094,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456690</v>
+        <v>456491</v>
       </c>
       <c r="R104" t="n">
-        <v>6800603</v>
+        <v>6800537</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11118,19 +11127,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11145,22 +11144,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814698</v>
+        <v>128814737</v>
       </c>
       <c r="B105" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11168,21 +11167,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11192,10 +11191,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456491</v>
+        <v>456555</v>
       </c>
       <c r="R105" t="n">
-        <v>6800537</v>
+        <v>6800627</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11257,7 +11256,7 @@
         <v>128814624</v>
       </c>
       <c r="B106" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11355,48 +11354,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814713</v>
+        <v>128814725</v>
       </c>
       <c r="B107" t="n">
-        <v>90890</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456692</v>
+        <v>456598</v>
       </c>
       <c r="R107" t="n">
-        <v>6800391</v>
+        <v>6800407</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11431,13 +11427,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>128814632</v>
       </c>
       <c r="B108" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128804554</v>
+        <v>128814683</v>
       </c>
       <c r="B109" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11582,16 +11582,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456768</v>
+        <v>456644</v>
       </c>
       <c r="R109" t="n">
-        <v>6800626</v>
+        <v>6800358</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11621,49 +11624,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814683</v>
+        <v>128804554</v>
       </c>
       <c r="B110" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11689,19 +11683,16 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456644</v>
+        <v>456768</v>
       </c>
       <c r="R110" t="n">
-        <v>6800358</v>
+        <v>6800626</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11731,30 +11722,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11764,7 +11764,7 @@
         <v>128805558</v>
       </c>
       <c r="B111" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>128814731</v>
       </c>
       <c r="B112" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>128814696</v>
       </c>
       <c r="B113" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>128803369</v>
       </c>
       <c r="B114" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>128814614</v>
       </c>
       <c r="B115" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>128814687</v>
       </c>
       <c r="B116" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814646</v>
+        <v>128814634</v>
       </c>
       <c r="B117" t="n">
-        <v>57717</v>
+        <v>57723</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12374,16 +12374,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12406,10 +12406,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456519</v>
+        <v>456405</v>
       </c>
       <c r="R117" t="n">
-        <v>6800414</v>
+        <v>6800457</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12468,10 +12468,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814634</v>
+        <v>128814679</v>
       </c>
       <c r="B118" t="n">
-        <v>57720</v>
+        <v>78787</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12479,42 +12479,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456405</v>
+        <v>456753</v>
       </c>
       <c r="R118" t="n">
-        <v>6800457</v>
+        <v>6800533</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12573,10 +12565,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814679</v>
+        <v>128814646</v>
       </c>
       <c r="B119" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12584,34 +12576,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456753</v>
+        <v>456519</v>
       </c>
       <c r="R119" t="n">
-        <v>6800533</v>
+        <v>6800414</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12673,7 +12673,7 @@
         <v>128805585</v>
       </c>
       <c r="B120" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>128814706</v>
       </c>
       <c r="B121" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>128804496</v>
       </c>
       <c r="B122" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>128814700</v>
       </c>
       <c r="B123" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>128816339</v>
       </c>
       <c r="B124" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>128816342</v>
       </c>
       <c r="B125" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>128816336</v>
       </c>
       <c r="B126" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816343</v>
+        <v>128816353</v>
       </c>
       <c r="B127" t="n">
-        <v>57720</v>
+        <v>78786</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,42 +13392,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456341</v>
+        <v>456522</v>
       </c>
       <c r="R127" t="n">
-        <v>6800306</v>
+        <v>6800357</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13489,7 +13481,7 @@
         <v>128816338</v>
       </c>
       <c r="B128" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13587,10 +13579,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816353</v>
+        <v>128816343</v>
       </c>
       <c r="B129" t="n">
-        <v>78881</v>
+        <v>57723</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13598,34 +13590,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456522</v>
+        <v>456341</v>
       </c>
       <c r="R129" t="n">
-        <v>6800357</v>
+        <v>6800306</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13687,7 +13687,7 @@
         <v>128816347</v>
       </c>
       <c r="B130" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>128816349</v>
       </c>
       <c r="B131" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>128816354</v>
       </c>
       <c r="B132" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>128816356</v>
       </c>
       <c r="B133" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>128816351</v>
       </c>
       <c r="B134" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>128816340</v>
       </c>
       <c r="B135" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14278,10 +14278,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128816335</v>
+        <v>128816331</v>
       </c>
       <c r="B136" t="n">
-        <v>79743</v>
+        <v>79061</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14289,34 +14289,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>456564</v>
+        <v>456376</v>
       </c>
       <c r="R136" t="n">
-        <v>6800617</v>
+        <v>6800472</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14357,6 +14360,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14375,10 +14379,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128816331</v>
+        <v>128816335</v>
       </c>
       <c r="B137" t="n">
-        <v>79156</v>
+        <v>79648</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14386,37 +14390,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>456376</v>
+        <v>456564</v>
       </c>
       <c r="R137" t="n">
-        <v>6800472</v>
+        <v>6800617</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14457,7 +14458,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14476,10 +14476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128816352</v>
+        <v>128816348</v>
       </c>
       <c r="B138" t="n">
-        <v>78881</v>
+        <v>78787</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14487,37 +14487,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>456483</v>
+        <v>456703</v>
       </c>
       <c r="R138" t="n">
-        <v>6800432</v>
+        <v>6800475</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14558,7 +14555,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14577,10 +14573,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128816348</v>
+        <v>128816352</v>
       </c>
       <c r="B139" t="n">
-        <v>78882</v>
+        <v>78786</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14588,34 +14584,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456703</v>
+        <v>456483</v>
       </c>
       <c r="R139" t="n">
-        <v>6800475</v>
+        <v>6800432</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14656,6 +14655,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14677,7 +14677,7 @@
         <v>128816350</v>
       </c>
       <c r="B140" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>128816334</v>
       </c>
       <c r="B141" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>128816358</v>
       </c>
       <c r="B142" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>128816361</v>
       </c>
       <c r="B143" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15066,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816359</v>
+        <v>128816332</v>
       </c>
       <c r="B144" t="n">
-        <v>79124</v>
+        <v>79061</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15077,34 +15077,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456335</v>
+        <v>456355</v>
       </c>
       <c r="R144" t="n">
-        <v>6800427</v>
+        <v>6800454</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15145,6 +15148,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15163,10 +15167,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816345</v>
+        <v>128816359</v>
       </c>
       <c r="B145" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15174,42 +15178,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456606</v>
+        <v>456335</v>
       </c>
       <c r="R145" t="n">
-        <v>6800517</v>
+        <v>6800427</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15268,10 +15264,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816332</v>
+        <v>128816345</v>
       </c>
       <c r="B146" t="n">
-        <v>79156</v>
+        <v>57720</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15279,26 +15275,31 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15306,10 +15307,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456355</v>
+        <v>456606</v>
       </c>
       <c r="R146" t="n">
-        <v>6800454</v>
+        <v>6800517</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15350,7 +15351,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15372,7 +15372,7 @@
         <v>128816333</v>
       </c>
       <c r="B147" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>128816346</v>
       </c>
       <c r="B148" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>128816341</v>
       </c>
       <c r="B149" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>128816337</v>
       </c>
       <c r="B150" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>128816360</v>
       </c>
       <c r="B151" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128814701</v>
+        <v>128800923</v>
       </c>
       <c r="B2" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456547</v>
+        <v>456692</v>
       </c>
       <c r="R2" t="n">
-        <v>6800436</v>
+        <v>6800405</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128800923</v>
+        <v>128799069</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456692</v>
+        <v>456632</v>
       </c>
       <c r="R3" t="n">
-        <v>6800405</v>
+        <v>6800431</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +873,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128799069</v>
+        <v>128814701</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>78791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456632</v>
+        <v>456547</v>
       </c>
       <c r="R4" t="n">
-        <v>6800431</v>
+        <v>6800436</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +967,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,44 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128803579</v>
+        <v>128803425</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456698</v>
+        <v>456681</v>
       </c>
       <c r="R5" t="n">
-        <v>6800503</v>
+        <v>6800496</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1077,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128805128</v>
+        <v>128801339</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456660</v>
+        <v>456742</v>
       </c>
       <c r="R6" t="n">
-        <v>6800603</v>
+        <v>6800421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128814728</v>
+        <v>128803579</v>
       </c>
       <c r="B7" t="n">
         <v>79034</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456616</v>
+        <v>456698</v>
       </c>
       <c r="R7" t="n">
-        <v>6800533</v>
+        <v>6800503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,9 +1278,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,22 +1310,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128814658</v>
+        <v>128805128</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,42 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456645</v>
+        <v>456660</v>
       </c>
       <c r="R8" t="n">
-        <v>6800444</v>
+        <v>6800603</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,9 +1390,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,44 +1417,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128803425</v>
+        <v>128814728</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456681</v>
+        <v>456616</v>
       </c>
       <c r="R9" t="n">
-        <v>6800496</v>
+        <v>6800533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,19 +1497,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,22 +1514,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128801339</v>
+        <v>128814640</v>
       </c>
       <c r="B10" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,34 +1537,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456742</v>
+        <v>456331</v>
       </c>
       <c r="R10" t="n">
-        <v>6800421</v>
+        <v>6800312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,19 +1602,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,22 +1619,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128814640</v>
+        <v>128814658</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1664,7 +1664,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456331</v>
+        <v>456645</v>
       </c>
       <c r="R11" t="n">
-        <v>6800312</v>
+        <v>6800444</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128804638</v>
+        <v>128814744</v>
       </c>
       <c r="B15" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456748</v>
+        <v>456737</v>
       </c>
       <c r="R15" t="n">
-        <v>6800617</v>
+        <v>6800417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,19 +2113,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,22 +2130,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814744</v>
+        <v>128814693</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456737</v>
+        <v>456515</v>
       </c>
       <c r="R16" t="n">
-        <v>6800417</v>
+        <v>6800380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2764,10 +2754,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814693</v>
+        <v>128804638</v>
       </c>
       <c r="B22" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,21 +2765,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2799,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456515</v>
+        <v>456748</v>
       </c>
       <c r="R22" t="n">
-        <v>6800380</v>
+        <v>6800617</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,9 +2822,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,12 +2849,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128814735</v>
+        <v>128799700</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456477</v>
+        <v>456668</v>
       </c>
       <c r="R59" t="n">
-        <v>6800413</v>
+        <v>6800363</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,9 +6562,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6579,19 +6589,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814734</v>
+        <v>128814735</v>
       </c>
       <c r="B60" t="n">
         <v>79034</v>
@@ -6626,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456472</v>
+        <v>456477</v>
       </c>
       <c r="R60" t="n">
-        <v>6800343</v>
+        <v>6800413</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6688,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128799700</v>
+        <v>128814734</v>
       </c>
       <c r="B61" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6699,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6723,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456668</v>
+        <v>456472</v>
       </c>
       <c r="R61" t="n">
-        <v>6800363</v>
+        <v>6800343</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6756,19 +6766,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,12 +6783,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128802133</v>
+        <v>128802369</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456775</v>
+        <v>456718</v>
       </c>
       <c r="R63" t="n">
-        <v>6800500</v>
+        <v>6800502</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6973,11 +6973,6 @@
       <c r="AB63" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7004,10 +6999,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128814721</v>
+        <v>128804576</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7015,34 +7010,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456414</v>
+        <v>456761</v>
       </c>
       <c r="R64" t="n">
-        <v>6800442</v>
+        <v>6800606</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7072,9 +7072,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7089,19 +7099,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128804576</v>
+        <v>128814656</v>
       </c>
       <c r="B65" t="n">
         <v>57720</v>
@@ -7130,21 +7140,24 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456761</v>
+        <v>456658</v>
       </c>
       <c r="R65" t="n">
-        <v>6800606</v>
+        <v>6800419</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,19 +7187,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7201,19 +7204,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128814656</v>
+        <v>128814660</v>
       </c>
       <c r="B66" t="n">
         <v>57720</v>
@@ -7246,7 +7249,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7256,10 +7259,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456658</v>
+        <v>456747</v>
       </c>
       <c r="R66" t="n">
-        <v>6800419</v>
+        <v>6800420</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7318,10 +7321,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128814660</v>
+        <v>128814675</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,31 +7332,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7361,10 +7359,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456747</v>
+        <v>456513</v>
       </c>
       <c r="R67" t="n">
-        <v>6800420</v>
+        <v>6800383</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,6 +7403,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7423,10 +7422,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128802369</v>
+        <v>128802133</v>
       </c>
       <c r="B68" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7434,21 +7433,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7458,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456718</v>
+        <v>456775</v>
       </c>
       <c r="R68" t="n">
-        <v>6800502</v>
+        <v>6800500</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7504,6 +7503,11 @@
       <c r="AB68" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7530,10 +7534,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128814675</v>
+        <v>128814721</v>
       </c>
       <c r="B69" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7541,37 +7545,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456513</v>
+        <v>456414</v>
       </c>
       <c r="R69" t="n">
-        <v>6800383</v>
+        <v>6800442</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,7 +7613,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814717</v>
+        <v>128803330</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456529</v>
+        <v>456690</v>
       </c>
       <c r="R73" t="n">
-        <v>6800501</v>
+        <v>6800454</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7990,9 +7990,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8007,22 +8017,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128814714</v>
+        <v>128799394</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>91470</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,21 +8040,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8054,10 +8064,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456599</v>
+        <v>456679</v>
       </c>
       <c r="R74" t="n">
-        <v>6800361</v>
+        <v>6800380</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8087,9 +8097,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8104,22 +8124,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128803330</v>
+        <v>128814717</v>
       </c>
       <c r="B75" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,21 +8147,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8151,10 +8171,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456690</v>
+        <v>456529</v>
       </c>
       <c r="R75" t="n">
-        <v>6800454</v>
+        <v>6800501</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,19 +8204,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8211,22 +8221,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128799394</v>
+        <v>128814714</v>
       </c>
       <c r="B76" t="n">
-        <v>91470</v>
+        <v>79034</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8234,21 +8244,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8258,10 +8268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456679</v>
+        <v>456599</v>
       </c>
       <c r="R76" t="n">
-        <v>6800380</v>
+        <v>6800361</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8291,19 +8301,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,22 +8318,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128800436</v>
+        <v>128814722</v>
       </c>
       <c r="B77" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456671</v>
+        <v>456349</v>
       </c>
       <c r="R77" t="n">
-        <v>6800350</v>
+        <v>6800436</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8398,19 +8398,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8425,12 +8415,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8534,7 +8524,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814702</v>
+        <v>128814695</v>
       </c>
       <c r="B79" t="n">
         <v>78791</v>
@@ -8569,10 +8559,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456788</v>
+        <v>456547</v>
       </c>
       <c r="R79" t="n">
-        <v>6800626</v>
+        <v>6800403</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,10 +8621,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814695</v>
+        <v>128814618</v>
       </c>
       <c r="B80" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,21 +8632,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8666,10 +8656,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456547</v>
+        <v>456450</v>
       </c>
       <c r="R80" t="n">
-        <v>6800403</v>
+        <v>6800571</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8728,7 +8718,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814618</v>
+        <v>128800436</v>
       </c>
       <c r="B81" t="n">
         <v>79653</v>
@@ -8763,10 +8753,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456450</v>
+        <v>456671</v>
       </c>
       <c r="R81" t="n">
-        <v>6800571</v>
+        <v>6800350</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8796,9 +8786,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8813,22 +8813,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814677</v>
+        <v>128814702</v>
       </c>
       <c r="B82" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456747</v>
+        <v>456788</v>
       </c>
       <c r="R82" t="n">
-        <v>6800569</v>
+        <v>6800626</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8922,48 +8922,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128801262</v>
+        <v>128800812</v>
       </c>
       <c r="B83" t="n">
-        <v>78792</v>
+        <v>58093</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456703</v>
+        <v>456691</v>
       </c>
       <c r="R83" t="n">
-        <v>6800429</v>
+        <v>6800368</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9029,10 +9034,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814722</v>
+        <v>128814677</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9040,21 +9045,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9064,10 +9069,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456349</v>
+        <v>456747</v>
       </c>
       <c r="R84" t="n">
-        <v>6800436</v>
+        <v>6800569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9126,53 +9131,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128800812</v>
+        <v>128801262</v>
       </c>
       <c r="B85" t="n">
-        <v>58093</v>
+        <v>78792</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456691</v>
+        <v>456703</v>
       </c>
       <c r="R85" t="n">
-        <v>6800368</v>
+        <v>6800429</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814630</v>
+        <v>128814741</v>
       </c>
       <c r="B86" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456496</v>
+        <v>456637</v>
       </c>
       <c r="R86" t="n">
-        <v>6800554</v>
+        <v>6800536</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814741</v>
+        <v>128814726</v>
       </c>
       <c r="B87" t="n">
         <v>79034</v>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456637</v>
+        <v>456524</v>
       </c>
       <c r="R87" t="n">
-        <v>6800536</v>
+        <v>6800431</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814726</v>
+        <v>128814723</v>
       </c>
       <c r="B88" t="n">
         <v>79034</v>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456524</v>
+        <v>456351</v>
       </c>
       <c r="R88" t="n">
-        <v>6800431</v>
+        <v>6800371</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814723</v>
+        <v>128814630</v>
       </c>
       <c r="B89" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456351</v>
+        <v>456496</v>
       </c>
       <c r="R89" t="n">
-        <v>6800371</v>
+        <v>6800554</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10632,48 +10632,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128814713</v>
+        <v>128814632</v>
       </c>
       <c r="B100" t="n">
-        <v>90902</v>
+        <v>79624</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5685</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456692</v>
+        <v>456382</v>
       </c>
       <c r="R100" t="n">
-        <v>6800391</v>
+        <v>6800427</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10714,7 +10711,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10733,10 +10729,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805054</v>
+        <v>128804554</v>
       </c>
       <c r="B101" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10744,21 +10740,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10768,10 +10764,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456690</v>
+        <v>456768</v>
       </c>
       <c r="R101" t="n">
-        <v>6800603</v>
+        <v>6800626</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10840,10 +10836,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814698</v>
+        <v>128814683</v>
       </c>
       <c r="B102" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10851,34 +10847,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456491</v>
+        <v>456644</v>
       </c>
       <c r="R102" t="n">
-        <v>6800537</v>
+        <v>6800358</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,6 +10918,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10937,32 +10937,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814624</v>
+        <v>128814713</v>
       </c>
       <c r="B103" t="n">
-        <v>79653</v>
+        <v>90902</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456688</v>
+        <v>456692</v>
       </c>
       <c r="R103" t="n">
-        <v>6800585</v>
+        <v>6800391</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128804050</v>
+        <v>128805054</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456753</v>
+        <v>456690</v>
       </c>
       <c r="R104" t="n">
-        <v>6800562</v>
+        <v>6800603</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11119,11 +11119,6 @@
       <c r="AB104" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11150,10 +11145,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128805203</v>
+        <v>128814698</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11161,21 +11156,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11185,10 +11180,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456650</v>
+        <v>456491</v>
       </c>
       <c r="R105" t="n">
-        <v>6800594</v>
+        <v>6800537</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11218,19 +11213,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11245,22 +11230,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814737</v>
+        <v>128814624</v>
       </c>
       <c r="B106" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11268,34 +11253,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456555</v>
+        <v>456688</v>
       </c>
       <c r="R106" t="n">
-        <v>6800627</v>
+        <v>6800585</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11336,6 +11324,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11354,7 +11343,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814725</v>
+        <v>128804050</v>
       </c>
       <c r="B107" t="n">
         <v>79034</v>
@@ -11389,10 +11378,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456598</v>
+        <v>456753</v>
       </c>
       <c r="R107" t="n">
-        <v>6800407</v>
+        <v>6800562</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11422,14 +11411,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11444,22 +11443,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128814632</v>
+        <v>128805203</v>
       </c>
       <c r="B108" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11467,21 +11466,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11491,10 +11490,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456382</v>
+        <v>456650</v>
       </c>
       <c r="R108" t="n">
-        <v>6800427</v>
+        <v>6800594</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11524,9 +11523,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11541,22 +11550,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128804554</v>
+        <v>128814737</v>
       </c>
       <c r="B109" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11564,21 +11573,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11588,10 +11597,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456768</v>
+        <v>456555</v>
       </c>
       <c r="R109" t="n">
-        <v>6800626</v>
+        <v>6800627</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11621,19 +11630,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11648,22 +11647,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814683</v>
+        <v>128814725</v>
       </c>
       <c r="B110" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11671,37 +11670,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456644</v>
+        <v>456598</v>
       </c>
       <c r="R110" t="n">
-        <v>6800358</v>
+        <v>6800407</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11736,13 +11732,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12062,10 +12062,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814687</v>
+        <v>128814634</v>
       </c>
       <c r="B114" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12073,34 +12073,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456556</v>
+        <v>456405</v>
       </c>
       <c r="R114" t="n">
-        <v>6800320</v>
+        <v>6800457</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12159,10 +12167,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814634</v>
+        <v>128814646</v>
       </c>
       <c r="B115" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12170,16 +12178,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12202,10 +12210,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456405</v>
+        <v>456519</v>
       </c>
       <c r="R115" t="n">
-        <v>6800457</v>
+        <v>6800414</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12264,10 +12272,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814679</v>
+        <v>128805558</v>
       </c>
       <c r="B116" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12275,21 +12283,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12299,10 +12307,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456753</v>
+        <v>456627</v>
       </c>
       <c r="R116" t="n">
-        <v>6800533</v>
+        <v>6800521</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12332,9 +12340,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12349,19 +12367,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128805558</v>
+        <v>128814731</v>
       </c>
       <c r="B117" t="n">
         <v>79034</v>
@@ -12396,10 +12414,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456627</v>
+        <v>456580</v>
       </c>
       <c r="R117" t="n">
-        <v>6800521</v>
+        <v>6800292</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12429,19 +12447,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12456,22 +12464,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814731</v>
+        <v>128814687</v>
       </c>
       <c r="B118" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12479,21 +12487,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12503,10 +12511,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456580</v>
+        <v>456556</v>
       </c>
       <c r="R118" t="n">
-        <v>6800292</v>
+        <v>6800320</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12565,10 +12573,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814646</v>
+        <v>128814679</v>
       </c>
       <c r="B119" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12576,42 +12584,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456519</v>
+        <v>456753</v>
       </c>
       <c r="R119" t="n">
-        <v>6800414</v>
+        <v>6800533</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15369,10 +15369,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128816333</v>
+        <v>128816346</v>
       </c>
       <c r="B147" t="n">
-        <v>79066</v>
+        <v>78792</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15380,34 +15380,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>456756</v>
+        <v>456521</v>
       </c>
       <c r="R147" t="n">
-        <v>6800522</v>
+        <v>6800343</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15448,6 +15451,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15466,10 +15470,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128816346</v>
+        <v>128816333</v>
       </c>
       <c r="B148" t="n">
-        <v>78792</v>
+        <v>79066</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15477,37 +15481,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>456521</v>
+        <v>456756</v>
       </c>
       <c r="R148" t="n">
-        <v>6800343</v>
+        <v>6800522</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15548,7 +15549,6 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128800923</v>
+        <v>128799069</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456692</v>
+        <v>456632</v>
       </c>
       <c r="R2" t="n">
-        <v>6800405</v>
+        <v>6800431</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +761,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128799069</v>
+        <v>128814701</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>78791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456632</v>
+        <v>456547</v>
       </c>
       <c r="R3" t="n">
-        <v>6800431</v>
+        <v>6800436</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +855,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128814701</v>
+        <v>128800923</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456547</v>
+        <v>456692</v>
       </c>
       <c r="R4" t="n">
-        <v>6800436</v>
+        <v>6800405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,9 +952,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128801339</v>
+        <v>128814640</v>
       </c>
       <c r="B6" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1114,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456742</v>
+        <v>456331</v>
       </c>
       <c r="R6" t="n">
-        <v>6800421</v>
+        <v>6800312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,19 +1179,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,12 +1196,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1322,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128805128</v>
+        <v>128801339</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456660</v>
+        <v>456742</v>
       </c>
       <c r="R8" t="n">
-        <v>6800603</v>
+        <v>6800421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814728</v>
+        <v>128805128</v>
       </c>
       <c r="B9" t="n">
         <v>79034</v>
@@ -1464,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456616</v>
+        <v>456660</v>
       </c>
       <c r="R9" t="n">
-        <v>6800533</v>
+        <v>6800603</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,9 +1495,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,22 +1522,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814640</v>
+        <v>128814728</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,42 +1545,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456331</v>
+        <v>456616</v>
       </c>
       <c r="R10" t="n">
-        <v>6800312</v>
+        <v>6800533</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814681</v>
+        <v>128814666</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,34 +1747,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456761</v>
+        <v>456659</v>
       </c>
       <c r="R12" t="n">
-        <v>6800515</v>
+        <v>6800402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814666</v>
+        <v>128804672</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,42 +1852,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456659</v>
+        <v>456733</v>
       </c>
       <c r="R13" t="n">
-        <v>6800402</v>
+        <v>6800618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,9 +1909,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1926,22 +1936,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128804672</v>
+        <v>128814681</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456733</v>
+        <v>456761</v>
       </c>
       <c r="R14" t="n">
-        <v>6800618</v>
+        <v>6800515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,19 +2016,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2033,22 +2033,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814744</v>
+        <v>128814654</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,34 +2056,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456737</v>
+        <v>456705</v>
       </c>
       <c r="R15" t="n">
-        <v>6800417</v>
+        <v>6800486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814693</v>
+        <v>128814744</v>
       </c>
       <c r="B16" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,21 +2161,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456515</v>
+        <v>456737</v>
       </c>
       <c r="R16" t="n">
-        <v>6800380</v>
+        <v>6800417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814729</v>
+        <v>128804638</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2258,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456606</v>
+        <v>456748</v>
       </c>
       <c r="R17" t="n">
-        <v>6800334</v>
+        <v>6800617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,9 +2315,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,19 +2342,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128805619</v>
+        <v>128814729</v>
       </c>
       <c r="B18" t="n">
         <v>79034</v>
@@ -2371,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456600</v>
+        <v>456606</v>
       </c>
       <c r="R18" t="n">
-        <v>6800539</v>
+        <v>6800334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,19 +2422,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,19 +2439,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805376</v>
+        <v>128805619</v>
       </c>
       <c r="B19" t="n">
         <v>79034</v>
@@ -2478,10 +2486,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456589</v>
+        <v>456600</v>
       </c>
       <c r="R19" t="n">
-        <v>6800567</v>
+        <v>6800539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,7 +2558,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128814715</v>
+        <v>128805376</v>
       </c>
       <c r="B20" t="n">
         <v>79034</v>
@@ -2588,7 +2596,7 @@
         <v>456589</v>
       </c>
       <c r="R20" t="n">
-        <v>6800303</v>
+        <v>6800567</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,9 +2626,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,22 +2653,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128804261</v>
+        <v>128814693</v>
       </c>
       <c r="B21" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456794</v>
+        <v>456515</v>
       </c>
       <c r="R21" t="n">
-        <v>6800605</v>
+        <v>6800380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,19 +2733,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2742,22 +2750,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128804638</v>
+        <v>128814715</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,21 +2773,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2789,10 +2797,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456748</v>
+        <v>456589</v>
       </c>
       <c r="R22" t="n">
-        <v>6800617</v>
+        <v>6800303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,19 +2830,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128814654</v>
+        <v>128804261</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,42 +2870,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456705</v>
+        <v>456794</v>
       </c>
       <c r="R23" t="n">
-        <v>6800486</v>
+        <v>6800605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,9 +2927,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,22 +2954,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814616</v>
+        <v>128814673</v>
       </c>
       <c r="B24" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456487</v>
+        <v>456469</v>
       </c>
       <c r="R24" t="n">
-        <v>6800546</v>
+        <v>6800542</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128805061</v>
+        <v>128814616</v>
       </c>
       <c r="B25" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456690</v>
+        <v>456487</v>
       </c>
       <c r="R25" t="n">
-        <v>6800603</v>
+        <v>6800546</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,19 +3131,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,22 +3148,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814703</v>
+        <v>128814716</v>
       </c>
       <c r="B26" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3181,21 +3171,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3205,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456766</v>
+        <v>456477</v>
       </c>
       <c r="R26" t="n">
-        <v>6800611</v>
+        <v>6800324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3241,6 +3231,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3267,10 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814716</v>
+        <v>128805061</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,21 +3273,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3302,10 +3297,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456477</v>
+        <v>456690</v>
       </c>
       <c r="R27" t="n">
-        <v>6800324</v>
+        <v>6800603</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,14 +3330,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3357,22 +3357,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814724</v>
+        <v>128814703</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456520</v>
+        <v>456766</v>
       </c>
       <c r="R28" t="n">
-        <v>6800367</v>
+        <v>6800611</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814673</v>
+        <v>128814724</v>
       </c>
       <c r="B29" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456469</v>
+        <v>456520</v>
       </c>
       <c r="R29" t="n">
-        <v>6800542</v>
+        <v>6800367</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814743</v>
+        <v>128804553</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456566</v>
+        <v>456768</v>
       </c>
       <c r="R36" t="n">
-        <v>6800498</v>
+        <v>6800626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,14 +4229,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,22 +4256,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814727</v>
+        <v>128814689</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,21 +4279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456600</v>
+        <v>456495</v>
       </c>
       <c r="R37" t="n">
-        <v>6800519</v>
+        <v>6800433</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,10 +4365,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128804553</v>
+        <v>128814743</v>
       </c>
       <c r="B38" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,21 +4376,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4395,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456768</v>
+        <v>456566</v>
       </c>
       <c r="R38" t="n">
-        <v>6800626</v>
+        <v>6800498</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4428,19 +4433,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,22 +4455,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814689</v>
+        <v>128814727</v>
       </c>
       <c r="B39" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456495</v>
+        <v>456600</v>
       </c>
       <c r="R39" t="n">
-        <v>6800433</v>
+        <v>6800519</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B46" t="n">
         <v>79653</v>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R46" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B47" t="n">
         <v>79653</v>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R47" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128799275</v>
+        <v>128814612</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,21 +5692,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456665</v>
+        <v>456539</v>
       </c>
       <c r="R51" t="n">
-        <v>6800399</v>
+        <v>6800496</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,24 +5749,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5781,22 +5766,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814612</v>
+        <v>128814719</v>
       </c>
       <c r="B52" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5804,21 +5789,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5828,10 +5813,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456539</v>
+        <v>456527</v>
       </c>
       <c r="R52" t="n">
-        <v>6800496</v>
+        <v>6800610</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5890,10 +5875,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814620</v>
+        <v>128814736</v>
       </c>
       <c r="B53" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5901,37 +5886,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456385</v>
+        <v>456569</v>
       </c>
       <c r="R53" t="n">
-        <v>6800430</v>
+        <v>6800599</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5972,7 +5954,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5991,10 +5972,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814719</v>
+        <v>128814620</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6002,34 +5983,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456527</v>
+        <v>456385</v>
       </c>
       <c r="R54" t="n">
-        <v>6800610</v>
+        <v>6800430</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6070,6 +6054,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6088,7 +6073,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814736</v>
+        <v>128814718</v>
       </c>
       <c r="B55" t="n">
         <v>79034</v>
@@ -6123,10 +6108,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456569</v>
+        <v>456559</v>
       </c>
       <c r="R55" t="n">
-        <v>6800599</v>
+        <v>6800586</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6185,10 +6170,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814718</v>
+        <v>128802364</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6196,21 +6181,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6220,10 +6205,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456559</v>
+        <v>456718</v>
       </c>
       <c r="R56" t="n">
-        <v>6800586</v>
+        <v>6800502</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6253,9 +6238,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6270,22 +6265,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128802364</v>
+        <v>128799275</v>
       </c>
       <c r="B57" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6293,21 +6288,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6317,10 +6312,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456718</v>
+        <v>456665</v>
       </c>
       <c r="R57" t="n">
-        <v>6800502</v>
+        <v>6800399</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6363,6 +6358,11 @@
       <c r="AB57" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6892,10 +6892,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128802369</v>
+        <v>128814675</v>
       </c>
       <c r="B63" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,34 +6903,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456718</v>
+        <v>456513</v>
       </c>
       <c r="R63" t="n">
-        <v>6800502</v>
+        <v>6800383</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,49 +6963,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128804576</v>
+        <v>128802133</v>
       </c>
       <c r="B64" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7010,39 +7004,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456761</v>
+        <v>456775</v>
       </c>
       <c r="R64" t="n">
-        <v>6800606</v>
+        <v>6800500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7085,6 +7074,11 @@
       <c r="AB64" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7111,10 +7105,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128814656</v>
+        <v>128802369</v>
       </c>
       <c r="B65" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7122,42 +7116,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456658</v>
+        <v>456718</v>
       </c>
       <c r="R65" t="n">
-        <v>6800419</v>
+        <v>6800502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7187,9 +7173,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7204,22 +7200,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128814660</v>
+        <v>128814721</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7227,42 +7223,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456747</v>
+        <v>456414</v>
       </c>
       <c r="R66" t="n">
-        <v>6800420</v>
+        <v>6800442</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7321,10 +7309,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128814675</v>
+        <v>128804576</v>
       </c>
       <c r="B67" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7332,37 +7320,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456513</v>
+        <v>456761</v>
       </c>
       <c r="R67" t="n">
-        <v>6800383</v>
+        <v>6800606</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7392,40 +7382,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128802133</v>
+        <v>128814656</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7433,34 +7432,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456775</v>
+        <v>456658</v>
       </c>
       <c r="R68" t="n">
-        <v>6800500</v>
+        <v>6800419</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7490,24 +7497,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7522,22 +7514,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128814721</v>
+        <v>128814660</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7545,34 +7537,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456414</v>
+        <v>456747</v>
       </c>
       <c r="R69" t="n">
-        <v>6800442</v>
+        <v>6800420</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814707</v>
+        <v>128814717</v>
       </c>
       <c r="B71" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7739,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456665</v>
+        <v>456529</v>
       </c>
       <c r="R71" t="n">
-        <v>6800450</v>
+        <v>6800501</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128814697</v>
+        <v>128814707</v>
       </c>
       <c r="B72" t="n">
         <v>78791</v>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>456499</v>
+        <v>456665</v>
       </c>
       <c r="R72" t="n">
-        <v>6800562</v>
+        <v>6800450</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128803330</v>
+        <v>128814714</v>
       </c>
       <c r="B73" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456690</v>
+        <v>456599</v>
       </c>
       <c r="R73" t="n">
-        <v>6800454</v>
+        <v>6800361</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7990,19 +7990,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8017,22 +8007,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128799394</v>
+        <v>128814697</v>
       </c>
       <c r="B74" t="n">
-        <v>91470</v>
+        <v>78791</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8040,21 +8030,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8064,10 +8054,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456679</v>
+        <v>456499</v>
       </c>
       <c r="R74" t="n">
-        <v>6800380</v>
+        <v>6800562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8097,19 +8087,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8124,22 +8104,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128814717</v>
+        <v>128799394</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>91473</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8147,21 +8127,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8171,10 +8151,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456529</v>
+        <v>456679</v>
       </c>
       <c r="R75" t="n">
-        <v>6800501</v>
+        <v>6800380</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8204,9 +8184,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8221,22 +8211,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128814714</v>
+        <v>128803330</v>
       </c>
       <c r="B76" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8244,21 +8234,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8268,10 +8258,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456599</v>
+        <v>456690</v>
       </c>
       <c r="R76" t="n">
-        <v>6800361</v>
+        <v>6800454</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,9 +8291,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8318,60 +8318,65 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128814722</v>
+        <v>128800812</v>
       </c>
       <c r="B77" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456349</v>
+        <v>456691</v>
       </c>
       <c r="R77" t="n">
-        <v>6800436</v>
+        <v>6800368</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8398,9 +8403,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8415,22 +8430,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128814709</v>
+        <v>128814677</v>
       </c>
       <c r="B78" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8438,21 +8453,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8462,10 +8477,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456706</v>
+        <v>456747</v>
       </c>
       <c r="R78" t="n">
-        <v>6800520</v>
+        <v>6800569</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8524,10 +8539,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814695</v>
+        <v>128801262</v>
       </c>
       <c r="B79" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8535,21 +8550,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8559,10 +8574,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456547</v>
+        <v>456703</v>
       </c>
       <c r="R79" t="n">
-        <v>6800403</v>
+        <v>6800429</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8592,9 +8607,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8609,19 +8634,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814618</v>
+        <v>128800436</v>
       </c>
       <c r="B80" t="n">
         <v>79653</v>
@@ -8656,10 +8681,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456450</v>
+        <v>456671</v>
       </c>
       <c r="R80" t="n">
-        <v>6800571</v>
+        <v>6800350</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,9 +8714,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8706,22 +8741,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128800436</v>
+        <v>128814709</v>
       </c>
       <c r="B81" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8729,21 +8764,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8753,10 +8788,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456671</v>
+        <v>456706</v>
       </c>
       <c r="R81" t="n">
-        <v>6800350</v>
+        <v>6800520</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,19 +8821,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8813,12 +8838,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8922,53 +8947,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128800812</v>
+        <v>128814722</v>
       </c>
       <c r="B83" t="n">
-        <v>58093</v>
+        <v>79034</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456691</v>
+        <v>456349</v>
       </c>
       <c r="R83" t="n">
-        <v>6800368</v>
+        <v>6800436</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8995,19 +9015,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9022,22 +9032,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814677</v>
+        <v>128814695</v>
       </c>
       <c r="B84" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9045,21 +9055,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9069,10 +9079,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456747</v>
+        <v>456547</v>
       </c>
       <c r="R84" t="n">
-        <v>6800569</v>
+        <v>6800403</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9131,10 +9141,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128801262</v>
+        <v>128814618</v>
       </c>
       <c r="B85" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9142,21 +9152,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9166,10 +9176,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456703</v>
+        <v>456450</v>
       </c>
       <c r="R85" t="n">
-        <v>6800429</v>
+        <v>6800571</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9199,19 +9209,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9226,12 +9226,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128799696</v>
+        <v>128814664</v>
       </c>
       <c r="B90" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,34 +9637,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456668</v>
+        <v>456676</v>
       </c>
       <c r="R90" t="n">
-        <v>6800363</v>
+        <v>6800380</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9694,19 +9702,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9721,12 +9719,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9927,10 +9925,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814690</v>
+        <v>128814732</v>
       </c>
       <c r="B93" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9938,21 +9936,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9962,10 +9960,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456465</v>
+        <v>456571</v>
       </c>
       <c r="R93" t="n">
-        <v>6800546</v>
+        <v>6800296</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10024,7 +10022,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814699</v>
+        <v>128814690</v>
       </c>
       <c r="B94" t="n">
         <v>78791</v>
@@ -10059,10 +10057,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456496</v>
+        <v>456465</v>
       </c>
       <c r="R94" t="n">
-        <v>6800549</v>
+        <v>6800546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10121,7 +10119,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814694</v>
+        <v>128814699</v>
       </c>
       <c r="B95" t="n">
         <v>78791</v>
@@ -10156,10 +10154,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456594</v>
+        <v>456496</v>
       </c>
       <c r="R95" t="n">
-        <v>6800423</v>
+        <v>6800549</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,10 +10216,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128804256</v>
+        <v>128814694</v>
       </c>
       <c r="B96" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10229,21 +10227,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10253,10 +10251,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456794</v>
+        <v>456594</v>
       </c>
       <c r="R96" t="n">
-        <v>6800605</v>
+        <v>6800423</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10286,19 +10284,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10313,22 +10301,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814732</v>
+        <v>128804256</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10336,21 +10324,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10360,10 +10348,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456571</v>
+        <v>456794</v>
       </c>
       <c r="R97" t="n">
-        <v>6800296</v>
+        <v>6800605</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10393,9 +10381,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10410,12 +10408,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10527,10 +10525,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128814664</v>
+        <v>128799696</v>
       </c>
       <c r="B99" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10538,42 +10536,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456676</v>
+        <v>456668</v>
       </c>
       <c r="R99" t="n">
-        <v>6800380</v>
+        <v>6800363</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10603,9 +10593,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10620,22 +10620,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128814632</v>
+        <v>128805054</v>
       </c>
       <c r="B100" t="n">
-        <v>79624</v>
+        <v>79653</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10643,21 +10643,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456382</v>
+        <v>456690</v>
       </c>
       <c r="R100" t="n">
-        <v>6800427</v>
+        <v>6800603</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10700,9 +10700,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10717,22 +10727,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128804554</v>
+        <v>128804050</v>
       </c>
       <c r="B101" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10740,21 +10750,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10764,10 +10774,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456768</v>
+        <v>456753</v>
       </c>
       <c r="R101" t="n">
-        <v>6800626</v>
+        <v>6800562</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10810,6 +10820,11 @@
       <c r="AB101" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10836,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814683</v>
+        <v>128805203</v>
       </c>
       <c r="B102" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10847,37 +10862,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456644</v>
+        <v>456650</v>
       </c>
       <c r="R102" t="n">
-        <v>6800358</v>
+        <v>6800594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10907,78 +10919,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814713</v>
+        <v>128814698</v>
       </c>
       <c r="B103" t="n">
-        <v>90902</v>
+        <v>78791</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5685</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456692</v>
+        <v>456491</v>
       </c>
       <c r="R103" t="n">
-        <v>6800391</v>
+        <v>6800537</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11019,7 +11037,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11038,10 +11055,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805054</v>
+        <v>128814737</v>
       </c>
       <c r="B104" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11049,21 +11066,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11073,10 +11090,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456690</v>
+        <v>456555</v>
       </c>
       <c r="R104" t="n">
-        <v>6800603</v>
+        <v>6800627</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11106,19 +11123,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11133,22 +11140,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814698</v>
+        <v>128814624</v>
       </c>
       <c r="B105" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11156,34 +11163,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456491</v>
+        <v>456688</v>
       </c>
       <c r="R105" t="n">
-        <v>6800537</v>
+        <v>6800585</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11224,6 +11234,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11242,10 +11253,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814624</v>
+        <v>128814725</v>
       </c>
       <c r="B106" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11253,37 +11264,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456688</v>
+        <v>456598</v>
       </c>
       <c r="R106" t="n">
-        <v>6800585</v>
+        <v>6800407</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11318,13 +11326,17 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11343,10 +11355,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128804050</v>
+        <v>128814632</v>
       </c>
       <c r="B107" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11354,21 +11366,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11378,10 +11390,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456753</v>
+        <v>456382</v>
       </c>
       <c r="R107" t="n">
-        <v>6800562</v>
+        <v>6800427</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11411,24 +11423,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11443,22 +11440,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128805203</v>
+        <v>128804554</v>
       </c>
       <c r="B108" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11466,21 +11463,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11490,10 +11487,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456650</v>
+        <v>456768</v>
       </c>
       <c r="R108" t="n">
-        <v>6800594</v>
+        <v>6800626</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11562,10 +11559,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128814737</v>
+        <v>128814683</v>
       </c>
       <c r="B109" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11573,34 +11570,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456555</v>
+        <v>456644</v>
       </c>
       <c r="R109" t="n">
-        <v>6800627</v>
+        <v>6800358</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11641,6 +11641,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11659,45 +11660,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814725</v>
+        <v>128814713</v>
       </c>
       <c r="B110" t="n">
-        <v>79034</v>
+        <v>90905</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456598</v>
+        <v>456692</v>
       </c>
       <c r="R110" t="n">
-        <v>6800407</v>
+        <v>6800391</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11732,17 +11736,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128814696</v>
+        <v>128814679</v>
       </c>
       <c r="B111" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,21 +11772,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456559</v>
+        <v>456753</v>
       </c>
       <c r="R111" t="n">
-        <v>6800576</v>
+        <v>6800533</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11858,10 +11858,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128803369</v>
+        <v>128805558</v>
       </c>
       <c r="B112" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11869,21 +11869,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456688</v>
+        <v>456627</v>
       </c>
       <c r="R112" t="n">
-        <v>6800474</v>
+        <v>6800521</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11965,10 +11965,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814614</v>
+        <v>128814731</v>
       </c>
       <c r="B113" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11976,21 +11976,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456522</v>
+        <v>456580</v>
       </c>
       <c r="R113" t="n">
-        <v>6800319</v>
+        <v>6800292</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12062,10 +12062,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814634</v>
+        <v>128814696</v>
       </c>
       <c r="B114" t="n">
-        <v>57723</v>
+        <v>78791</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12073,42 +12073,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456405</v>
+        <v>456559</v>
       </c>
       <c r="R114" t="n">
-        <v>6800457</v>
+        <v>6800576</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12167,10 +12159,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814646</v>
+        <v>128803369</v>
       </c>
       <c r="B115" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12178,42 +12170,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456519</v>
+        <v>456688</v>
       </c>
       <c r="R115" t="n">
-        <v>6800414</v>
+        <v>6800474</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12243,9 +12227,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12260,22 +12254,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128805558</v>
+        <v>128814614</v>
       </c>
       <c r="B116" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12283,21 +12277,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12307,10 +12301,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456627</v>
+        <v>456522</v>
       </c>
       <c r="R116" t="n">
-        <v>6800521</v>
+        <v>6800319</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12340,19 +12334,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12367,22 +12351,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814731</v>
+        <v>128814687</v>
       </c>
       <c r="B117" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12390,21 +12374,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12414,10 +12398,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456580</v>
+        <v>456556</v>
       </c>
       <c r="R117" t="n">
-        <v>6800292</v>
+        <v>6800320</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12476,10 +12460,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814687</v>
+        <v>128814646</v>
       </c>
       <c r="B118" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12487,34 +12471,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456556</v>
+        <v>456519</v>
       </c>
       <c r="R118" t="n">
-        <v>6800320</v>
+        <v>6800414</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12573,10 +12565,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814679</v>
+        <v>128814634</v>
       </c>
       <c r="B119" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12584,34 +12576,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456753</v>
+        <v>456405</v>
       </c>
       <c r="R119" t="n">
-        <v>6800533</v>
+        <v>6800457</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816353</v>
+        <v>128816343</v>
       </c>
       <c r="B127" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,34 +13392,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456522</v>
+        <v>456341</v>
       </c>
       <c r="R127" t="n">
-        <v>6800357</v>
+        <v>6800306</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13478,10 +13486,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816343</v>
+        <v>128816353</v>
       </c>
       <c r="B128" t="n">
-        <v>57723</v>
+        <v>78791</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13489,42 +13497,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456341</v>
+        <v>456522</v>
       </c>
       <c r="R128" t="n">
-        <v>6800306</v>
+        <v>6800357</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13684,7 +13684,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128816347</v>
+        <v>128816349</v>
       </c>
       <c r="B130" t="n">
         <v>78792</v>
@@ -13713,19 +13713,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>456473</v>
+        <v>456688</v>
       </c>
       <c r="R130" t="n">
-        <v>6800370</v>
+        <v>6800401</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13766,7 +13763,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13785,7 +13781,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128816349</v>
+        <v>128816347</v>
       </c>
       <c r="B131" t="n">
         <v>78792</v>
@@ -13814,16 +13810,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>456688</v>
+        <v>456473</v>
       </c>
       <c r="R131" t="n">
-        <v>6800401</v>
+        <v>6800370</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13864,6 +13863,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14476,10 +14476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128816352</v>
+        <v>128816348</v>
       </c>
       <c r="B138" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14487,37 +14487,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>456483</v>
+        <v>456703</v>
       </c>
       <c r="R138" t="n">
-        <v>6800432</v>
+        <v>6800475</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14558,7 +14555,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14577,10 +14573,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128816348</v>
+        <v>128816352</v>
       </c>
       <c r="B139" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14588,34 +14584,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456703</v>
+        <v>456483</v>
       </c>
       <c r="R139" t="n">
-        <v>6800475</v>
+        <v>6800432</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14656,6 +14655,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15167,10 +15167,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816359</v>
+        <v>128816345</v>
       </c>
       <c r="B145" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15178,34 +15178,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456335</v>
+        <v>456606</v>
       </c>
       <c r="R145" t="n">
-        <v>6800427</v>
+        <v>6800517</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15264,10 +15272,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816345</v>
+        <v>128816359</v>
       </c>
       <c r="B146" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15275,42 +15283,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456606</v>
+        <v>456335</v>
       </c>
       <c r="R146" t="n">
-        <v>6800517</v>
+        <v>6800427</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15369,10 +15369,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128816346</v>
+        <v>128816333</v>
       </c>
       <c r="B147" t="n">
-        <v>78792</v>
+        <v>79066</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15380,37 +15380,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>456521</v>
+        <v>456756</v>
       </c>
       <c r="R147" t="n">
-        <v>6800343</v>
+        <v>6800522</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15451,7 +15448,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15470,10 +15466,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128816333</v>
+        <v>128816346</v>
       </c>
       <c r="B148" t="n">
-        <v>79066</v>
+        <v>78792</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15481,34 +15477,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>456756</v>
+        <v>456521</v>
       </c>
       <c r="R148" t="n">
-        <v>6800522</v>
+        <v>6800343</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15549,6 +15548,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -15668,10 +15668,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128816360</v>
+        <v>128816337</v>
       </c>
       <c r="B150" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15679,21 +15679,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>456583</v>
+        <v>456758</v>
       </c>
       <c r="R150" t="n">
-        <v>6800417</v>
+        <v>6800574</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15765,10 +15765,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128816337</v>
+        <v>128816360</v>
       </c>
       <c r="B151" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15776,21 +15776,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15800,10 +15800,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>456758</v>
+        <v>456583</v>
       </c>
       <c r="R151" t="n">
-        <v>6800574</v>
+        <v>6800417</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128814701</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128800923</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128803425</v>
+        <v>128803579</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456681</v>
+        <v>456698</v>
       </c>
       <c r="R5" t="n">
-        <v>6800496</v>
+        <v>6800503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1077,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128814640</v>
+        <v>128801339</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,42 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456331</v>
+        <v>456742</v>
       </c>
       <c r="R6" t="n">
-        <v>6800312</v>
+        <v>6800421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,9 +1176,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128803579</v>
+        <v>128805128</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456698</v>
+        <v>456660</v>
       </c>
       <c r="R7" t="n">
-        <v>6800503</v>
+        <v>6800603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,11 +1296,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128801339</v>
+        <v>128814728</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456742</v>
+        <v>456616</v>
       </c>
       <c r="R8" t="n">
-        <v>6800421</v>
+        <v>6800533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,19 +1390,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,22 +1407,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128805128</v>
+        <v>128814658</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,34 +1430,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456660</v>
+        <v>456645</v>
       </c>
       <c r="R9" t="n">
-        <v>6800603</v>
+        <v>6800444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,19 +1495,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,22 +1512,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814728</v>
+        <v>128814640</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,34 +1535,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456616</v>
+        <v>456331</v>
       </c>
       <c r="R10" t="n">
-        <v>6800533</v>
+        <v>6800312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,53 +1629,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128814658</v>
+        <v>128803425</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456645</v>
+        <v>456681</v>
       </c>
       <c r="R11" t="n">
-        <v>6800444</v>
+        <v>6800496</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,9 +1697,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814666</v>
+        <v>128804672</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,42 +1747,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456659</v>
+        <v>456733</v>
       </c>
       <c r="R12" t="n">
-        <v>6800402</v>
+        <v>6800618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,9 +1804,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,22 +1831,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128804672</v>
+        <v>128814666</v>
       </c>
       <c r="B13" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,34 +1854,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456733</v>
+        <v>456659</v>
       </c>
       <c r="R13" t="n">
-        <v>6800618</v>
+        <v>6800402</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,19 +1919,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,12 +1936,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1951,7 +1951,7 @@
         <v>128814681</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814654</v>
+        <v>128814744</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,42 +2056,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456705</v>
+        <v>456737</v>
       </c>
       <c r="R15" t="n">
-        <v>6800486</v>
+        <v>6800417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814744</v>
+        <v>128814729</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456737</v>
+        <v>456606</v>
       </c>
       <c r="R16" t="n">
-        <v>6800417</v>
+        <v>6800334</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128804638</v>
+        <v>128805619</v>
       </c>
       <c r="B17" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2258,21 +2250,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2282,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456748</v>
+        <v>456600</v>
       </c>
       <c r="R17" t="n">
-        <v>6800617</v>
+        <v>6800539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128814729</v>
+        <v>128814715</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2389,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456606</v>
+        <v>456589</v>
       </c>
       <c r="R18" t="n">
-        <v>6800334</v>
+        <v>6800303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805619</v>
+        <v>128814654</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,34 +2454,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456600</v>
+        <v>456705</v>
       </c>
       <c r="R19" t="n">
-        <v>6800539</v>
+        <v>6800486</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,19 +2519,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,22 +2536,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128805376</v>
+        <v>128804638</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2559,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456589</v>
+        <v>456748</v>
       </c>
       <c r="R20" t="n">
-        <v>6800567</v>
+        <v>6800617</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128814693</v>
+        <v>128805376</v>
       </c>
       <c r="B21" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2666,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456515</v>
+        <v>456589</v>
       </c>
       <c r="R21" t="n">
-        <v>6800380</v>
+        <v>6800567</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,9 +2723,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,22 +2750,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814715</v>
+        <v>128814693</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456589</v>
+        <v>456515</v>
       </c>
       <c r="R22" t="n">
-        <v>6800303</v>
+        <v>6800380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,7 +2862,7 @@
         <v>128804261</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814673</v>
+        <v>128814652</v>
       </c>
       <c r="B24" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,34 +2977,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456469</v>
+        <v>456781</v>
       </c>
       <c r="R24" t="n">
-        <v>6800542</v>
+        <v>6800644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814616</v>
+        <v>128814644</v>
       </c>
       <c r="B25" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,34 +3082,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456487</v>
+        <v>456603</v>
       </c>
       <c r="R25" t="n">
-        <v>6800546</v>
+        <v>6800371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,7 +3179,7 @@
         <v>128814716</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128805061</v>
+        <v>128814724</v>
       </c>
       <c r="B27" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3273,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3297,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456690</v>
+        <v>456520</v>
       </c>
       <c r="R27" t="n">
-        <v>6800603</v>
+        <v>6800367</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,19 +3346,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3357,22 +3363,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814703</v>
+        <v>128814616</v>
       </c>
       <c r="B28" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,21 +3386,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456766</v>
+        <v>456487</v>
       </c>
       <c r="R28" t="n">
-        <v>6800611</v>
+        <v>6800546</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,10 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128814724</v>
+        <v>128805061</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3501,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456520</v>
+        <v>456690</v>
       </c>
       <c r="R29" t="n">
-        <v>6800367</v>
+        <v>6800603</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3534,9 +3540,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3551,22 +3567,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814652</v>
+        <v>128814703</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3574,42 +3590,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456781</v>
+        <v>456766</v>
       </c>
       <c r="R30" t="n">
-        <v>6800644</v>
+        <v>6800611</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,10 +3676,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128814644</v>
+        <v>128814673</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3679,42 +3687,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456603</v>
+        <v>456469</v>
       </c>
       <c r="R31" t="n">
-        <v>6800371</v>
+        <v>6800542</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814692</v>
+        <v>128814720</v>
       </c>
       <c r="B32" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456354</v>
+        <v>456446</v>
       </c>
       <c r="R32" t="n">
-        <v>6800374</v>
+        <v>6800471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814626</v>
+        <v>128814692</v>
       </c>
       <c r="B33" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456763</v>
+        <v>456354</v>
       </c>
       <c r="R33" t="n">
-        <v>6800617</v>
+        <v>6800374</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814708</v>
+        <v>128814626</v>
       </c>
       <c r="B34" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456702</v>
+        <v>456763</v>
       </c>
       <c r="R34" t="n">
-        <v>6800512</v>
+        <v>6800617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814720</v>
+        <v>128814708</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456446</v>
+        <v>456702</v>
       </c>
       <c r="R35" t="n">
-        <v>6800471</v>
+        <v>6800512</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128804553</v>
+        <v>128814743</v>
       </c>
       <c r="B36" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456768</v>
+        <v>456566</v>
       </c>
       <c r="R36" t="n">
-        <v>6800626</v>
+        <v>6800498</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,19 +4229,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,22 +4251,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814689</v>
+        <v>128814727</v>
       </c>
       <c r="B37" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4279,21 +4274,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4303,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456495</v>
+        <v>456600</v>
       </c>
       <c r="R37" t="n">
-        <v>6800433</v>
+        <v>6800519</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4365,10 +4360,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128814743</v>
+        <v>128804553</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,21 +4371,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4400,10 +4395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456566</v>
+        <v>456768</v>
       </c>
       <c r="R38" t="n">
-        <v>6800498</v>
+        <v>6800626</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4433,14 +4428,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,22 +4455,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814727</v>
+        <v>128814689</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456600</v>
+        <v>456495</v>
       </c>
       <c r="R39" t="n">
-        <v>6800519</v>
+        <v>6800433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
         <v>128814710</v>
       </c>
       <c r="B40" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>128814711</v>
       </c>
       <c r="B41" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128814739</v>
+        <v>128805036</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456351</v>
+        <v>456690</v>
       </c>
       <c r="R42" t="n">
-        <v>6800353</v>
+        <v>6800603</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4826,9 +4826,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4843,22 +4853,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128814733</v>
+        <v>128805352</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4890,10 +4900,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456547</v>
+        <v>456605</v>
       </c>
       <c r="R43" t="n">
-        <v>6800300</v>
+        <v>6800580</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4923,9 +4933,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4940,22 +4960,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128805352</v>
+        <v>128814739</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4987,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456605</v>
+        <v>456351</v>
       </c>
       <c r="R44" t="n">
-        <v>6800580</v>
+        <v>6800353</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5020,19 +5040,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5047,22 +5057,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128805036</v>
+        <v>128814733</v>
       </c>
       <c r="B45" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5070,21 +5080,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5104,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456690</v>
+        <v>456547</v>
       </c>
       <c r="R45" t="n">
-        <v>6800603</v>
+        <v>6800300</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5127,19 +5137,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,12 +5154,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5169,7 +5169,7 @@
         <v>128801266</v>
       </c>
       <c r="B46" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>128799698</v>
       </c>
       <c r="B47" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>128814742</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>128814730</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>128805326</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128814612</v>
+        <v>128799275</v>
       </c>
       <c r="B51" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,21 +5692,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456539</v>
+        <v>456665</v>
       </c>
       <c r="R51" t="n">
-        <v>6800496</v>
+        <v>6800399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,9 +5749,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5766,12 +5781,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5781,7 +5796,7 @@
         <v>128814719</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5878,7 +5893,7 @@
         <v>128814736</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5972,10 +5987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814620</v>
+        <v>128814718</v>
       </c>
       <c r="B54" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5983,37 +5998,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456385</v>
+        <v>456559</v>
       </c>
       <c r="R54" t="n">
-        <v>6800430</v>
+        <v>6800586</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6054,7 +6066,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6073,10 +6084,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814718</v>
+        <v>128814612</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,21 +6095,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6108,10 +6119,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456559</v>
+        <v>456539</v>
       </c>
       <c r="R55" t="n">
-        <v>6800586</v>
+        <v>6800496</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6170,10 +6181,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128802364</v>
+        <v>128814620</v>
       </c>
       <c r="B56" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6181,34 +6192,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456718</v>
+        <v>456385</v>
       </c>
       <c r="R56" t="n">
-        <v>6800502</v>
+        <v>6800430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6238,49 +6252,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128799275</v>
+        <v>128814648</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,34 +6293,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456665</v>
+        <v>456618</v>
       </c>
       <c r="R57" t="n">
-        <v>6800399</v>
+        <v>6800564</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,24 +6358,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6377,22 +6375,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128814648</v>
+        <v>128802364</v>
       </c>
       <c r="B58" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6400,42 +6398,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456618</v>
+        <v>456718</v>
       </c>
       <c r="R58" t="n">
-        <v>6800564</v>
+        <v>6800502</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6465,9 +6455,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,12 +6482,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6497,7 +6497,7 @@
         <v>128799700</v>
       </c>
       <c r="B59" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814735</v>
+        <v>128814628</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6612,21 +6612,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456477</v>
+        <v>456549</v>
       </c>
       <c r="R60" t="n">
-        <v>6800413</v>
+        <v>6800517</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814734</v>
+        <v>128814735</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456472</v>
+        <v>456477</v>
       </c>
       <c r="R61" t="n">
-        <v>6800343</v>
+        <v>6800413</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,10 +6795,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128814628</v>
+        <v>128814734</v>
       </c>
       <c r="B62" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6806,21 +6806,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456549</v>
+        <v>456472</v>
       </c>
       <c r="R62" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6895,7 +6895,7 @@
         <v>128814675</v>
       </c>
       <c r="B63" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>128802133</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7105,10 +7105,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128802369</v>
+        <v>128814721</v>
       </c>
       <c r="B65" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456718</v>
+        <v>456414</v>
       </c>
       <c r="R65" t="n">
-        <v>6800502</v>
+        <v>6800442</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7173,19 +7173,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7200,22 +7190,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128814721</v>
+        <v>128804576</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7223,34 +7213,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456414</v>
+        <v>456761</v>
       </c>
       <c r="R66" t="n">
-        <v>6800442</v>
+        <v>6800606</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7280,9 +7275,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7297,19 +7302,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128804576</v>
+        <v>128814656</v>
       </c>
       <c r="B67" t="n">
         <v>57720</v>
@@ -7338,21 +7343,24 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456761</v>
+        <v>456658</v>
       </c>
       <c r="R67" t="n">
-        <v>6800606</v>
+        <v>6800419</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7382,19 +7390,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7409,22 +7407,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128814656</v>
+        <v>128802369</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7432,42 +7430,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456658</v>
+        <v>456718</v>
       </c>
       <c r="R68" t="n">
-        <v>6800419</v>
+        <v>6800502</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7497,9 +7487,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7514,12 +7514,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128814691</v>
+        <v>128814717</v>
       </c>
       <c r="B70" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456385</v>
+        <v>456529</v>
       </c>
       <c r="R70" t="n">
-        <v>6800430</v>
+        <v>6800501</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814717</v>
+        <v>128814691</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7739,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456529</v>
+        <v>456385</v>
       </c>
       <c r="R71" t="n">
-        <v>6800501</v>
+        <v>6800430</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7828,7 +7828,7 @@
         <v>128814707</v>
       </c>
       <c r="B72" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814714</v>
+        <v>128814697</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456599</v>
+        <v>456499</v>
       </c>
       <c r="R73" t="n">
-        <v>6800361</v>
+        <v>6800562</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128814697</v>
+        <v>128803330</v>
       </c>
       <c r="B74" t="n">
-        <v>78791</v>
+        <v>79625</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,21 +8030,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8054,10 +8054,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456499</v>
+        <v>456690</v>
       </c>
       <c r="R74" t="n">
-        <v>6800562</v>
+        <v>6800454</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8087,9 +8087,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8104,22 +8114,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128799394</v>
+        <v>128814714</v>
       </c>
       <c r="B75" t="n">
-        <v>91473</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8127,21 +8137,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8151,10 +8161,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456679</v>
+        <v>456599</v>
       </c>
       <c r="R75" t="n">
-        <v>6800380</v>
+        <v>6800361</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,19 +8194,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8211,22 +8211,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128803330</v>
+        <v>128799394</v>
       </c>
       <c r="B76" t="n">
-        <v>79624</v>
+        <v>91476</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8234,21 +8234,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>112</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>456690</v>
+        <v>456679</v>
       </c>
       <c r="R76" t="n">
-        <v>6800454</v>
+        <v>6800380</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8330,53 +8330,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128800812</v>
+        <v>128814722</v>
       </c>
       <c r="B77" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456691</v>
+        <v>456349</v>
       </c>
       <c r="R77" t="n">
-        <v>6800368</v>
+        <v>6800436</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8403,19 +8398,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8430,22 +8415,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128814677</v>
+        <v>128800436</v>
       </c>
       <c r="B78" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8453,21 +8438,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8477,10 +8462,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456747</v>
+        <v>456671</v>
       </c>
       <c r="R78" t="n">
-        <v>6800569</v>
+        <v>6800350</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8510,9 +8495,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8527,19 +8522,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128801262</v>
+        <v>128814709</v>
       </c>
       <c r="B79" t="n">
         <v>78792</v>
@@ -8550,21 +8545,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8574,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456703</v>
+        <v>456706</v>
       </c>
       <c r="R79" t="n">
-        <v>6800429</v>
+        <v>6800520</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8607,19 +8602,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8634,22 +8619,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128800436</v>
+        <v>128814702</v>
       </c>
       <c r="B80" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8657,21 +8642,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8681,10 +8666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456671</v>
+        <v>456788</v>
       </c>
       <c r="R80" t="n">
-        <v>6800350</v>
+        <v>6800626</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8714,19 +8699,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8741,22 +8716,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128814709</v>
+        <v>128814695</v>
       </c>
       <c r="B81" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8788,10 +8763,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456706</v>
+        <v>456547</v>
       </c>
       <c r="R81" t="n">
-        <v>6800520</v>
+        <v>6800403</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8850,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128814702</v>
+        <v>128814618</v>
       </c>
       <c r="B82" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8861,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8885,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456788</v>
+        <v>456450</v>
       </c>
       <c r="R82" t="n">
-        <v>6800626</v>
+        <v>6800571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8947,48 +8922,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128814722</v>
+        <v>128800812</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456349</v>
+        <v>456691</v>
       </c>
       <c r="R83" t="n">
-        <v>6800436</v>
+        <v>6800368</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9015,9 +8995,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9032,22 +9022,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128814695</v>
+        <v>128814677</v>
       </c>
       <c r="B84" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9055,21 +9045,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9079,10 +9069,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456547</v>
+        <v>456747</v>
       </c>
       <c r="R84" t="n">
-        <v>6800403</v>
+        <v>6800569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9141,10 +9131,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128814618</v>
+        <v>128801262</v>
       </c>
       <c r="B85" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9152,21 +9142,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9176,10 +9166,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456450</v>
+        <v>456703</v>
       </c>
       <c r="R85" t="n">
-        <v>6800571</v>
+        <v>6800429</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9209,9 +9199,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9226,22 +9226,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814741</v>
+        <v>128814630</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456637</v>
+        <v>456496</v>
       </c>
       <c r="R86" t="n">
-        <v>6800536</v>
+        <v>6800554</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814726</v>
+        <v>128814741</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456524</v>
+        <v>456637</v>
       </c>
       <c r="R87" t="n">
-        <v>6800431</v>
+        <v>6800536</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814723</v>
+        <v>128814726</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456351</v>
+        <v>456524</v>
       </c>
       <c r="R88" t="n">
-        <v>6800371</v>
+        <v>6800431</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814630</v>
+        <v>128814723</v>
       </c>
       <c r="B89" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456496</v>
+        <v>456351</v>
       </c>
       <c r="R89" t="n">
-        <v>6800554</v>
+        <v>6800371</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128814664</v>
+        <v>128814732</v>
       </c>
       <c r="B90" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,42 +9637,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456676</v>
+        <v>456571</v>
       </c>
       <c r="R90" t="n">
-        <v>6800380</v>
+        <v>6800296</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9731,10 +9723,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814705</v>
+        <v>128814664</v>
       </c>
       <c r="B91" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9742,34 +9734,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456749</v>
+        <v>456676</v>
       </c>
       <c r="R91" t="n">
-        <v>6800566</v>
+        <v>6800380</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9828,10 +9828,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128814622</v>
+        <v>128799696</v>
       </c>
       <c r="B92" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9839,21 +9839,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9863,10 +9863,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456546</v>
+        <v>456668</v>
       </c>
       <c r="R92" t="n">
-        <v>6800434</v>
+        <v>6800363</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9896,9 +9896,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9913,22 +9923,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814732</v>
+        <v>128814705</v>
       </c>
       <c r="B93" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9936,21 +9946,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9960,10 +9970,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456571</v>
+        <v>456749</v>
       </c>
       <c r="R93" t="n">
-        <v>6800296</v>
+        <v>6800566</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10022,10 +10032,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814690</v>
+        <v>128814622</v>
       </c>
       <c r="B94" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10033,21 +10043,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10057,10 +10067,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456465</v>
+        <v>456546</v>
       </c>
       <c r="R94" t="n">
-        <v>6800546</v>
+        <v>6800434</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10119,10 +10129,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814699</v>
+        <v>128814690</v>
       </c>
       <c r="B95" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10154,10 +10164,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456496</v>
+        <v>456465</v>
       </c>
       <c r="R95" t="n">
-        <v>6800549</v>
+        <v>6800546</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10216,10 +10226,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814694</v>
+        <v>128814699</v>
       </c>
       <c r="B96" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10251,10 +10261,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456594</v>
+        <v>456496</v>
       </c>
       <c r="R96" t="n">
-        <v>6800423</v>
+        <v>6800549</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10313,10 +10323,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128804256</v>
+        <v>128814694</v>
       </c>
       <c r="B97" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10324,21 +10334,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10348,10 +10358,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456794</v>
+        <v>456594</v>
       </c>
       <c r="R97" t="n">
-        <v>6800605</v>
+        <v>6800423</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10381,19 +10391,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10408,22 +10408,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128814637</v>
+        <v>128804256</v>
       </c>
       <c r="B98" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10431,42 +10431,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456352</v>
+        <v>456794</v>
       </c>
       <c r="R98" t="n">
-        <v>6800325</v>
+        <v>6800605</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10496,9 +10488,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10513,22 +10515,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128799696</v>
+        <v>128814637</v>
       </c>
       <c r="B99" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10536,34 +10538,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456668</v>
+        <v>456352</v>
       </c>
       <c r="R99" t="n">
-        <v>6800363</v>
+        <v>6800325</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10593,19 +10603,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10620,12 +10620,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10635,7 +10635,7 @@
         <v>128805054</v>
       </c>
       <c r="B100" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10739,10 +10739,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128804050</v>
+        <v>128805203</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456753</v>
+        <v>456650</v>
       </c>
       <c r="R101" t="n">
-        <v>6800562</v>
+        <v>6800594</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10820,11 +10820,6 @@
       <c r="AB101" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10851,10 +10846,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805203</v>
+        <v>128814698</v>
       </c>
       <c r="B102" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,21 +10857,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10886,10 +10881,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456650</v>
+        <v>456491</v>
       </c>
       <c r="R102" t="n">
-        <v>6800594</v>
+        <v>6800537</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10919,19 +10914,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10946,22 +10931,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814698</v>
+        <v>128814624</v>
       </c>
       <c r="B103" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10969,34 +10954,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456491</v>
+        <v>456688</v>
       </c>
       <c r="R103" t="n">
-        <v>6800537</v>
+        <v>6800585</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11037,6 +11025,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11055,10 +11044,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128814737</v>
+        <v>128804050</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11090,10 +11079,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456555</v>
+        <v>456753</v>
       </c>
       <c r="R104" t="n">
-        <v>6800627</v>
+        <v>6800562</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11123,9 +11112,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11140,44 +11144,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814624</v>
+        <v>128814713</v>
       </c>
       <c r="B105" t="n">
-        <v>79653</v>
+        <v>90908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11190,10 +11194,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456688</v>
+        <v>456692</v>
       </c>
       <c r="R105" t="n">
-        <v>6800585</v>
+        <v>6800391</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11253,10 +11257,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814725</v>
+        <v>128814737</v>
       </c>
       <c r="B106" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11288,10 +11292,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456598</v>
+        <v>456555</v>
       </c>
       <c r="R106" t="n">
-        <v>6800407</v>
+        <v>6800627</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11324,11 +11328,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11355,10 +11354,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814632</v>
+        <v>128814725</v>
       </c>
       <c r="B107" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11366,21 +11365,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11390,10 +11389,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456382</v>
+        <v>456598</v>
       </c>
       <c r="R107" t="n">
-        <v>6800427</v>
+        <v>6800407</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11426,6 +11425,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11452,10 +11456,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128804554</v>
+        <v>128814632</v>
       </c>
       <c r="B108" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11463,21 +11467,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11487,10 +11491,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456768</v>
+        <v>456382</v>
       </c>
       <c r="R108" t="n">
-        <v>6800626</v>
+        <v>6800427</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11520,19 +11524,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11547,22 +11541,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128814683</v>
+        <v>128804554</v>
       </c>
       <c r="B109" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11588,19 +11582,16 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456644</v>
+        <v>456768</v>
       </c>
       <c r="R109" t="n">
-        <v>6800358</v>
+        <v>6800626</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11630,62 +11621,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814713</v>
+        <v>128814683</v>
       </c>
       <c r="B110" t="n">
-        <v>90905</v>
+        <v>78793</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456692</v>
+        <v>456644</v>
       </c>
       <c r="R110" t="n">
-        <v>6800391</v>
+        <v>6800358</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11764,7 +11764,7 @@
         <v>128814679</v>
       </c>
       <c r="B111" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11858,10 +11858,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128805558</v>
+        <v>128814696</v>
       </c>
       <c r="B112" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11869,21 +11869,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456627</v>
+        <v>456559</v>
       </c>
       <c r="R112" t="n">
-        <v>6800521</v>
+        <v>6800576</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11926,19 +11926,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11953,22 +11943,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128814731</v>
+        <v>128803369</v>
       </c>
       <c r="B113" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11976,21 +11966,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12000,10 +11990,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456580</v>
+        <v>456688</v>
       </c>
       <c r="R113" t="n">
-        <v>6800292</v>
+        <v>6800474</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12033,9 +12023,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12050,22 +12050,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814696</v>
+        <v>128814614</v>
       </c>
       <c r="B114" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12073,21 +12073,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12097,10 +12097,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456559</v>
+        <v>456522</v>
       </c>
       <c r="R114" t="n">
-        <v>6800576</v>
+        <v>6800319</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12159,10 +12159,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128803369</v>
+        <v>128814687</v>
       </c>
       <c r="B115" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12170,21 +12170,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456688</v>
+        <v>456556</v>
       </c>
       <c r="R115" t="n">
-        <v>6800474</v>
+        <v>6800320</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12227,19 +12227,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12254,22 +12244,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814614</v>
+        <v>128814634</v>
       </c>
       <c r="B116" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12277,34 +12267,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456522</v>
+        <v>456405</v>
       </c>
       <c r="R116" t="n">
-        <v>6800319</v>
+        <v>6800457</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12363,10 +12361,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128814687</v>
+        <v>128814646</v>
       </c>
       <c r="B117" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12374,34 +12372,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456556</v>
+        <v>456519</v>
       </c>
       <c r="R117" t="n">
-        <v>6800320</v>
+        <v>6800414</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12460,10 +12466,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128814646</v>
+        <v>128805558</v>
       </c>
       <c r="B118" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12471,42 +12477,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456519</v>
+        <v>456627</v>
       </c>
       <c r="R118" t="n">
-        <v>6800414</v>
+        <v>6800521</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12536,9 +12534,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12553,22 +12561,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814634</v>
+        <v>128814731</v>
       </c>
       <c r="B119" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12576,42 +12584,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456405</v>
+        <v>456580</v>
       </c>
       <c r="R119" t="n">
-        <v>6800457</v>
+        <v>6800292</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12673,7 +12673,7 @@
         <v>128805585</v>
       </c>
       <c r="B120" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>128814706</v>
       </c>
       <c r="B121" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>128804496</v>
       </c>
       <c r="B122" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>128814700</v>
       </c>
       <c r="B123" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>128816339</v>
       </c>
       <c r="B124" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>128816336</v>
       </c>
       <c r="B126" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816343</v>
+        <v>128816338</v>
       </c>
       <c r="B127" t="n">
-        <v>57723</v>
+        <v>79625</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,31 +13392,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13424,10 +13419,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456341</v>
+        <v>456478</v>
       </c>
       <c r="R127" t="n">
-        <v>6800306</v>
+        <v>6800591</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13468,6 +13463,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13489,7 +13485,7 @@
         <v>128816353</v>
       </c>
       <c r="B128" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13583,10 +13579,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816338</v>
+        <v>128816343</v>
       </c>
       <c r="B129" t="n">
-        <v>79624</v>
+        <v>57723</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13594,26 +13590,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13621,10 +13622,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456478</v>
+        <v>456341</v>
       </c>
       <c r="R129" t="n">
-        <v>6800591</v>
+        <v>6800306</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13665,7 +13666,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13684,10 +13684,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128816349</v>
+        <v>128816347</v>
       </c>
       <c r="B130" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13713,16 +13713,19 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>456688</v>
+        <v>456473</v>
       </c>
       <c r="R130" t="n">
-        <v>6800401</v>
+        <v>6800370</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13763,6 +13766,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13781,10 +13785,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128816347</v>
+        <v>128816349</v>
       </c>
       <c r="B131" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13810,19 +13814,16 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>456473</v>
+        <v>456688</v>
       </c>
       <c r="R131" t="n">
-        <v>6800370</v>
+        <v>6800401</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13863,7 +13864,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>128816354</v>
       </c>
       <c r="B132" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>128816356</v>
       </c>
       <c r="B133" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>128816351</v>
       </c>
       <c r="B134" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>128816340</v>
       </c>
       <c r="B135" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>128816331</v>
       </c>
       <c r="B136" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>128816335</v>
       </c>
       <c r="B137" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128816348</v>
+        <v>128816352</v>
       </c>
       <c r="B138" t="n">
         <v>78792</v>
@@ -14487,34 +14487,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>456703</v>
+        <v>456483</v>
       </c>
       <c r="R138" t="n">
-        <v>6800475</v>
+        <v>6800432</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14555,6 +14558,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14573,10 +14577,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128816352</v>
+        <v>128816348</v>
       </c>
       <c r="B139" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14584,37 +14588,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456483</v>
+        <v>456703</v>
       </c>
       <c r="R139" t="n">
-        <v>6800432</v>
+        <v>6800475</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14655,7 +14656,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14677,7 +14677,7 @@
         <v>128816350</v>
       </c>
       <c r="B140" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>128816334</v>
       </c>
       <c r="B141" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>128816358</v>
       </c>
       <c r="B142" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>128816361</v>
       </c>
       <c r="B143" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15066,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816332</v>
+        <v>128816359</v>
       </c>
       <c r="B144" t="n">
-        <v>79066</v>
+        <v>79035</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15077,37 +15077,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456355</v>
+        <v>456335</v>
       </c>
       <c r="R144" t="n">
-        <v>6800454</v>
+        <v>6800427</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15148,7 +15145,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15272,10 +15268,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128816359</v>
+        <v>128816332</v>
       </c>
       <c r="B146" t="n">
-        <v>79034</v>
+        <v>79067</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15283,34 +15279,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>456335</v>
+        <v>456355</v>
       </c>
       <c r="R146" t="n">
-        <v>6800427</v>
+        <v>6800454</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15351,6 +15350,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15369,10 +15369,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128816333</v>
+        <v>128816346</v>
       </c>
       <c r="B147" t="n">
-        <v>79066</v>
+        <v>78793</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15380,34 +15380,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>456756</v>
+        <v>456521</v>
       </c>
       <c r="R147" t="n">
-        <v>6800522</v>
+        <v>6800343</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15448,6 +15451,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -15466,10 +15470,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128816346</v>
+        <v>128816333</v>
       </c>
       <c r="B148" t="n">
-        <v>78792</v>
+        <v>79067</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15477,37 +15481,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>456521</v>
+        <v>456756</v>
       </c>
       <c r="R148" t="n">
-        <v>6800343</v>
+        <v>6800522</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15548,7 +15549,6 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -15570,7 +15570,7 @@
         <v>128816341</v>
       </c>
       <c r="B149" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>128816337</v>
       </c>
       <c r="B150" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>128816360</v>
       </c>
       <c r="B151" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128799069</v>
+        <v>128814701</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456632</v>
+        <v>456547</v>
       </c>
       <c r="R2" t="n">
-        <v>6800431</v>
+        <v>6800436</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128814701</v>
+        <v>128800923</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456547</v>
+        <v>456692</v>
       </c>
       <c r="R3" t="n">
-        <v>6800436</v>
+        <v>6800405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,9 +840,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128800923</v>
+        <v>128799069</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456692</v>
+        <v>456632</v>
       </c>
       <c r="R4" t="n">
-        <v>6800405</v>
+        <v>6800431</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,11 +970,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1419,53 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128814658</v>
+        <v>128803425</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456645</v>
+        <v>456681</v>
       </c>
       <c r="R9" t="n">
-        <v>6800444</v>
+        <v>6800496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,9 +1487,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,22 +1514,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814640</v>
+        <v>128814658</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,16 +1537,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,7 +1559,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1567,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456331</v>
+        <v>456645</v>
       </c>
       <c r="R10" t="n">
-        <v>6800312</v>
+        <v>6800444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,45 +1631,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128803425</v>
+        <v>128814640</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456681</v>
+        <v>456331</v>
       </c>
       <c r="R11" t="n">
-        <v>6800496</v>
+        <v>6800312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,19 +1707,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,22 +1724,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128804672</v>
+        <v>128814666</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,34 +1747,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456733</v>
+        <v>456659</v>
       </c>
       <c r="R12" t="n">
-        <v>6800618</v>
+        <v>6800402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,19 +1812,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,22 +1829,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814666</v>
+        <v>128814681</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,42 +1852,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456659</v>
+        <v>456761</v>
       </c>
       <c r="R13" t="n">
-        <v>6800402</v>
+        <v>6800515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814681</v>
+        <v>128804672</v>
       </c>
       <c r="B14" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456761</v>
+        <v>456733</v>
       </c>
       <c r="R14" t="n">
-        <v>6800515</v>
+        <v>6800618</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,9 +2006,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2033,22 +2033,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128814744</v>
+        <v>128814654</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,34 +2056,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456737</v>
+        <v>456705</v>
       </c>
       <c r="R15" t="n">
-        <v>6800417</v>
+        <v>6800486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,7 +2150,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814729</v>
+        <v>128814744</v>
       </c>
       <c r="B16" t="n">
         <v>79035</v>
@@ -2177,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456606</v>
+        <v>456737</v>
       </c>
       <c r="R16" t="n">
-        <v>6800334</v>
+        <v>6800417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128805619</v>
+        <v>128804638</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2258,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456600</v>
+        <v>456748</v>
       </c>
       <c r="R17" t="n">
-        <v>6800539</v>
+        <v>6800617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,7 +2354,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128814715</v>
+        <v>128814729</v>
       </c>
       <c r="B18" t="n">
         <v>79035</v>
@@ -2381,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456589</v>
+        <v>456606</v>
       </c>
       <c r="R18" t="n">
-        <v>6800303</v>
+        <v>6800334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128814654</v>
+        <v>128805619</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,42 +2462,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456705</v>
+        <v>456600</v>
       </c>
       <c r="R19" t="n">
-        <v>6800486</v>
+        <v>6800539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,9 +2519,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,22 +2546,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128804638</v>
+        <v>128805376</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2583,10 +2593,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456748</v>
+        <v>456589</v>
       </c>
       <c r="R20" t="n">
-        <v>6800617</v>
+        <v>6800567</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128805376</v>
+        <v>128814693</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2690,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456589</v>
+        <v>456515</v>
       </c>
       <c r="R21" t="n">
-        <v>6800567</v>
+        <v>6800380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,19 +2733,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,22 +2750,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128814693</v>
+        <v>128814715</v>
       </c>
       <c r="B22" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456515</v>
+        <v>456589</v>
       </c>
       <c r="R22" t="n">
-        <v>6800380</v>
+        <v>6800303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128814652</v>
+        <v>128814616</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,42 +2977,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456781</v>
+        <v>456487</v>
       </c>
       <c r="R24" t="n">
-        <v>6800644</v>
+        <v>6800546</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128814644</v>
+        <v>128814716</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,42 +3074,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456603</v>
+        <v>456477</v>
       </c>
       <c r="R25" t="n">
-        <v>6800371</v>
+        <v>6800324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,6 +3134,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 10 m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,10 +3165,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128814716</v>
+        <v>128805061</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3176,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456477</v>
+        <v>456690</v>
       </c>
       <c r="R26" t="n">
-        <v>6800324</v>
+        <v>6800603</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,14 +3233,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 10 m.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3266,22 +3260,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128814724</v>
+        <v>128814703</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456520</v>
+        <v>456766</v>
       </c>
       <c r="R27" t="n">
-        <v>6800367</v>
+        <v>6800611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128814616</v>
+        <v>128814724</v>
       </c>
       <c r="B28" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,21 +3380,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456487</v>
+        <v>456520</v>
       </c>
       <c r="R28" t="n">
-        <v>6800546</v>
+        <v>6800367</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128805061</v>
+        <v>128814644</v>
       </c>
       <c r="B29" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3483,34 +3477,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456690</v>
+        <v>456603</v>
       </c>
       <c r="R29" t="n">
-        <v>6800603</v>
+        <v>6800371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,19 +3542,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3567,22 +3559,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128814703</v>
+        <v>128814652</v>
       </c>
       <c r="B30" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,34 +3582,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456766</v>
+        <v>456781</v>
       </c>
       <c r="R30" t="n">
-        <v>6800611</v>
+        <v>6800644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128814720</v>
+        <v>128814692</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456446</v>
+        <v>456354</v>
       </c>
       <c r="R32" t="n">
-        <v>6800471</v>
+        <v>6800374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128814692</v>
+        <v>128814626</v>
       </c>
       <c r="B33" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456354</v>
+        <v>456763</v>
       </c>
       <c r="R33" t="n">
-        <v>6800374</v>
+        <v>6800617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128814626</v>
+        <v>128814708</v>
       </c>
       <c r="B34" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456763</v>
+        <v>456702</v>
       </c>
       <c r="R34" t="n">
-        <v>6800617</v>
+        <v>6800512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128814708</v>
+        <v>128814720</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456702</v>
+        <v>456446</v>
       </c>
       <c r="R35" t="n">
-        <v>6800512</v>
+        <v>6800471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128814743</v>
+        <v>128804553</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456566</v>
+        <v>456768</v>
       </c>
       <c r="R36" t="n">
-        <v>6800498</v>
+        <v>6800626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,14 +4229,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Foto 14.24</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,22 +4256,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128814727</v>
+        <v>128814689</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,21 +4279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456600</v>
+        <v>456495</v>
       </c>
       <c r="R37" t="n">
-        <v>6800519</v>
+        <v>6800433</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,10 +4365,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128804553</v>
+        <v>128814743</v>
       </c>
       <c r="B38" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,21 +4376,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4395,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456768</v>
+        <v>456566</v>
       </c>
       <c r="R38" t="n">
-        <v>6800626</v>
+        <v>6800498</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4428,19 +4433,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:20</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Foto 14.24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,22 +4455,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128814689</v>
+        <v>128814727</v>
       </c>
       <c r="B39" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456495</v>
+        <v>456600</v>
       </c>
       <c r="R39" t="n">
-        <v>6800433</v>
+        <v>6800519</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128805352</v>
+        <v>128814739</v>
       </c>
       <c r="B43" t="n">
         <v>79035</v>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456605</v>
+        <v>456351</v>
       </c>
       <c r="R43" t="n">
-        <v>6800580</v>
+        <v>6800353</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4933,19 +4933,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4960,19 +4950,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128814739</v>
+        <v>128814733</v>
       </c>
       <c r="B44" t="n">
         <v>79035</v>
@@ -5007,10 +4997,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456351</v>
+        <v>456547</v>
       </c>
       <c r="R44" t="n">
-        <v>6800353</v>
+        <v>6800300</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5069,7 +5059,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128814733</v>
+        <v>128805352</v>
       </c>
       <c r="B45" t="n">
         <v>79035</v>
@@ -5104,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456547</v>
+        <v>456605</v>
       </c>
       <c r="R45" t="n">
-        <v>6800300</v>
+        <v>6800580</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5137,9 +5127,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,12 +5154,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5681,10 +5681,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128799275</v>
+        <v>128814648</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5692,34 +5692,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456665</v>
+        <v>456618</v>
       </c>
       <c r="R51" t="n">
-        <v>6800399</v>
+        <v>6800564</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5749,24 +5757,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5781,22 +5774,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128814719</v>
+        <v>128802364</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5804,21 +5797,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5828,10 +5821,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456527</v>
+        <v>456718</v>
       </c>
       <c r="R52" t="n">
-        <v>6800610</v>
+        <v>6800502</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5861,9 +5854,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5878,19 +5881,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128814736</v>
+        <v>128799275</v>
       </c>
       <c r="B53" t="n">
         <v>79035</v>
@@ -5925,10 +5928,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456569</v>
+        <v>456665</v>
       </c>
       <c r="R53" t="n">
-        <v>6800599</v>
+        <v>6800399</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5958,9 +5961,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5975,22 +5993,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128814718</v>
+        <v>128814612</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5998,21 +6016,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6022,10 +6040,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456559</v>
+        <v>456539</v>
       </c>
       <c r="R54" t="n">
-        <v>6800586</v>
+        <v>6800496</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6084,10 +6102,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128814612</v>
+        <v>128814719</v>
       </c>
       <c r="B55" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6095,21 +6113,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6119,10 +6137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456539</v>
+        <v>456527</v>
       </c>
       <c r="R55" t="n">
-        <v>6800496</v>
+        <v>6800610</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6181,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128814620</v>
+        <v>128814736</v>
       </c>
       <c r="B56" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6192,37 +6210,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456385</v>
+        <v>456569</v>
       </c>
       <c r="R56" t="n">
-        <v>6800430</v>
+        <v>6800599</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6263,7 +6278,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6282,10 +6296,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128814648</v>
+        <v>128814620</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6293,31 +6307,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6325,10 +6334,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456618</v>
+        <v>456385</v>
       </c>
       <c r="R57" t="n">
-        <v>6800564</v>
+        <v>6800430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6369,6 +6378,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6387,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128802364</v>
+        <v>128814718</v>
       </c>
       <c r="B58" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,21 +6408,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6422,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456718</v>
+        <v>456559</v>
       </c>
       <c r="R58" t="n">
-        <v>6800502</v>
+        <v>6800586</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6455,19 +6465,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,22 +6482,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128799700</v>
+        <v>128814735</v>
       </c>
       <c r="B59" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456668</v>
+        <v>456477</v>
       </c>
       <c r="R59" t="n">
-        <v>6800363</v>
+        <v>6800413</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,19 +6562,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6589,22 +6579,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814628</v>
+        <v>128814734</v>
       </c>
       <c r="B60" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6612,21 +6602,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6636,10 +6626,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456549</v>
+        <v>456472</v>
       </c>
       <c r="R60" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6688,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814735</v>
+        <v>128814628</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6699,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6723,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456477</v>
+        <v>456549</v>
       </c>
       <c r="R61" t="n">
-        <v>6800413</v>
+        <v>6800517</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128814734</v>
+        <v>128799700</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6806,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6830,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456472</v>
+        <v>456668</v>
       </c>
       <c r="R62" t="n">
-        <v>6800343</v>
+        <v>6800363</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6863,9 +6853,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,22 +6880,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128814675</v>
+        <v>128802133</v>
       </c>
       <c r="B63" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6903,37 +6903,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456513</v>
+        <v>456775</v>
       </c>
       <c r="R63" t="n">
-        <v>6800383</v>
+        <v>6800500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6963,40 +6960,54 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128802133</v>
+        <v>128802369</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7004,21 +7015,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7028,10 +7039,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456775</v>
+        <v>456718</v>
       </c>
       <c r="R64" t="n">
-        <v>6800500</v>
+        <v>6800502</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7074,11 +7085,6 @@
       <c r="AB64" t="inlineStr">
         <is>
           <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7202,7 +7208,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128804576</v>
+        <v>128814656</v>
       </c>
       <c r="B66" t="n">
         <v>57720</v>
@@ -7231,21 +7237,24 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456761</v>
+        <v>456658</v>
       </c>
       <c r="R66" t="n">
-        <v>6800606</v>
+        <v>6800419</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7275,19 +7284,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7302,19 +7301,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128814656</v>
+        <v>128814660</v>
       </c>
       <c r="B67" t="n">
         <v>57720</v>
@@ -7347,7 +7346,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7357,10 +7356,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456658</v>
+        <v>456747</v>
       </c>
       <c r="R67" t="n">
-        <v>6800419</v>
+        <v>6800420</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7419,10 +7418,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128802369</v>
+        <v>128804576</v>
       </c>
       <c r="B68" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7430,34 +7429,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456718</v>
+        <v>456761</v>
       </c>
       <c r="R68" t="n">
-        <v>6800502</v>
+        <v>6800606</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7526,10 +7530,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128814660</v>
+        <v>128814675</v>
       </c>
       <c r="B69" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7537,31 +7541,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7569,10 +7568,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456747</v>
+        <v>456513</v>
       </c>
       <c r="R69" t="n">
-        <v>6800420</v>
+        <v>6800383</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7613,6 +7612,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128814717</v>
+        <v>128814691</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456529</v>
+        <v>456385</v>
       </c>
       <c r="R70" t="n">
-        <v>6800501</v>
+        <v>6800430</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128814691</v>
+        <v>128814717</v>
       </c>
       <c r="B71" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7739,21 +7739,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456385</v>
+        <v>456529</v>
       </c>
       <c r="R71" t="n">
-        <v>6800430</v>
+        <v>6800501</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128814697</v>
+        <v>128814714</v>
       </c>
       <c r="B73" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,21 +7933,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456499</v>
+        <v>456599</v>
       </c>
       <c r="R73" t="n">
-        <v>6800562</v>
+        <v>6800361</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128803330</v>
+        <v>128814697</v>
       </c>
       <c r="B74" t="n">
-        <v>79625</v>
+        <v>78792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,21 +8030,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8054,10 +8054,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456690</v>
+        <v>456499</v>
       </c>
       <c r="R74" t="n">
-        <v>6800454</v>
+        <v>6800562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8087,19 +8087,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8114,22 +8104,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128814714</v>
+        <v>128803330</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8137,21 +8127,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8151,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456599</v>
+        <v>456690</v>
       </c>
       <c r="R75" t="n">
-        <v>6800361</v>
+        <v>6800454</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8194,9 +8184,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8211,12 +8211,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128814722</v>
+        <v>128800436</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8341,21 +8341,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456349</v>
+        <v>456671</v>
       </c>
       <c r="R77" t="n">
-        <v>6800436</v>
+        <v>6800350</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8398,9 +8398,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8415,22 +8425,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128800436</v>
+        <v>128814709</v>
       </c>
       <c r="B78" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8438,21 +8448,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8462,10 +8472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>456671</v>
+        <v>456706</v>
       </c>
       <c r="R78" t="n">
-        <v>6800350</v>
+        <v>6800520</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8495,19 +8505,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,19 +8522,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128814709</v>
+        <v>128814702</v>
       </c>
       <c r="B79" t="n">
         <v>78792</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456706</v>
+        <v>456788</v>
       </c>
       <c r="R79" t="n">
-        <v>6800520</v>
+        <v>6800626</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,10 +8631,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128814702</v>
+        <v>128814722</v>
       </c>
       <c r="B80" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8642,21 +8642,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456788</v>
+        <v>456349</v>
       </c>
       <c r="R80" t="n">
-        <v>6800626</v>
+        <v>6800436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128814630</v>
+        <v>128814741</v>
       </c>
       <c r="B86" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456496</v>
+        <v>456637</v>
       </c>
       <c r="R86" t="n">
-        <v>6800554</v>
+        <v>6800536</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128814741</v>
+        <v>128814726</v>
       </c>
       <c r="B87" t="n">
         <v>79035</v>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456637</v>
+        <v>456524</v>
       </c>
       <c r="R87" t="n">
-        <v>6800536</v>
+        <v>6800431</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128814726</v>
+        <v>128814723</v>
       </c>
       <c r="B88" t="n">
         <v>79035</v>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456524</v>
+        <v>456351</v>
       </c>
       <c r="R88" t="n">
-        <v>6800431</v>
+        <v>6800371</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128814723</v>
+        <v>128814630</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9540,21 +9540,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456351</v>
+        <v>456496</v>
       </c>
       <c r="R89" t="n">
-        <v>6800371</v>
+        <v>6800554</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128814732</v>
+        <v>128814664</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,34 +9637,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456571</v>
+        <v>456676</v>
       </c>
       <c r="R90" t="n">
-        <v>6800296</v>
+        <v>6800380</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9723,10 +9731,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128814664</v>
+        <v>128814705</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9734,42 +9742,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456676</v>
+        <v>456749</v>
       </c>
       <c r="R91" t="n">
-        <v>6800380</v>
+        <v>6800566</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9828,10 +9828,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128799696</v>
+        <v>128814622</v>
       </c>
       <c r="B92" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9839,21 +9839,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9863,10 +9863,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>456668</v>
+        <v>456546</v>
       </c>
       <c r="R92" t="n">
-        <v>6800363</v>
+        <v>6800434</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9896,19 +9896,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9923,22 +9913,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128814705</v>
+        <v>128814732</v>
       </c>
       <c r="B93" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9946,21 +9936,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9970,10 +9960,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456749</v>
+        <v>456571</v>
       </c>
       <c r="R93" t="n">
-        <v>6800566</v>
+        <v>6800296</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10032,10 +10022,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128814622</v>
+        <v>128814690</v>
       </c>
       <c r="B94" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10043,21 +10033,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10067,10 +10057,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456546</v>
+        <v>456465</v>
       </c>
       <c r="R94" t="n">
-        <v>6800434</v>
+        <v>6800546</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10129,7 +10119,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128814690</v>
+        <v>128814699</v>
       </c>
       <c r="B95" t="n">
         <v>78792</v>
@@ -10164,10 +10154,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456465</v>
+        <v>456496</v>
       </c>
       <c r="R95" t="n">
-        <v>6800546</v>
+        <v>6800549</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10226,7 +10216,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128814699</v>
+        <v>128814694</v>
       </c>
       <c r="B96" t="n">
         <v>78792</v>
@@ -10261,10 +10251,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456496</v>
+        <v>456594</v>
       </c>
       <c r="R96" t="n">
-        <v>6800549</v>
+        <v>6800423</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10323,10 +10313,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128814694</v>
+        <v>128804256</v>
       </c>
       <c r="B97" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10334,21 +10324,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10358,10 +10348,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>456594</v>
+        <v>456794</v>
       </c>
       <c r="R97" t="n">
-        <v>6800423</v>
+        <v>6800605</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10391,9 +10381,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10408,22 +10408,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128804256</v>
+        <v>128814637</v>
       </c>
       <c r="B98" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10431,34 +10431,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456794</v>
+        <v>456352</v>
       </c>
       <c r="R98" t="n">
-        <v>6800605</v>
+        <v>6800325</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10488,19 +10496,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10515,22 +10513,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128814637</v>
+        <v>128799696</v>
       </c>
       <c r="B99" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10538,42 +10536,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>456352</v>
+        <v>456668</v>
       </c>
       <c r="R99" t="n">
-        <v>6800325</v>
+        <v>6800363</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10603,9 +10593,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10620,12 +10620,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10739,7 +10739,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805203</v>
+        <v>128804050</v>
       </c>
       <c r="B101" t="n">
         <v>79035</v>
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456650</v>
+        <v>456753</v>
       </c>
       <c r="R101" t="n">
-        <v>6800594</v>
+        <v>6800562</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10820,6 +10820,11 @@
       <c r="AB101" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10846,10 +10851,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128814698</v>
+        <v>128805203</v>
       </c>
       <c r="B102" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10857,21 +10862,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10881,10 +10886,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>456491</v>
+        <v>456650</v>
       </c>
       <c r="R102" t="n">
-        <v>6800537</v>
+        <v>6800594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10914,9 +10919,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10931,22 +10946,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128814624</v>
+        <v>128814698</v>
       </c>
       <c r="B103" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10954,37 +10969,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456688</v>
+        <v>456491</v>
       </c>
       <c r="R103" t="n">
-        <v>6800585</v>
+        <v>6800537</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11025,7 +11037,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11044,7 +11055,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128804050</v>
+        <v>128814737</v>
       </c>
       <c r="B104" t="n">
         <v>79035</v>
@@ -11079,10 +11090,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456753</v>
+        <v>456555</v>
       </c>
       <c r="R104" t="n">
-        <v>6800562</v>
+        <v>6800627</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11112,24 +11123,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11144,44 +11140,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128814713</v>
+        <v>128814624</v>
       </c>
       <c r="B105" t="n">
-        <v>90908</v>
+        <v>79654</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11194,10 +11190,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456692</v>
+        <v>456688</v>
       </c>
       <c r="R105" t="n">
-        <v>6800391</v>
+        <v>6800585</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11257,7 +11253,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128814737</v>
+        <v>128814725</v>
       </c>
       <c r="B106" t="n">
         <v>79035</v>
@@ -11292,10 +11288,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456555</v>
+        <v>456598</v>
       </c>
       <c r="R106" t="n">
-        <v>6800627</v>
+        <v>6800407</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11328,6 +11324,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11354,45 +11355,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814725</v>
+        <v>128814713</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>90908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456598</v>
+        <v>456692</v>
       </c>
       <c r="R107" t="n">
-        <v>6800407</v>
+        <v>6800391</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11427,17 +11431,13 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128814679</v>
+        <v>128805558</v>
       </c>
       <c r="B111" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11772,21 +11772,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456753</v>
+        <v>456627</v>
       </c>
       <c r="R111" t="n">
-        <v>6800533</v>
+        <v>6800521</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11829,9 +11829,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11846,22 +11856,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128814696</v>
+        <v>128814731</v>
       </c>
       <c r="B112" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11869,21 +11879,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11893,10 +11903,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456559</v>
+        <v>456580</v>
       </c>
       <c r="R112" t="n">
-        <v>6800576</v>
+        <v>6800292</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11955,10 +11965,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128803369</v>
+        <v>128814696</v>
       </c>
       <c r="B113" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11966,21 +11976,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11990,10 +12000,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456688</v>
+        <v>456559</v>
       </c>
       <c r="R113" t="n">
-        <v>6800474</v>
+        <v>6800576</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12023,19 +12033,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12050,19 +12050,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128814614</v>
+        <v>128803369</v>
       </c>
       <c r="B114" t="n">
         <v>79654</v>
@@ -12097,10 +12097,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456522</v>
+        <v>456688</v>
       </c>
       <c r="R114" t="n">
-        <v>6800319</v>
+        <v>6800474</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12130,9 +12130,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12147,22 +12157,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128814687</v>
+        <v>128814614</v>
       </c>
       <c r="B115" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12170,21 +12180,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12194,10 +12204,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456556</v>
+        <v>456522</v>
       </c>
       <c r="R115" t="n">
-        <v>6800320</v>
+        <v>6800319</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12256,10 +12266,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128814634</v>
+        <v>128814687</v>
       </c>
       <c r="B116" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12267,42 +12277,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456405</v>
+        <v>456556</v>
       </c>
       <c r="R116" t="n">
-        <v>6800457</v>
+        <v>6800320</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12466,10 +12468,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128805558</v>
+        <v>128814634</v>
       </c>
       <c r="B118" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12477,34 +12479,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456627</v>
+        <v>456405</v>
       </c>
       <c r="R118" t="n">
-        <v>6800521</v>
+        <v>6800457</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12534,19 +12544,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12561,22 +12561,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128814731</v>
+        <v>128814679</v>
       </c>
       <c r="B119" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12584,21 +12584,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12608,10 +12608,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456580</v>
+        <v>456753</v>
       </c>
       <c r="R119" t="n">
-        <v>6800292</v>
+        <v>6800533</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13381,10 +13381,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128816338</v>
+        <v>128816343</v>
       </c>
       <c r="B127" t="n">
-        <v>79625</v>
+        <v>57723</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13392,26 +13392,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13419,10 +13424,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456478</v>
+        <v>456341</v>
       </c>
       <c r="R127" t="n">
-        <v>6800591</v>
+        <v>6800306</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13463,7 +13468,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13482,10 +13486,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128816353</v>
+        <v>128816338</v>
       </c>
       <c r="B128" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13493,34 +13497,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456522</v>
+        <v>456478</v>
       </c>
       <c r="R128" t="n">
-        <v>6800357</v>
+        <v>6800591</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13561,6 +13568,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13579,10 +13587,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128816343</v>
+        <v>128816353</v>
       </c>
       <c r="B129" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13590,42 +13598,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456341</v>
+        <v>456522</v>
       </c>
       <c r="R129" t="n">
-        <v>6800306</v>
+        <v>6800357</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13979,10 +13979,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128816356</v>
+        <v>128816340</v>
       </c>
       <c r="B133" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13990,34 +13990,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>456672</v>
+        <v>456564</v>
       </c>
       <c r="R133" t="n">
-        <v>6800413</v>
+        <v>6800618</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14058,6 +14061,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14076,7 +14080,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128816351</v>
+        <v>128816356</v>
       </c>
       <c r="B134" t="n">
         <v>78792</v>
@@ -14105,19 +14109,16 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>456472</v>
+        <v>456672</v>
       </c>
       <c r="R134" t="n">
-        <v>6800370</v>
+        <v>6800413</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14158,7 +14159,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14177,10 +14177,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128816340</v>
+        <v>128816351</v>
       </c>
       <c r="B135" t="n">
-        <v>79625</v>
+        <v>78792</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14188,21 +14188,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14215,10 +14215,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>456564</v>
+        <v>456472</v>
       </c>
       <c r="R135" t="n">
-        <v>6800618</v>
+        <v>6800370</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14278,10 +14278,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128816331</v>
+        <v>128816335</v>
       </c>
       <c r="B136" t="n">
-        <v>79067</v>
+        <v>79654</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14289,37 +14289,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>456376</v>
+        <v>456564</v>
       </c>
       <c r="R136" t="n">
-        <v>6800472</v>
+        <v>6800617</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14360,7 +14357,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14379,10 +14375,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128816335</v>
+        <v>128816331</v>
       </c>
       <c r="B137" t="n">
-        <v>79654</v>
+        <v>79067</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14390,34 +14386,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>456564</v>
+        <v>456376</v>
       </c>
       <c r="R137" t="n">
-        <v>6800617</v>
+        <v>6800472</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14458,6 +14457,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15066,10 +15066,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128816359</v>
+        <v>128816345</v>
       </c>
       <c r="B144" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15077,34 +15077,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>456335</v>
+        <v>456606</v>
       </c>
       <c r="R144" t="n">
-        <v>6800427</v>
+        <v>6800517</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15163,10 +15171,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816345</v>
+        <v>128816359</v>
       </c>
       <c r="B145" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15174,42 +15182,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Södra Våmsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>456606</v>
+        <v>456335</v>
       </c>
       <c r="R145" t="n">
-        <v>6800517</v>
+        <v>6800427</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 44417-2025 artfynd.xlsx
+++ b/artfynd/A 44417-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128814701</v>
+        <v>128799069</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456547</v>
+        <v>456632</v>
       </c>
       <c r="R2" t="n">
-        <v>6800436</v>
+        <v>6800431</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +748,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128800923</v>
+        <v>128814701</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456692</v>
+        <v>456547</v>
       </c>
       <c r="R3" t="n">
-        <v>6800405</v>
+        <v>6800436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,24 +855,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128799069</v>
+        <v>128800923</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456632</v>
+        <v>456692</v>
       </c>
       <c r="R4" t="n">
-        <v>6800431</v>
+        <v>6800405</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,6 +965,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -5166,7 +5166,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128801266</v>
+        <v>128799698</v>
       </c>
       <c r="B46" t="n">
         <v>79654</v>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456703</v>
+        <v>456668</v>
       </c>
       <c r="R46" t="n">
-        <v>6800429</v>
+        <v>6800363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128799698</v>
+        <v>128801266</v>
       </c>
       <c r="B47" t="n">
         <v>79654</v>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456668</v>
+        <v>456703</v>
       </c>
       <c r="R47" t="n">
-        <v>6800363</v>
+        <v>6800429</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128814735</v>
+        <v>128799700</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6505,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456477</v>
+        <v>456668</v>
       </c>
       <c r="R59" t="n">
-        <v>6800413</v>
+        <v>6800363</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,9 +6562,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6579,19 +6589,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128814734</v>
+        <v>128814735</v>
       </c>
       <c r="B60" t="n">
         <v>79035</v>
@@ -6626,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456472</v>
+        <v>456477</v>
       </c>
       <c r="R60" t="n">
-        <v>6800343</v>
+        <v>6800413</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6688,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128814628</v>
+        <v>128814734</v>
       </c>
       <c r="B61" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6699,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6723,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456549</v>
+        <v>456472</v>
       </c>
       <c r="R61" t="n">
-        <v>6800517</v>
+        <v>6800343</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6785,7 +6795,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128799700</v>
+        <v>128814628</v>
       </c>
       <c r="B62" t="n">
         <v>79625</v>
@@ -6820,10 +6830,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456668</v>
+        <v>456549</v>
       </c>
       <c r="R62" t="n">
-        <v>6800363</v>
+        <v>6800517</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6853,19 +6863,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,12 +6880,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -11355,48 +11355,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128814713</v>
+        <v>128814632</v>
       </c>
       <c r="B107" t="n">
-        <v>90908</v>
+        <v>79625</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5685</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456692</v>
+        <v>456382</v>
       </c>
       <c r="R107" t="n">
-        <v>6800391</v>
+        <v>6800427</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11437,7 +11434,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11452,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128814632</v>
+        <v>128804554</v>
       </c>
       <c r="B108" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11467,21 +11463,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11491,10 +11487,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456382</v>
+        <v>456768</v>
       </c>
       <c r="R108" t="n">
-        <v>6800427</v>
+        <v>6800626</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11524,9 +11520,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11541,19 +11547,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128804554</v>
+        <v>128814683</v>
       </c>
       <c r="B109" t="n">
         <v>78793</v>
@@ -11582,16 +11588,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Millberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>456768</v>
+        <v>456644</v>
       </c>
       <c r="R109" t="n">
-        <v>6800626</v>
+        <v>6800358</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11621,71 +11630,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128814683</v>
+        <v>128814713</v>
       </c>
       <c r="B110" t="n">
-        <v>78793</v>
+        <v>90908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>5685</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456644</v>
+        <v>456692</v>
       </c>
       <c r="R110" t="n">
-        <v>6800358</v>
+        <v>6800391</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -15171,10 +15171,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128816359</v>
+        <v>128816332</v>
       </c>
       <c r="B145" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15182,34 +15182,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+ 